--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -19,7 +19,7 @@
     <sheet name="Changelog" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Changelog'!$A$1:$E$306</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Changelog'!$A$1:$E$307</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E306"/>
+  <dimension ref="A1:E307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11154,8 +11154,35 @@
         </is>
       </c>
     </row>
+    <row r="307" ht="60" customHeight="1">
+      <c r="A307" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B307" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Performance · Cash flow · DEC-2484</t>
+        </is>
+      </c>
+      <c r="C307" s="4" t="inlineStr">
+        <is>
+          <t>Everything changed in the code for the first two batches of the outside review of Net worth is approved: the findings fixed, the defects found while fixing them, and the choices made on the way without asking him. Each stands as built and tested.</t>
+        </is>
+      </c>
+      <c r="D307" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “all the code changes, findings and changes - for batch one and two - I approved.”</t>
+        </is>
+      </c>
+      <c r="E307" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-2484; written here the same day</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E306"/>
+  <autoFilter ref="A1:E307"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -19,7 +19,7 @@
     <sheet name="Changelog" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Changelog'!$A$1:$E$307</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Changelog'!$A$1:$E$308</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E307"/>
+  <dimension ref="A1:E308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11181,8 +11181,35 @@
         </is>
       </c>
     </row>
+    <row r="308" ht="60" customHeight="1">
+      <c r="A308" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B308" s="4" t="inlineStr">
+        <is>
+          <t>App-wide · process · DEC-2634</t>
+        </is>
+      </c>
+      <c r="C308" s="4" t="inlineStr">
+        <is>
+          <t>Every change that comes out of the outside review of the calculations counts as a change he has approved, and is treated the way his own feedback is: recorded in the decision log, the Changelog, the standard it belongs to, the master file, the tracker and the drawings, the same day. Post Feedback Sync is the sweep that brings all of those level with the code — not only the folding-in of his feedback files.</t>
+        </is>
+      </c>
+      <c r="D308" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “The changes we are making with this audit are also changes I am approving, and while not my direct feedback - these are findings and changes.”</t>
+        </is>
+      </c>
+      <c r="E308" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-2634; written here the same day</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E307"/>
+  <autoFilter ref="A1:E308"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E308"/>
+  <dimension ref="A1:E311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11205,6 +11205,87 @@
       <c r="E308" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-2634; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="60" customHeight="1">
+      <c r="A309" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B309" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Performance · DEC-2746</t>
+        </is>
+      </c>
+      <c r="C309" s="4" t="inlineStr">
+        <is>
+          <t>Every change from the third batch of the outside review of Net worth stands as his decision: a car is only a vehicle; the retirement rate and spread are blended over exactly the money set aside, with no invented figure when nothing is; contributions are capped at the legal limit; history is never rounded up to a year; itemising never lowers a total.</t>
+        </is>
+      </c>
+      <c r="D309" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “Commit, Update all revelevant documents, execute PFS, write brief for batch 03 for gemini to re-check all the updates.”</t>
+        </is>
+      </c>
+      <c r="E309" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-2746; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="60" customHeight="1">
+      <c r="A310" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B310" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-2747</t>
+        </is>
+      </c>
+      <c r="C310" s="4" t="inlineStr">
+        <is>
+          <t>Every change from the fourth batch of the outside review of Net worth stands as his decision: the list under the class rows uses the same split as the rows; a money-market settlement fund is a fund; a company name with a bond word is not a bond; with two properties and no use stated, the one entered first is the home; no invented growth or volatility. His "no" means the asset total gains no count of accounts with no value.</t>
+        </is>
+      </c>
+      <c r="D310" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “no. Go ahead and commit this.”</t>
+        </is>
+      </c>
+      <c r="E310" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-2747; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="60" customHeight="1">
+      <c r="A311" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B311" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Bonds · Performance · DEC-2748</t>
+        </is>
+      </c>
+      <c r="C311" s="4" t="inlineStr">
+        <is>
+          <t>Every change from the fifth batch of the outside review of Net worth stands as his decision: a face value or rate never entered is blank, never $0; one rule for a year of interest; a matured bond pays nothing more; yields use the price without accrued interest; the rates-move estimate compares like with like and refuses a CD; years count calendar days; a confirmed account is never re-classed; a record with no accounts is nothing saved.</t>
+        </is>
+      </c>
+      <c r="D311" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “perfect. Commit it all, and execute PFS.”</t>
+        </is>
+      </c>
+      <c r="E311" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-2748; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E311"/>
+  <dimension ref="A1:E327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11286,6 +11286,438 @@
       <c r="E311" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-2748; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B312" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3035</t>
+        </is>
+      </c>
+      <c r="C312" s="4" t="inlineStr">
+        <is>
+          <t>His approval of the second-round review of Net worth batches 2, 3 and 4, as a whole. Each rule it approved is its own row beside this one.</t>
+        </is>
+      </c>
+      <c r="D312" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “here are second round audit files for batches 2,3,4.” — approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E312" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3035; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B313" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3035b</t>
+        </is>
+      </c>
+      <c r="C313" s="4" t="inlineStr">
+        <is>
+          <t>The retirement money’s twelve-month return weighs each account by what was set aside when the year began: Σ now ÷ Σ start − 1. Before: weighed by today’s amounts, 13.72% where 12.98% is right.</t>
+        </is>
+      </c>
+      <c r="D313" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “here are second round audit files for batches 2,3,4.” — approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E313" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3035b; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B314" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3035c</t>
+        </is>
+      </c>
+      <c r="C314" s="4" t="inlineStr">
+        <is>
+          <t>A 529’s and an HSA’s tax words are fixed by what they are; ‘(Roth)’ appears only for an account in the Roth bucket. Before: a 529 stated tax-free read ‘tax-free (Roth)’.</t>
+        </is>
+      </c>
+      <c r="D314" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “here are second round audit files for batches 2,3,4.” — approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E314" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3035c; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B315" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3035d</t>
+        </is>
+      </c>
+      <c r="C315" s="4" t="inlineStr">
+        <is>
+          <t>A hand-built account is split holding by holding, so a T-bill inside it is Bonds &amp; CDs. Before: everything but its cash was filed under the account’s own class.</t>
+        </is>
+      </c>
+      <c r="D315" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “here are second round audit files for batches 2,3,4.” — approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E315" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3035d; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B316" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3035e</t>
+        </is>
+      </c>
+      <c r="C316" s="4" t="inlineStr">
+        <is>
+          <t>A Roth 401(k) reads Roth 401(k), and a tax-advantaged account with no kind and known digits shows its tax word. Before: ‘Fidelity 401(k)’ for both a Roth and a pre-tax 401(k); ‘Vanguard -1234’ for a Roth.</t>
+        </is>
+      </c>
+      <c r="D316" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “here are second round audit files for batches 2,3,4.” — approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E316" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3035e; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B317" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3035f</t>
+        </is>
+      </c>
+      <c r="C317" s="4" t="inlineStr">
+        <is>
+          <t>A holding with nothing stored — no tag, no kind, nothing in its name — is Unclassified, never Stocks / Funds by default. Before: it was filed as Stocks / Funds (against DEC-2160).</t>
+        </is>
+      </c>
+      <c r="D317" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “here are second round audit files for batches 2,3,4.” — approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E317" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3035f; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B318" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3035g</t>
+        </is>
+      </c>
+      <c r="C318" s="4" t="inlineStr">
+        <is>
+          <t>Broker Treasury wording (TREAS, UST, T-bond) counts as a Treasury in the words under an account, and more than one reads Treasuries. Before: a broker’s T-bill read ‘1 bond’.</t>
+        </is>
+      </c>
+      <c r="D318" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “here are second round audit files for batches 2,3,4.” — approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E318" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3035g; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B319" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3035h</t>
+        </is>
+      </c>
+      <c r="C319" s="4" t="inlineStr">
+        <is>
+          <t>A value dated by its month alone is shown as the 1st of that month. Before: the stored text was handed back unchanged.</t>
+        </is>
+      </c>
+      <c r="D319" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “here are second round audit files for batches 2,3,4.” — approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E319" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3035h; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B320" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3035i</t>
+        </is>
+      </c>
+      <c r="C320" s="4" t="inlineStr">
+        <is>
+          <t>Performance draws no walk for a window its record exists but cannot reach; a sentence names the record’s first day. Before: the beginning was worked back from today and wealth generated shown as if measured.</t>
+        </is>
+      </c>
+      <c r="D320" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “here are second round audit files for batches 2,3,4.” — approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E320" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3035i; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B321" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3035j</t>
+        </is>
+      </c>
+      <c r="C321" s="4" t="inlineStr">
+        <is>
+          <t>A rate the person set themselves is labelled an estimate. Before: it took the record’s flag.</t>
+        </is>
+      </c>
+      <c r="D321" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “here are second round audit files for batches 2,3,4.” — approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E321" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3035j; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B322" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3035k</t>
+        </is>
+      </c>
+      <c r="C322" s="4" t="inlineStr">
+        <is>
+          <t>An employer’s percent match is taken on the 401(k) figure after the yearly limit. Before: on the figure as typed — $1,600 where $1,490 is right.</t>
+        </is>
+      </c>
+      <c r="D322" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “here are second round audit files for batches 2,3,4.” — approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E322" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3035k; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B323" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3035l</t>
+        </is>
+      </c>
+      <c r="C323" s="4" t="inlineStr">
+        <is>
+          <t>History shared is rounded down and its sentence built from whole months only. Before: one day short of a year read ‘1 year’.</t>
+        </is>
+      </c>
+      <c r="D323" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “here are second round audit files for batches 2,3,4.” — approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E323" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3035l; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B324" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3035m</t>
+        </is>
+      </c>
+      <c r="C324" s="4" t="inlineStr">
+        <is>
+          <t>Accounts made by itemising carry the typical rate for their class, never 0%, and a bond rate not entered stays blank. Before: every itemised account had a 0% rate.</t>
+        </is>
+      </c>
+      <c r="D324" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “here are second round audit files for batches 2,3,4.” — approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E324" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3035m; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B325" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3035n</t>
+        </is>
+      </c>
+      <c r="C325" s="4" t="inlineStr">
+        <is>
+          <t>The Other investments summary reads the class split, so its total is the Alternatives line’s dollars and each part is rated by what it is. Before: whole accounts only — $18,641 where the Alternatives line read $23,031.</t>
+        </is>
+      </c>
+      <c r="D325" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “here are second round audit files for batches 2,3,4.” — approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E325" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3035n; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B326" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3035o</t>
+        </is>
+      </c>
+      <c r="C326" s="4" t="inlineStr">
+        <is>
+          <t>A property’s name is not read as evidence of its class; a fund that writes options is a fund. Before: ‘Silver Lake house’ read as an alternative and a covered-call ETF as options.</t>
+        </is>
+      </c>
+      <c r="D326" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “here are second round audit files for batches 2,3,4.” — approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E326" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3035o; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B327" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3035p</t>
+        </is>
+      </c>
+      <c r="C327" s="4" t="inlineStr">
+        <is>
+          <t>What a property is for has one reading for every function; handed the rent entries, a property is a rental only when an entry names it, and a household with no home is told so. Before: three functions read it three ways; a rented-out house marked home counted as the home.</t>
+        </is>
+      </c>
+      <c r="D327" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “here are second round audit files for batches 2,3,4.” — approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E327" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3035p; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E327"/>
+  <dimension ref="A1:E328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11718,6 +11718,33 @@
       <c r="E327" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3035p; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B328" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3146</t>
+        </is>
+      </c>
+      <c r="C328" s="4" t="inlineStr">
+        <is>
+          <t>Under each class heading, every account that holds money in that class is listed by its name with only its part in that class (for example Vanguard -0008 $45,000, Chase -0333 $34,000), so the rows under a heading add up to the heading. It replaces the batch 4 rule that listed a split account once, under its largest class, at its whole balance.</t>
+        </is>
+      </c>
+      <c r="D328" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-07: “no need for mockup. build it per mockup 07 where under each class you list each account Vanguard-0008 $45000, Chase - 0333 $34000. THe rule you changed in batch…”</t>
+        </is>
+      </c>
+      <c r="E328" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3146; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E328"/>
+  <dimension ref="A1:E338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11745,6 +11745,276 @@
       <c r="E328" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-3146; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B329" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3279</t>
+        </is>
+      </c>
+      <c r="C329" s="4" t="inlineStr">
+        <is>
+          <t>His approval of the batch 06 fix brief, as a whole. Each rule is its own row beside this one.</t>
+        </is>
+      </c>
+      <c r="D329" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-08: “from claude” — the batch 06 fix brief, approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E329" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-08) — recorded in the decision log as DEC-3279; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B330" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3279b</t>
+        </is>
+      </c>
+      <c r="C330" s="4" t="inlineStr">
+        <is>
+          <t>Years to maturity are exact, by anniversaries: one year to the day is exactly 1. Before: days ÷ 365.25 (0.9993 for one year).</t>
+        </is>
+      </c>
+      <c r="D330" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-08: “from claude” — the batch 06 fix brief, approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E330" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-08) — recorded in the decision log as DEC-3279b; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B331" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3279c</t>
+        </is>
+      </c>
+      <c r="C331" s="4" t="inlineStr">
+        <is>
+          <t>A bond is priced at exact times, its yearly coupon on each maturity anniversary; a matured bond or one with no date has no price. Before: years rounded to a whole number, at least 1, so a matured bond still paid.</t>
+        </is>
+      </c>
+      <c r="D331" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-08: “from claude” — the batch 06 fix brief, approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E331" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-08) — recorded in the decision log as DEC-3279c; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B332" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3279d</t>
+        </is>
+      </c>
+      <c r="C332" s="4" t="inlineStr">
+        <is>
+          <t>Yield to maturity is solved exactly on the full value as entered; a CD yields its stated rate. Before: the textbook approximation — a short 4% note read −0.69% where 5.73% is right.</t>
+        </is>
+      </c>
+      <c r="D332" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-08: “from claude” — the batch 06 fix brief, approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E332" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-08) — recorded in the decision log as DEC-3279d; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B333" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3279e</t>
+        </is>
+      </c>
+      <c r="C333" s="4" t="inlineStr">
+        <is>
+          <t>A missing balance is never $0: it is left out of the total and the amber box names the account. Before: a linked account that failed to sync added 0 and the total looked complete.</t>
+        </is>
+      </c>
+      <c r="D333" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-08: “from claude” — the batch 06 fix brief, approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E333" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-08) — recorded in the decision log as DEC-3279e; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B334" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3279f</t>
+        </is>
+      </c>
+      <c r="C334" s="4" t="inlineStr">
+        <is>
+          <t>Itemised sums are exact decimals, a holding with no value is left out, and the remainder is then not final. Before: a missing value was 0 and the remainder looked complete; sums could leave a fraction of a cent.</t>
+        </is>
+      </c>
+      <c r="D334" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-08: “from claude” — the batch 06 fix brief, approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E334" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-08) — recorded in the decision log as DEC-3279f; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B335" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3279g</t>
+        </is>
+      </c>
+      <c r="C335" s="4" t="inlineStr">
+        <is>
+          <t>A kind that names contents — crypto, private equity, hedge funds, other — claims no Brokerage wrapper unless the person confirmed one. Before: ‘Coinbase Brokerage’ for a crypto wallet.</t>
+        </is>
+      </c>
+      <c r="D335" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-08: “from claude” — the batch 06 fix brief, approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E335" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-08) — recorded in the decision log as DEC-3279g; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B336" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3279h</t>
+        </is>
+      </c>
+      <c r="C336" s="4" t="inlineStr">
+        <is>
+          <t>CDs, certificates of deposit and share certificates are recognised as CDs; ABCD Growth Fund is not. Before: ‘No-Penalty CDs’ was not a CD.</t>
+        </is>
+      </c>
+      <c r="D336" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-08: “from claude” — the batch 06 fix brief, approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E336" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-08) — recorded in the decision log as DEC-3279h; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B337" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3279i</t>
+        </is>
+      </c>
+      <c r="C337" s="4" t="inlineStr">
+        <is>
+          <t>The accrued-interest note shows only for a bond that pays interest and has no accrued figure entered. Before: a zero-coupon bond got the note.</t>
+        </is>
+      </c>
+      <c r="D337" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-08: “from claude” — the batch 06 fix brief, approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E337" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-08) — recorded in the decision log as DEC-3279i; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B338" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3279j</t>
+        </is>
+      </c>
+      <c r="C338" s="4" t="inlineStr">
+        <is>
+          <t>Dates are read as calendar dates, never shifted by a time zone; an empty date shows nothing. Before: a midnight-UTC date could show the day before in Pacific time.</t>
+        </is>
+      </c>
+      <c r="D338" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-08: “from claude” — the batch 06 fix brief, approved under his standing word (DEC-2634)</t>
+        </is>
+      </c>
+      <c r="E338" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-08) — recorded in the decision log as DEC-3279j; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E338"/>
+  <dimension ref="A1:E339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12015,6 +12015,33 @@
       <c r="E338" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-08) — recorded in the decision log as DEC-3279j; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B339" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Bonds · DEC-3390</t>
+        </is>
+      </c>
+      <c r="C339" s="4" t="inlineStr">
+        <is>
+          <t>The value typed for a bond is what the statement shows, which leaves out the interest earned since the last coupon. For the yield to maturity, that interest is added: the figure entered, or an estimate from the coupon schedule, and then the screen reads: "Added estimated $1,119 in accrued interest to bond value at 4.5% coupon for 363 days to calculate YTM. If this is not accurate, enter actual accrued interest". The yield on today's value is on the value as entered. A $25,000 4.5% Treasury worth $24,200 two days before its coupon now reads 5.69%, not 7.44%.</t>
+        </is>
+      </c>
+      <c r="D339" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-09: “I like your recommendation to add accrued interest. Say …”</t>
+        </is>
+      </c>
+      <c r="E339" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-09) — recorded in the decision log as DEC-3390; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E339"/>
+  <dimension ref="A1:E340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12042,6 +12042,33 @@
       <c r="E339" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-09) — recorded in the decision log as DEC-3390; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B340" s="4" t="inlineStr">
+        <is>
+          <t>App-wide · tenets · DEC-3523</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr">
+        <is>
+          <t>The eight tenets are approved, in this order: 1. A wrong number ends trust. 2. Every number shows how it was made. 3. Unknown is not zero. 4. One thing, one number, one word. 5. The person's word outranks the app's guess. 6. His decision is the design. 7. Honest like a fiduciary. 8. Plain words for a reader of 55 to 70. When two pull against each other, the higher one wins.</t>
+        </is>
+      </c>
+      <c r="D340" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-09: “tenets approved”</t>
+        </is>
+      </c>
+      <c r="E340" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-09) — recorded in the decision log as DEC-3523; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E340"/>
+  <dimension ref="A1:E342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12069,6 +12069,60 @@
       <c r="E340" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-09) — recorded in the decision log as DEC-3523; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B341" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Performance · DEC-3656</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="inlineStr">
+        <is>
+          <t>When the daily record does not reach back to the window's first day, the beginning is worked back from today. A CD with a stated rate gains by its rate ($10,500 at 5% for a year gained $500); a holding with no price history and no rate — a bond typed by hand — leaves that account with no beginning and no wealth generated, and a sentence names it: "The beginning can't be worked back: Treasury 2031 has no price history." Before: its gain counted $0, so the beginning read too high.</t>
+        </is>
+      </c>
+      <c r="D341" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-09: “MK-NW-F-091 - recommend #1 and 2 approved.”</t>
+        </is>
+      </c>
+      <c r="E341" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-09) — recorded in the decision log as DEC-3656; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B342" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-3657</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="inlineStr">
+        <is>
+          <t>A missing balance on Net worth reads "Value not entered" — an account row, a bank, a class, a group, a debt row. By institution: "Ally · Value not entered". Before: "Ally · not entered".</t>
+        </is>
+      </c>
+      <c r="D342" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-09: “"Ally · not entered" is Ally name of bank? Should say "Ally . Value not entered"”</t>
+        </is>
+      </c>
+      <c r="E342" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-09) — recorded in the decision log as DEC-3657; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E342"/>
+  <dimension ref="A1:E346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12123,6 +12123,114 @@
       <c r="E342" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-09) — recorded in the decision log as DEC-3657; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B343" s="4" t="inlineStr">
+        <is>
+          <t>Performance · DEC-3768b</t>
+        </is>
+      </c>
+      <c r="C343" s="4" t="inlineStr">
+        <is>
+          <t>A window that reaches back whole months (1M, 3M, 6M, 1Y, 2Y) stops at the month's last day: Mar 31 less one month is Feb 28; Feb 29 less a year is Feb 28. Before: 1M from Mar 31 started Mar 3 — a 28-day window.</t>
+        </is>
+      </c>
+      <c r="D343" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “#2,3 - approved.”</t>
+        </is>
+      </c>
+      <c r="E343" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-3768b; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B344" s="4" t="inlineStr">
+        <is>
+          <t>Income · Net worth · DEC-3768c</t>
+        </is>
+      </c>
+      <c r="C344" s="4" t="inlineStr">
+        <is>
+          <t>A rent or running-cost figure with words in it ("about 2k") is not read: it counts as not entered, and the Income screen's rent fields keep digits only. Before: "about 2k" was read as $2 and the property counted as a rental.</t>
+        </is>
+      </c>
+      <c r="D344" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “#2,3 - approved.”</t>
+        </is>
+      </c>
+      <c r="E344" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-3768c; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B345" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Emergency fund · DEC-3769</t>
+        </is>
+      </c>
+      <c r="C345" s="4" t="inlineStr">
+        <is>
+          <t>When a property's rent is not known (entry blank or unreadable), the emergency fund still gives its months, counted without that rent, and says: "5 months, rent not included. Enter rent to include."</t>
+        </is>
+      </c>
+      <c r="D345" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “#1: How about we say "5 month xx, rent not included. Enter rent to include." instead of just showing nothing.”</t>
+        </is>
+      </c>
+      <c r="E345" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-3769; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B346" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Income · Net worth · DEC-3768</t>
+        </is>
+      </c>
+      <c r="C346" s="4" t="inlineStr">
+        <is>
+          <t>His approval of items 2 and 3 of the open points from OpenAI's final audit of Net worth, as a whole: (a) a window reaching back whole months stops at the month's last day (DEC-3768b); (b) a rent figure with words in it is refused (DEC-3768c). Each has its own row.</t>
+        </is>
+      </c>
+      <c r="D346" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “#2,3 - approved.”</t>
+        </is>
+      </c>
+      <c r="E346" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-3768; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E346"/>
+  <dimension ref="A1:E348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12231,6 +12231,60 @@
       <c r="E346" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-3768; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B347" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Job safety · Stress test · DEC-3836</t>
+        </is>
+      </c>
+      <c r="C347" s="4" t="inlineStr">
+        <is>
+          <t>The "rent not included. Enter rent to include." line (DEC-3769) sits with the emergency fund's months wherever they show — Net worth, Job safety and Stress test. Before: only Net worth carried it.</t>
+        </is>
+      </c>
+      <c r="D347" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: approved my recommendation (“…I recommend adding it there too… - approved.”)</t>
+        </is>
+      </c>
+      <c r="E347" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-3836; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B348" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Bonds · Add an account · DEC-3837</t>
+        </is>
+      </c>
+      <c r="C348" s="4" t="inlineStr">
+        <is>
+          <t>Adding a CD asks once: "Bought from the bank, or through a broker?" A bank CD yields its interest rate and gets no if-rates-move estimate; a broker CD is worked out like a bond ($10,000 face, 4.2%, worth $9,850, 2 years left → about 5.0%) and gets the estimate. Before: every CD showed its interest rate as its yield to maturity.</t>
+        </is>
+      </c>
+      <c r="D348" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “… yield to maturity could be different from coupon/interest rate % for CD bought in secondary market … #4 - yes”</t>
+        </is>
+      </c>
+      <c r="E348" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-3837; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E348"/>
+  <dimension ref="A1:E365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12285,6 +12285,465 @@
       <c r="E348" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-3837; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B349" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Bonds · Plan · DEC-4036</t>
+        </is>
+      </c>
+      <c r="C349" s="4" t="inlineStr">
+        <is>
+          <t>His answers on OpenAI's open Net worth points: undated bond keeps its interest, row says 'maturity date not entered' (b); CD never read from the institution (c); 529 always tax-free for education (d); HSA always pre-tax (e); no tax type is never assumed taxable (f); 'savings or portfolio' asked about (g); '$1,500 asset type not classified' (h); overdraft is negative cash (i); a vehicle with no value named (j); retirement money names what it leaves out (k).</t>
+        </is>
+      </c>
+      <c r="D349" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “1 to 5 - Approved … 7 - approved … 11: "$1500 asset type not classified". 12: approved. 13: approved. 14: approved.”</t>
+        </is>
+      </c>
+      <c r="E349" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-4036 (parts b–k); written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B350" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Income · DEC-4059</t>
+        </is>
+      </c>
+      <c r="C350" s="4" t="inlineStr">
+        <is>
+          <t>Date pickers for every bond and CD date (b); an unreadable history start date says 'History start date cannot be read. Edit date' and can be corrected (c); a rent entry is not counted until its property is picked (d).</t>
+        </is>
+      </c>
+      <c r="D350" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “8: … Use date picker for date. 9: Say date cannot be read. Edit date … 10 -approved.”</t>
+        </is>
+      </c>
+      <c r="E350" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-4059 (parts b–d); written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B351" s="4" t="inlineStr">
+        <is>
+          <t>App-wide · DEC-4082</t>
+        </is>
+      </c>
+      <c r="C351" s="4" t="inlineStr">
+        <is>
+          <t>Counted words take their plural from one list of every counted word and its plural (2 Treasuries, 0 properties); the risk swing for Will my money last is parked until the Plan module.</t>
+        </is>
+      </c>
+      <c r="D351" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “6 - let's park for now, and 15 - why not go ahead and make a list of words and plurals.”</t>
+        </is>
+      </c>
+      <c r="E351" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-4082; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B352" s="4" t="inlineStr">
+        <is>
+          <t>Plan · DEC-4105</t>
+        </is>
+      </c>
+      <c r="C352" s="4" t="inlineStr">
+        <is>
+          <t>Withdrawal planning counts an account whose tax the app cannot tell as taxable and names it: 'Brokerage — tax type not stated; counted as taxable until you choose.' The split reads tax as the account page does, so a 401(k) with no stored type is pre-tax.</t>
+        </is>
+      </c>
+      <c r="D352" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “… counted as taxable for the plan, with a line naming it … approved”</t>
+        </is>
+      </c>
+      <c r="E352" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-4105; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B353" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-4036b</t>
+        </is>
+      </c>
+      <c r="C353" s="4" t="inlineStr">
+        <is>
+          <t>A bond or CD with no maturity date entered keeps counting its interest (DEC-0332: unknown, not matured); its row reads "maturity date not entered". Treasury $10,000 at 4%, no date: $400 a year counted.</t>
+        </is>
+      </c>
+      <c r="D353" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “1 to 5 - Approved … 7 - approved … 11 … 12: approved. 13: approved. 14: approved.”</t>
+        </is>
+      </c>
+      <c r="E353" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-4036b; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B354" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-4036c</t>
+        </is>
+      </c>
+      <c r="C354" s="4" t="inlineStr">
+        <is>
+          <t>"CD" is read only from an account's own name or type, never from its institution's name. A brokerage account at "CD Capital" is not a CD.</t>
+        </is>
+      </c>
+      <c r="D354" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “1 to 5 - Approved … 7 - approved … 11 … 12: approved. 13: approved. 14: approved.”</t>
+        </is>
+      </c>
+      <c r="E354" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-4036c; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B355" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-4036d</t>
+        </is>
+      </c>
+      <c r="C355" s="4" t="inlineStr">
+        <is>
+          <t>A 529 is always tax-free for education, whatever tax setting is stored; its type decides (DEC-3035c). Before: a 529 stored "taxable" was counted as taxable while its page said tax-free.</t>
+        </is>
+      </c>
+      <c r="D355" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “1 to 5 - Approved … 7 - approved … 11 … 12: approved. 13: approved. 14: approved.”</t>
+        </is>
+      </c>
+      <c r="E355" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-4036d; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B356" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-4036e</t>
+        </is>
+      </c>
+      <c r="C356" s="4" t="inlineStr">
+        <is>
+          <t>An HSA is always pre-tax going in and tax-free for medical costs, whatever bucket it is filed in. Before: an HSA filed under Roth was counted as tax-free going in.</t>
+        </is>
+      </c>
+      <c r="D356" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “1 to 5 - Approved … 7 - approved … 11 … 12: approved. 13: approved. 14: approved.”</t>
+        </is>
+      </c>
+      <c r="E356" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-4036e; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B357" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-4036f</t>
+        </is>
+      </c>
+      <c r="C357" s="4" t="inlineStr">
+        <is>
+          <t>An account with no account type chosen is never assumed taxable: its tax reads "tax type not stated" with a tap to choose. Before: counted and shown as a taxable brokerage.</t>
+        </is>
+      </c>
+      <c r="D357" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “1 to 5 - Approved … 7 - approved … 11 … 12: approved. 13: approved. 14: approved.”</t>
+        </is>
+      </c>
+      <c r="E357" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-4036f; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B358" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-4036g</t>
+        </is>
+      </c>
+      <c r="C358" s="4" t="inlineStr">
+        <is>
+          <t>The old sign-up answer "savings or portfolio" is filed Unclassified and asked about: "Is this cash savings or investments?" (DEC-2160). Before: always Stocks / Funds at 7%.</t>
+        </is>
+      </c>
+      <c r="D358" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “1 to 5 - Approved … 7 - approved … 11 … 12: approved. 13: approved. 14: approved.”</t>
+        </is>
+      </c>
+      <c r="E358" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-4036g; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B359" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-4036h</t>
+        </is>
+      </c>
+      <c r="C359" s="4" t="inlineStr">
+        <is>
+          <t>Money left in an alternatives part that no priced holding explains is shown as "$1,500 asset type not classified" — never labelled Other or given a growth rate. Before: "Other" at 5%.</t>
+        </is>
+      </c>
+      <c r="D359" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “1 to 5 - Approved … 7 - approved … 11 … 12: approved. 13: approved. 14: approved.”</t>
+        </is>
+      </c>
+      <c r="E359" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-4036h; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B360" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-4036i</t>
+        </is>
+      </c>
+      <c r="C360" s="4" t="inlineStr">
+        <is>
+          <t>An overdrawn hand-built account is negative cash: balance −$100 with a cash field of $50 is Cash −$100. Before: Cash $0 and Unclassified −$100.</t>
+        </is>
+      </c>
+      <c r="D360" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “1 to 5 - Approved … 7 - approved … 11 … 12: approved. 13: approved. 14: approved.”</t>
+        </is>
+      </c>
+      <c r="E360" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-4036i; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B361" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-4036j</t>
+        </is>
+      </c>
+      <c r="C361" s="4" t="inlineStr">
+        <is>
+          <t>Where a vehicle's value is not entered, the car you drive is still picked among the vehicles with a value, and a line says: "Car A's value not entered — it may be the car you drive."</t>
+        </is>
+      </c>
+      <c r="D361" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “1 to 5 - Approved … 7 - approved … 11 … 12: approved. 13: approved. 14: approved.”</t>
+        </is>
+      </c>
+      <c r="E361" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-4036j; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B362" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-4036k</t>
+        </is>
+      </c>
+      <c r="C362" s="4" t="inlineStr">
+        <is>
+          <t>The retirement money on the Plan screens names an account it leaves out: "leaves out Linked 401(k) — Value not entered" (DEC-3657 wording). Before: $10,000 with no note.</t>
+        </is>
+      </c>
+      <c r="D362" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “1 to 5 - Approved … 7 - approved … 11 … 12: approved. 13: approved. 14: approved.”</t>
+        </is>
+      </c>
+      <c r="E362" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-4036k; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B363" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-4059b</t>
+        </is>
+      </c>
+      <c r="C363" s="4" t="inlineStr">
+        <is>
+          <t>Every date a person enters for a bond or CD is picked from a date picker, never typed — the Net worth account editor too (it had a typed "Matures YYYY-MM" box). The app is not launched, so no typed date exists to carry over.</t>
+        </is>
+      </c>
+      <c r="D363" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “8: … Use date picker for date. 9: Say date cannot be read. Edit date … 10 -approved.”</t>
+        </is>
+      </c>
+      <c r="E363" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-4059b; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B364" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-4059c</t>
+        </is>
+      </c>
+      <c r="C364" s="4" t="inlineStr">
+        <is>
+          <t>When a linked account's history start date cannot be read (a date in the future, or not a date), the history line says "History start date cannot be read. Edit date", and a tap lets the person enter or correct the date with a date picker; the sentence then uses their date. Before: "a few days of history (from )".</t>
+        </is>
+      </c>
+      <c r="D364" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “8: … Use date picker for date. 9: Say date cannot be read. Edit date … 10 -approved.”</t>
+        </is>
+      </c>
+      <c r="E364" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-4059c; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B365" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-4059d</t>
+        </is>
+      </c>
+      <c r="C365" s="4" t="inlineStr">
+        <is>
+          <t>A rent entry cannot be saved until the property it is for is picked. With no property in Net worth, the entry says "Add the property in Net worth first" and links there; an older entry with no property shows the question in amber until answered.</t>
+        </is>
+      </c>
+      <c r="D365" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “8: … Use date picker for date. 9: Say date cannot be read. Edit date … 10 -approved.”</t>
+        </is>
+      </c>
+      <c r="E365" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-4059d; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E365"/>
+  <dimension ref="A1:E367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12744,6 +12744,60 @@
       <c r="E365" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-10) — recorded in the decision log as DEC-4059d; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B366" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding · Income · DEC-4327</t>
+        </is>
+      </c>
+      <c r="C366" s="4" t="inlineStr">
+        <is>
+          <t>When sign-up's rent step comes after a property was entered, it asks "Which property is it?" right there, so rent entered at sign-up counts at once. With no property entered yet it keeps its line: "The rent is counted once you pick its property on the Income screen." Before: sign-up never asked, so its rent was not counted until the property was picked on the Income screen (DEC-4059d).</t>
+        </is>
+      </c>
+      <c r="D366" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-10: “1: yes”</t>
+        </is>
+      </c>
+      <c r="E366" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat) — recorded in the decision log as DEC-4327; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B367" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding · Income · DEC-4350</t>
+        </is>
+      </c>
+      <c r="C367" s="4" t="inlineStr">
+        <is>
+          <t>Sign-up asks for rent before any property can exist, so its rent step carries a door: "Add the property first ›". It opens Add an account set to Real estate; saving brings the person back to the rent step, which asks "Which property is it?"; once picked, the rent counts at once. About 3 taps plus typing, without leaving sign-up. Before: the rent was kept but counted nowhere until the person added the property in Net worth and picked it on the Income screen, about 7 taps after sign-up.</t>
+        </is>
+      </c>
+      <c r="D367" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-11: “A - approved.”</t>
+        </is>
+      </c>
+      <c r="E367" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat) — recorded in the decision log as DEC-4350; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E367"/>
+  <dimension ref="A1:E368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12798,6 +12798,33 @@
       <c r="E367" s="4" t="inlineStr">
         <is>
           <t>Founder (chat) — recorded in the decision log as DEC-4350; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B368" s="4" t="inlineStr">
+        <is>
+          <t>Performance · DEC-4439</t>
+        </is>
+      </c>
+      <c r="C368" s="4" t="inlineStr">
+        <is>
+          <t>The time-weighted return counts money that moves on a day for that whole day: a day’s growth is the evening value ÷ (the previous evening’s value + money added that day − money taken out that day) − 1. A first deposit into a new account is now measured ($10,000 worth $10,050 that evening: +0.50%; worth $9,800: −2.00%), a value below the money just added is a loss rather than a refusal, and Vanguard ($50,000, $10,000 added in the morning, $60,300 that evening) reads +0.50%, not +0.60%. The refusal for a value below the money added, and its two sentences, are gone; a day with nothing to grow from still shows no percent and one sentence. Performance v17 carries a READ THIS FIRST row; no drawn return moves (the phones give no day for the money moved).</t>
+        </is>
+      </c>
+      <c r="D368" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-11: “approved.” — after asking why a $10,000 first deposit worth $10,050 that evening showed no return.</t>
+        </is>
+      </c>
+      <c r="E368" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-11) — recorded in the decision log as DEC-4439; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E368"/>
+  <dimension ref="A1:E370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12825,6 +12825,60 @@
       <c r="E368" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-11) — recorded in the decision log as DEC-4439; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B369" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-4528</t>
+        </is>
+      </c>
+      <c r="C369" s="4" t="inlineStr">
+        <is>
+          <t>With no debt entered, the Debts section's door reads "Add your debts ›" — the wording of the approved empty-state drawing. Before: Net worth v08 state C drew "Add a mortgage, card, or loan ›" while the empty-state drawing drew "Add your debts ›".</t>
+        </is>
+      </c>
+      <c r="D369" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-11: “1: "Add your debts &gt;"”</t>
+        </is>
+      </c>
+      <c r="E369" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-11) — recorded in the decision log as DEC-4528; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B370" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Bonds · Other investments · Holding detail · DEC-4529</t>
+        </is>
+      </c>
+      <c r="C370" s="4" t="inlineStr">
+        <is>
+          <t>Where an approved drawing shows a figure that is wrong and the app is right, the drawing is left as drawn and its READ THIS FIRST box gets a line naming the figure, what the drawing shows, what is right, and why, with the arithmetic — Net worth v08 B −0.40% → −0.41%; E (Aug 4) → (Aug 11); F 7 days → 14 days; Bonds v02 years left 2y/4y/1y → 1y/3y/0y; Other investments v02 "Annuity" → "Annuities"; Holding detail v02 gain $7,400.00 + $1,957.60 → $7,384 + $1,974 in whole dollars. And the edit sheet of a home (any property) no longer asks "What's it invested in?".</t>
+        </is>
+      </c>
+      <c r="D370" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-11: “agree - leave the drawing, add line detailing correction … ok”</t>
+        </is>
+      </c>
+      <c r="E370" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-11) — recorded in the decision log as DEC-4529; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E370"/>
+  <dimension ref="A1:E377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12879,6 +12879,195 @@
       <c r="E370" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-11) — recorded in the decision log as DEC-4529; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B371" s="4" t="inlineStr">
+        <is>
+          <t>Performance · DEC-4640</t>
+        </is>
+      </c>
+      <c r="C371" s="4" t="inlineStr">
+        <is>
+          <t>A window name the app does not have (for example "5Y") gives no figure — never a guessed start. One table of window names is read by startDateFor and windowStartKey; "Since" has its first day handed over (it was read as today, so a holding's Since figure was one day's move).</t>
+        </is>
+      </c>
+      <c r="D371" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-12: “1, 2 - approved.”</t>
+        </is>
+      </c>
+      <c r="E371" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-12) — recorded in the decision log as DEC-4640; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B372" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account portfolio · Holding detail · DEC-4641</t>
+        </is>
+      </c>
+      <c r="C372" s="4" t="inlineStr">
+        <is>
+          <t>A holding whose prices begin after the window opens is measured from its first price; wherever its window figure shows, the line reads "Prices for this holding go back 5 months, so the 1-year figure covers 5 months — not a year." One function writes it; the Account page's holding rows now carry it too.</t>
+        </is>
+      </c>
+      <c r="D372" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-12: “1, 2 - approved.”</t>
+        </is>
+      </c>
+      <c r="E372" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-12) — recorded in the decision log as DEC-4641; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B373" s="4" t="inlineStr">
+        <is>
+          <t>Performance · DEC-4642</t>
+        </is>
+      </c>
+      <c r="C373" s="4" t="inlineStr">
+        <is>
+          <t>Six functions no screen called are removed and their numbers retired: MK-PF-F-003 avgCost, MK-PF-F-016 attribution, MK-PF-F-017 allocation, MK-PF-F-018 portfolioTrend, MK-PF-F-019 portfolioPeriodReturn, MK-PF-F-021 periodDollarDelta. Their replacements: theHolding's average paid, thePerformance's time-weighted return and wealth generated, the graph from the saved daily values.</t>
+        </is>
+      </c>
+      <c r="D373" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-12: “3 - … are there new functions to replace these?” then “3,4, 8-approved.”</t>
+        </is>
+      </c>
+      <c r="E373" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-12) — recorded in the decision log as DEC-4642; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B374" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · DEC-4643</t>
+        </is>
+      </c>
+      <c r="C374" s="4" t="inlineStr">
+        <is>
+          <t>A sale bigger than the purchases on record (a linked broker sends about two years of activity) is counted once: bought 10 at $50, sold 15 at $70 → "$200 gain on 10 of 15 shares sold; what you paid for the other 5 is not on record." It read as two sales.</t>
+        </is>
+      </c>
+      <c r="D374" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-12: “4 - why the app does not block user from selling more than what's in portfolio.” then “3,4, 8-approved.”</t>
+        </is>
+      </c>
+      <c r="E374" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-12) — recorded in the decision log as DEC-4643; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B375" s="4" t="inlineStr">
+        <is>
+          <t>Performance · DEC-4644</t>
+        </is>
+      </c>
+      <c r="C375" s="4" t="inlineStr">
+        <is>
+          <t>A holding's return includes its dividends once: the price feed is dividend-adjusted, so a beginning worked back from each holding's return does not take the dividends off again ($100,000, not $98,800). His existing rule, recorded — not a new ruling.</t>
+        </is>
+      </c>
+      <c r="D375" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-12: “6, 7 - we made the rule in last session while working on NW.” (his 2026-10-06 words: “all return should be TWR”)</t>
+        </is>
+      </c>
+      <c r="E375" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-12) — recorded in the decision log as DEC-4644; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B376" s="4" t="inlineStr">
+        <is>
+          <t>Home · Performance · Holding detail · DEC-4645</t>
+        </is>
+      </c>
+      <c r="C376" s="4" t="inlineStr">
+        <is>
+          <t>Corrected 2026-10-12: the market figure uses SPY and AGG adjusted closes, which include their dividends and interest. His Home line stays word for word. The false "price only" statements carry a dated correction; the Holding page note reads "both include dividends and interest"; the gap line no longer says "price change only".</t>
+        </is>
+      </c>
+      <c r="D376" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-12: “Why did you not do the research that market return include dividend and interest?”</t>
+        </is>
+      </c>
+      <c r="E376" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-12) — recorded in the decision log as DEC-4645; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B377" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · Performance · DEC-4646</t>
+        </is>
+      </c>
+      <c r="C377" s="4" t="inlineStr">
+        <is>
+          <t>An option's shares per contract: 10 for a mini option as the broker marks it, else 100, stored with the option; an option typed by hand has a "Shares per contract" box, 100 unless changed.</t>
+        </is>
+      </c>
+      <c r="D377" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-12: “8 - tell me more.” then “3,4, 8-approved.”</t>
+        </is>
+      </c>
+      <c r="E377" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-12) — recorded in the decision log as DEC-4646; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E377"/>
+  <dimension ref="A1:E378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13068,6 +13068,33 @@
       <c r="E377" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-12) — recorded in the decision log as DEC-4646; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B378" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Plan · DEC-4913</t>
+        </is>
+      </c>
+      <c r="C378" s="4" t="inlineStr">
+        <is>
+          <t>Two properties: B marked the home with a rent entry naming B, A with no use stated. B is a rental and A a second home — the property entered first is made the home only when no use is stated on any property. Rent still counts as B's income. Retirement money counts both at 100%: A $400,000 + B $300,000 = $700,000 (was $300,000).</t>
+        </is>
+      </c>
+      <c r="D378" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-13: “approved.” (after the two-property example was explained)</t>
+        </is>
+      </c>
+      <c r="E378" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-13) — recorded in the decision log as DEC-4913; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -19,7 +19,7 @@
     <sheet name="Changelog" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Changelog'!$A$1:$E$308</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Changelog'!$A$1:$E$380</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E378"/>
+  <dimension ref="A1:E380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
     </row>
-    <row r="312">
+    <row r="312" ht="45" customHeight="1">
       <c r="A312" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -11316,7 +11316,7 @@
         </is>
       </c>
     </row>
-    <row r="313">
+    <row r="313" ht="60" customHeight="1">
       <c r="A313" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -11343,7 +11343,7 @@
         </is>
       </c>
     </row>
-    <row r="314">
+    <row r="314" ht="60" customHeight="1">
       <c r="A314" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -11370,7 +11370,7 @@
         </is>
       </c>
     </row>
-    <row r="315">
+    <row r="315" ht="60" customHeight="1">
       <c r="A315" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -11397,7 +11397,7 @@
         </is>
       </c>
     </row>
-    <row r="316">
+    <row r="316" ht="60" customHeight="1">
       <c r="A316" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -11424,7 +11424,7 @@
         </is>
       </c>
     </row>
-    <row r="317">
+    <row r="317" ht="60" customHeight="1">
       <c r="A317" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -11451,7 +11451,7 @@
         </is>
       </c>
     </row>
-    <row r="318">
+    <row r="318" ht="60" customHeight="1">
       <c r="A318" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -11478,7 +11478,7 @@
         </is>
       </c>
     </row>
-    <row r="319">
+    <row r="319" ht="45" customHeight="1">
       <c r="A319" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -11505,7 +11505,7 @@
         </is>
       </c>
     </row>
-    <row r="320">
+    <row r="320" ht="60" customHeight="1">
       <c r="A320" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -11532,7 +11532,7 @@
         </is>
       </c>
     </row>
-    <row r="321">
+    <row r="321" ht="45" customHeight="1">
       <c r="A321" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -11559,7 +11559,7 @@
         </is>
       </c>
     </row>
-    <row r="322">
+    <row r="322" ht="45" customHeight="1">
       <c r="A322" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -11586,7 +11586,7 @@
         </is>
       </c>
     </row>
-    <row r="323">
+    <row r="323" ht="45" customHeight="1">
       <c r="A323" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -11613,7 +11613,7 @@
         </is>
       </c>
     </row>
-    <row r="324">
+    <row r="324" ht="60" customHeight="1">
       <c r="A324" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -11640,7 +11640,7 @@
         </is>
       </c>
     </row>
-    <row r="325">
+    <row r="325" ht="60" customHeight="1">
       <c r="A325" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -11667,7 +11667,7 @@
         </is>
       </c>
     </row>
-    <row r="326">
+    <row r="326" ht="60" customHeight="1">
       <c r="A326" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -11694,7 +11694,7 @@
         </is>
       </c>
     </row>
-    <row r="327">
+    <row r="327" ht="60" customHeight="1">
       <c r="A327" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
     </row>
-    <row r="328">
+    <row r="328" ht="60" customHeight="1">
       <c r="A328" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -11748,7 +11748,7 @@
         </is>
       </c>
     </row>
-    <row r="329">
+    <row r="329" ht="45" customHeight="1">
       <c r="A329" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
@@ -11775,7 +11775,7 @@
         </is>
       </c>
     </row>
-    <row r="330">
+    <row r="330" ht="45" customHeight="1">
       <c r="A330" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
@@ -11802,7 +11802,7 @@
         </is>
       </c>
     </row>
-    <row r="331">
+    <row r="331" ht="60" customHeight="1">
       <c r="A331" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
@@ -11829,7 +11829,7 @@
         </is>
       </c>
     </row>
-    <row r="332">
+    <row r="332" ht="60" customHeight="1">
       <c r="A332" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
@@ -11856,7 +11856,7 @@
         </is>
       </c>
     </row>
-    <row r="333">
+    <row r="333" ht="60" customHeight="1">
       <c r="A333" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
@@ -11883,7 +11883,7 @@
         </is>
       </c>
     </row>
-    <row r="334">
+    <row r="334" ht="60" customHeight="1">
       <c r="A334" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
@@ -11910,7 +11910,7 @@
         </is>
       </c>
     </row>
-    <row r="335">
+    <row r="335" ht="60" customHeight="1">
       <c r="A335" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
@@ -11937,7 +11937,7 @@
         </is>
       </c>
     </row>
-    <row r="336">
+    <row r="336" ht="45" customHeight="1">
       <c r="A336" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
@@ -11964,7 +11964,7 @@
         </is>
       </c>
     </row>
-    <row r="337">
+    <row r="337" ht="45" customHeight="1">
       <c r="A337" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
@@ -11991,7 +11991,7 @@
         </is>
       </c>
     </row>
-    <row r="338">
+    <row r="338" ht="60" customHeight="1">
       <c r="A338" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
@@ -12018,7 +12018,7 @@
         </is>
       </c>
     </row>
-    <row r="339">
+    <row r="339" ht="60" customHeight="1">
       <c r="A339" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
     </row>
-    <row r="340">
+    <row r="340" ht="60" customHeight="1">
       <c r="A340" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -12072,7 +12072,7 @@
         </is>
       </c>
     </row>
-    <row r="341">
+    <row r="341" ht="60" customHeight="1">
       <c r="A341" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -12099,7 +12099,7 @@
         </is>
       </c>
     </row>
-    <row r="342">
+    <row r="342" ht="60" customHeight="1">
       <c r="A342" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -12126,7 +12126,7 @@
         </is>
       </c>
     </row>
-    <row r="343">
+    <row r="343" ht="60" customHeight="1">
       <c r="A343" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
     </row>
-    <row r="344">
+    <row r="344" ht="60" customHeight="1">
       <c r="A344" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12180,7 +12180,7 @@
         </is>
       </c>
     </row>
-    <row r="345">
+    <row r="345" ht="60" customHeight="1">
       <c r="A345" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12207,7 +12207,7 @@
         </is>
       </c>
     </row>
-    <row r="346">
+    <row r="346" ht="60" customHeight="1">
       <c r="A346" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12234,7 +12234,7 @@
         </is>
       </c>
     </row>
-    <row r="347">
+    <row r="347" ht="60" customHeight="1">
       <c r="A347" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12261,7 +12261,7 @@
         </is>
       </c>
     </row>
-    <row r="348">
+    <row r="348" ht="60" customHeight="1">
       <c r="A348" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12288,7 +12288,7 @@
         </is>
       </c>
     </row>
-    <row r="349">
+    <row r="349" ht="60" customHeight="1">
       <c r="A349" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12315,7 +12315,7 @@
         </is>
       </c>
     </row>
-    <row r="350">
+    <row r="350" ht="60" customHeight="1">
       <c r="A350" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12342,7 +12342,7 @@
         </is>
       </c>
     </row>
-    <row r="351">
+    <row r="351" ht="60" customHeight="1">
       <c r="A351" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12369,7 +12369,7 @@
         </is>
       </c>
     </row>
-    <row r="352">
+    <row r="352" ht="60" customHeight="1">
       <c r="A352" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12396,7 +12396,7 @@
         </is>
       </c>
     </row>
-    <row r="353">
+    <row r="353" ht="60" customHeight="1">
       <c r="A353" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12423,7 +12423,7 @@
         </is>
       </c>
     </row>
-    <row r="354">
+    <row r="354" ht="45" customHeight="1">
       <c r="A354" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12450,7 +12450,7 @@
         </is>
       </c>
     </row>
-    <row r="355">
+    <row r="355" ht="60" customHeight="1">
       <c r="A355" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12477,7 +12477,7 @@
         </is>
       </c>
     </row>
-    <row r="356">
+    <row r="356" ht="60" customHeight="1">
       <c r="A356" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12504,7 +12504,7 @@
         </is>
       </c>
     </row>
-    <row r="357">
+    <row r="357" ht="60" customHeight="1">
       <c r="A357" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12531,7 +12531,7 @@
         </is>
       </c>
     </row>
-    <row r="358">
+    <row r="358" ht="60" customHeight="1">
       <c r="A358" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12558,7 +12558,7 @@
         </is>
       </c>
     </row>
-    <row r="359">
+    <row r="359" ht="60" customHeight="1">
       <c r="A359" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12585,7 +12585,7 @@
         </is>
       </c>
     </row>
-    <row r="360">
+    <row r="360" ht="45" customHeight="1">
       <c r="A360" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12612,7 +12612,7 @@
         </is>
       </c>
     </row>
-    <row r="361">
+    <row r="361" ht="60" customHeight="1">
       <c r="A361" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12639,7 +12639,7 @@
         </is>
       </c>
     </row>
-    <row r="362">
+    <row r="362" ht="60" customHeight="1">
       <c r="A362" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12666,7 +12666,7 @@
         </is>
       </c>
     </row>
-    <row r="363">
+    <row r="363" ht="60" customHeight="1">
       <c r="A363" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12693,7 +12693,7 @@
         </is>
       </c>
     </row>
-    <row r="364">
+    <row r="364" ht="60" customHeight="1">
       <c r="A364" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12720,7 +12720,7 @@
         </is>
       </c>
     </row>
-    <row r="365">
+    <row r="365" ht="60" customHeight="1">
       <c r="A365" s="4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -12747,7 +12747,7 @@
         </is>
       </c>
     </row>
-    <row r="366">
+    <row r="366" ht="60" customHeight="1">
       <c r="A366" s="4" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -12774,7 +12774,7 @@
         </is>
       </c>
     </row>
-    <row r="367">
+    <row r="367" ht="60" customHeight="1">
       <c r="A367" s="4" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -12801,7 +12801,7 @@
         </is>
       </c>
     </row>
-    <row r="368">
+    <row r="368" ht="60" customHeight="1">
       <c r="A368" s="4" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -12828,7 +12828,7 @@
         </is>
       </c>
     </row>
-    <row r="369">
+    <row r="369" ht="60" customHeight="1">
       <c r="A369" s="4" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -12855,7 +12855,7 @@
         </is>
       </c>
     </row>
-    <row r="370">
+    <row r="370" ht="60" customHeight="1">
       <c r="A370" s="4" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -12882,7 +12882,7 @@
         </is>
       </c>
     </row>
-    <row r="371">
+    <row r="371" ht="60" customHeight="1">
       <c r="A371" s="4" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -12909,7 +12909,7 @@
         </is>
       </c>
     </row>
-    <row r="372">
+    <row r="372" ht="60" customHeight="1">
       <c r="A372" s="4" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -12936,7 +12936,7 @@
         </is>
       </c>
     </row>
-    <row r="373">
+    <row r="373" ht="60" customHeight="1">
       <c r="A373" s="4" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -12963,7 +12963,7 @@
         </is>
       </c>
     </row>
-    <row r="374">
+    <row r="374" ht="60" customHeight="1">
       <c r="A374" s="4" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -12990,7 +12990,7 @@
         </is>
       </c>
     </row>
-    <row r="375">
+    <row r="375" ht="60" customHeight="1">
       <c r="A375" s="4" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -13017,7 +13017,7 @@
         </is>
       </c>
     </row>
-    <row r="376">
+    <row r="376" ht="60" customHeight="1">
       <c r="A376" s="4" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -13044,7 +13044,7 @@
         </is>
       </c>
     </row>
-    <row r="377">
+    <row r="377" ht="60" customHeight="1">
       <c r="A377" s="4" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -13071,7 +13071,7 @@
         </is>
       </c>
     </row>
-    <row r="378">
+    <row r="378" ht="60" customHeight="1">
       <c r="A378" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -13098,8 +13098,62 @@
         </is>
       </c>
     </row>
+    <row r="379" ht="60" customHeight="1">
+      <c r="A379" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B379" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · DEC-5068</t>
+        </is>
+      </c>
+      <c r="C379" s="4" t="inlineStr">
+        <is>
+          <t>Where the daily record does not reach back and the beginning is worked back from today, Wealth generated, the walk and Return are shown for the holdings with a price history (a CD by its stated rate); a holding with no price history adds no gain and is left out of Return (never 0%), and below the summary: "Wealth generated and Return do not include Treasury 2031's gains, as it has no price history." $50,000 = VTI $40,000 (+10%) + Treasury 2031 $10,000 → Wealth generated $3,636, Return +10.00% (was —, —, no walk). Replaces part 2 of DEC-3656 (now DEC-3656b, not in use); part 1 (a CD gains by its rate) stands. Words differing from his: "Wealth generated" (screen label), "do" (two things), the holding's name for "treasury", ", as it has no price history" (a verb added; has/have from the plural list).</t>
+        </is>
+      </c>
+      <c r="D379" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-13: “Wealth Generated and Return should be calculated and displayed for every asset with history. Below it display "Wealth Generated and Return does not include treasury gains as no price history available."”</t>
+        </is>
+      </c>
+      <c r="E379" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-13) — recorded in the decision log as DEC-5068; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="380" ht="60" customHeight="1">
+      <c r="A380" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B380" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · DEC-5136</t>
+        </is>
+      </c>
+      <c r="C380" s="4" t="inlineStr">
+        <is>
+          <t>The walk card is always titled "HOW $&lt;beginning&gt; BECAME $&lt;ending&gt; · ALL ACCOUNTS" ("· THIS ACCOUNT" on an account's own page, as Performance v17 frame 2 draws it), day one included: "HOW $354,314 BECAME $354,314 · ALL ACCOUNTS". The day-one title "HOW TODAY'S VALUE STANDS" is retired from both screens and every test. READ THIS FIRST rows on Performance v17 and Ways to add an account v10; phones not redrawn.</t>
+        </is>
+      </c>
+      <c r="D380" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-13: “HOW $38,000 BECAME $52,704 · ALL ACCOUNTS - this is the title. Not - "How xxx stands. ALl Accounts"”</t>
+        </is>
+      </c>
+      <c r="E380" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-13) — recorded in the decision log as DEC-5136; written here the same day</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E308"/>
+  <autoFilter ref="A1:E380"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E380"/>
+  <dimension ref="A1:E381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13149,6 +13149,33 @@
       <c r="E380" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-13) — recorded in the decision log as DEC-5136; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="381" ht="60" customHeight="1">
+      <c r="A381" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B381" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · Home · DEC-5291</t>
+        </is>
+      </c>
+      <c r="C381" s="4" t="inlineStr">
+        <is>
+          <t>Let price history count. A window that starts before the daily record (Home writes today's record on first open) is no longer greyed: it is worked back from each holding's price history, Return = the holdings with a history, and what is left out is named. Example: Vanguard linked today, VTI $40,000 (+10% over a year), Treasury 2031 $10,000 by hand → 1Y +10.00%, Wealth generated $3,636, Return +10.00%, "Wealth generated and Return do not include Treasury 2031's gains, as it has no price history." (was greyed — and "The record begins Oct 13, 2026, so it cannot say what these accounts were worth on Oct 12, 2025."). That sentence stays only where no holding has a history. Some accounts reached, some not: the summary is the cards added up. Day-one line where a window is worked back: "Day one: your value is real and your daily record starts today. Longer windows are worked back from each holding's price history." Replaces DEC-3035i; DEC-0230 still holds for typed values.</t>
+        </is>
+      </c>
+      <c r="D381" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-13: “approved.” (to the recommendation “Let price history count …”)</t>
+        </is>
+      </c>
+      <c r="E381" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-13) — recorded in the decision log as DEC-5291; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E381"/>
+  <dimension ref="A1:E382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13165,7 +13165,7 @@
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>Let price history count. A window that starts before the daily record (Home writes today's record on first open) is no longer greyed: it is worked back from each holding's price history, Return = the holdings with a history, and what is left out is named. Example: Vanguard linked today, VTI $40,000 (+10% over a year), Treasury 2031 $10,000 by hand → 1Y +10.00%, Wealth generated $3,636, Return +10.00%, "Wealth generated and Return do not include Treasury 2031's gains, as it has no price history." (was greyed — and "The record begins Oct 13, 2026, so it cannot say what these accounts were worth on Oct 12, 2025."). That sentence stays only where no holding has a history. Some accounts reached, some not: the summary is the cards added up. Day-one line where a window is worked back: "Day one: your value is real and your daily record starts today. Longer windows are worked back from each holding's price history." Replaces DEC-3035i; DEC-0230 still holds for typed values.</t>
+          <t>Let price history count. A window that starts before the daily record (Home writes today's record on first open) is no longer greyed: it is worked back from each holding's price history, Return = the holdings with a history, and what is left out is named. Example: Vanguard linked today, VTI $40,000 (+10% over a year), Treasury 2031 $10,000 by hand → 1Y +10.00%, Wealth generated $3,636, Return +10.00%, "Wealth generated and Return do not include Treasury 2031's gains, as it has no price history." (was greyed — and "The record begins Oct 13, 2026, so it cannot say what these accounts were worth on Oct 12, 2025."). That sentence stays only where no holding has a history. Some accounts reached, some not: the summary is the cards added up. Day-one line where a window is worked back: "You added your accounts today. Figures for 1M, 1Y and longer come from each holding's past prices." (his words, DEC-5425, 2026-10-14; the wording first proposed here was replaced) Replaces DEC-3035i; DEC-0230 still holds for typed values.</t>
         </is>
       </c>
       <c r="D381" s="4" t="inlineStr">
@@ -13176,6 +13176,33 @@
       <c r="E381" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-13) — recorded in the decision log as DEC-5291; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="382" ht="60" customHeight="1">
+      <c r="A382" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B382" s="4" t="inlineStr">
+        <is>
+          <t>Performance · DEC-5425</t>
+        </is>
+      </c>
+      <c r="C382" s="4" t="inlineStr">
+        <is>
+          <t>The Performance tab's day-one line, shown only where a longer window is worked back from each holding's price history, reads "You added your accounts today. Figures for 1M, 1Y and longer come from each holding's past prices." Before (proposed with DEC-5291 on 2026-10-13): "Day one: your value is real and your daily record starts today. Longer windows are worked back from each holding's price history." His words kept as written, though the window buttons read "1M", "This year", "1Y", "2Y". On a true day one with no holding history v17's line is unchanged. READ THIS FIRST row on Performance v17; phones not redrawn.</t>
+        </is>
+      </c>
+      <c r="D382" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-14: “approved.” (to “You added your accounts today. Figures for 1M, 1Y and longer come from each holding's past prices.”) — the earlier wording rejected because “your value is real” and “daily record” meant nothing to him</t>
+        </is>
+      </c>
+      <c r="E382" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-14) — recorded in the decision log as DEC-5425; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E382"/>
+  <dimension ref="A1:E384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13203,6 +13203,60 @@
       <c r="E382" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-14) — recorded in the decision log as DEC-5425; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="383" ht="60" customHeight="1">
+      <c r="A383" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B383" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-0227</t>
+        </is>
+      </c>
+      <c r="C383" s="4" t="inlineStr">
+        <is>
+          <t>Net worth with nothing entered, on a later visit (no account and no debt yet, past the first day), is now the same screen as the first day: v08 state C, word for word. "Add your accounts ›" appears once (on the hero), the one line "Nothing entered yet. How do you want to add an account?" and the three ways to add appear once under What you own, Personal property shows $0, the emergency fund line shows, and the title carries no date. Before, the later visit repeated "Add your accounts ›" under Cash and Investments (3 in all) and showed "＋ Add an account", which state C does not draw. Held by src/screens/__tests__/nw_no_accounts_one_door.test.tsx, which reads every string of the state C phone from the drawing.</t>
+        </is>
+      </c>
+      <c r="D383" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-09-14, on Net worth v07 (v08 mark 14): “too much duplication” — the repeated door was removed from the first day; a later visit with nothing entered is the same data state and now reads the same.</t>
+        </is>
+      </c>
+      <c r="E383" s="4" t="inlineStr">
+        <is>
+          <t>Founder (Net worth v08, approved 2026-09-14) — recorded in the decision log as DEC-0227; applied here 2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="384" ht="60" customHeight="1">
+      <c r="A384" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B384" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-5758</t>
+        </is>
+      </c>
+      <c r="C384" s="4" t="inlineStr">
+        <is>
+          <t>Eight Net worth functions that nothing in the app called are removed and their numbers retired: MK-NW-F-006 isCashKind (screens use the account's class), MK-NW-F-013 realEstateUseOf (screens use MK-NW-F-107 propertyUses, the same rule), MK-NW-F-015 totalAssets (the total comes from MK-NW-F-039 buildAssetsState), MK-NW-F-017 equitiesTotal, MK-NW-F-018 fixedIncomeTotal, MK-NW-F-019 alternativesTotal, MK-NW-F-020 realEstateTotal (the class split, MK-NW-F-029 assetAllocation) and MK-NW-F-038 earmarkedKinds. All eight are deleted (MK-NW-F-006 was named only in an unused import on the Net worth screen, taken out the same day). No figure on any screen changes.</t>
+        </is>
+      </c>
+      <c r="D384" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-19: “Removing #4,5,6,7-10,11 - approved.” (to the inputs-and-use audit's Net worth list of unused functions, each with its reason)</t>
+        </is>
+      </c>
+      <c r="E384" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-5758; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E384"/>
+  <dimension ref="A1:E389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13257,6 +13257,141 @@
       <c r="E384" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-5758; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B385" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · DEC-5847</t>
+        </is>
+      </c>
+      <c r="C385" s="4" t="inlineStr">
+        <is>
+          <t>The account page's Bonds &amp; CDs bar keeps its yearly rate unchanged (each bond's and CD's own stated rate, weighted by what each is worth, e.g. 4.11%/year) and gains an info dot ⓘ before it, so the rate still ends on the one right edge. The dot opens Yearly pace, the same entry the ⓘ under the Performance tab's category table opens, now reading: "A figure marked /year is a yearly interest rate. For Bonds &amp; CDs it is the interest rate each bond and CD states for a year, averaged by what each one is worth. It is not measured over the dates shown. A figure without /year is the gain for the dates shown." Account-page drawing v01 row 23; Performance v17 READ THIS FIRST row, phones not redrawn. Held by src/screens/__tests__/account_page_itemize_and_bond_dot.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D385" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-19, on the account-page drawing v01: “No do not change the bond/CD rate. Let's add info dot next to "4.11%/year" in the sub-titel bar.”</t>
+        </is>
+      </c>
+      <c r="E385" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-5847; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B386" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · DEC-5848</t>
+        </is>
+      </c>
+      <c r="C386" s="4" t="inlineStr">
+        <is>
+          <t>The note under BY CATEGORY &amp; HOLDING on the account page reads "A holding's return is what its own price did in this window, its dividends included; the income is also on the line beneath it." Before: "…; the income it paid is also on the line beneath it." DEC-4645's rule is unchanged. Account-page drawing v01 row 24 (all three notes); Performance v17 READ THIS FIRST row, phones not redrawn.</t>
+        </is>
+      </c>
+      <c r="D386" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-19, on the account-page drawing v01: “"the income it paid is" - should be "the income is" delete "it paid" as income means it is paid.”</t>
+        </is>
+      </c>
+      <c r="E386" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-5848; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B387" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · DEC-5849</t>
+        </is>
+      </c>
+      <c r="C387" s="4" t="inlineStr">
+        <is>
+          <t>"Itemize into holdings" on the account page shows only on an account that can hold several holdings and was entered as one total: Stocks / Funds or unclassified (brokerage, 401(k), IRA, Roth, HSA). Never on a bond or CD, a single alternative (crypto, gold or commodities, annuity, other), a cash account or property; still never on an account that lists holdings or is linked. Before: any account with money and nothing recorded inside. Replaces DEC-0651's door condition on that one point. Account-page drawing v01: door removed from states B and E (row 25).</t>
+        </is>
+      </c>
+      <c r="D387" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-19: “approved.” — after his question “state B - why "itemize your holdings" when we already know it is Bond?”</t>
+        </is>
+      </c>
+      <c r="E387" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-5849; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B388" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · DEC-5982</t>
+        </is>
+      </c>
+      <c r="C388" s="4" t="inlineStr">
+        <is>
+          <t>The Itemize into holdings door on the account page is the app's amber action box, not green: amber-light background (#FAEEDA) with a 1-point amber edge (#854F0B), the same box as the missing-data banner, title in amber. Before: light green (primaryLight) with a dark-green title. Account-page drawing v01 row 26 (no drawn state shows the door after DEC-5849). Held by src/screens/__tests__/account_page_itemize_and_bond_dot.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D388" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-19: “ITemize your holdings box should be amber per color scheme and not green.”</t>
+        </is>
+      </c>
+      <c r="E388" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-5982; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B389" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Plan · DEC-6005</t>
+        </is>
+      </c>
+      <c r="C389" s="4" t="inlineStr">
+        <is>
+          <t>The account page's card for the typed 12-month return (actual_ttm; bonds, CDs and alternatives) is titled HISTORIC 12-MONTH RETURN, carries the line "Add historic 12-month return on your holdings. For bonds or CDs, enter the yield to maturity if it's different from the coupon rate. The Plan tab compares it with the typical return for this type of account." and reads "Not entered" when nothing was typed. Before: YOUR REPORTED RETURN (12 MO) and "not set — projections use the typical return until you report your own". The Retirement cockpit's editor of the same field uses the same line. Account-page drawing v01 row 27.</t>
+        </is>
+      </c>
+      <c r="D389" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-19: “change the wording keep is simple for users … Something like "Historic 12 Month Return" …”, then “ok. Update the language to reflect what is accurate.”, then “Add your historic 12-month - remove your. Rest approved.”</t>
+        </is>
+      </c>
+      <c r="E389" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-6005; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E389"/>
+  <dimension ref="A1:E396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13392,6 +13392,195 @@
       <c r="E389" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-6005; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B390" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Plan · DEC-6005</t>
+        </is>
+      </c>
+      <c r="C390" s="4" t="inlineStr">
+        <is>
+          <t>The HISTORIC 12-MONTH RETURN card's line gains a closing clause: "Add historic 12-month return on your holdings. For bonds or CDs, enter the yield to maturity if it's different from the coupon rate. The Plan tab compares it with the typical return for this type of account, and can grow your savings at it if you choose that there." Before: it ended "…for this type of account." The Retirement cockpit's editor prints the same line. Account-page drawing v01 row 29. Held by src/screens/__tests__/account_page_itemize_and_bond_dot.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D390" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-19: “approved.” — to adding the clause, because the Retirement cockpit's "Grow my nest egg using" choice has a "Your 12-mo" option that grows the savings at this figure.</t>
+        </is>
+      </c>
+      <c r="E390" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-6005 (amended); written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B391" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · DEC-6074</t>
+        </is>
+      </c>
+      <c r="C391" s="4" t="inlineStr">
+        <is>
+          <t>The IF INTEREST RATES MOVE card on a bond's account page keeps its move at 1 percentage point up and down (MK-NW-F-064 bondRateSensitivity, figure MK-NW-M-028): an estimate of what the bond would sell for if market rates moved 1 point today, not its actual value; held to maturity the face value comes back. The decision is cited beside the 1-point move in the code. Account-page drawing v01 row 22. Held by src/domain/bonds/dec_rate_move_one_point.test.ts.</t>
+        </is>
+      </c>
+      <c r="D391" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-19: “rate rise 1% - approved.”</t>
+        </is>
+      </c>
+      <c r="E391" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-6074; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B392" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · DEC-6075</t>
+        </is>
+      </c>
+      <c r="C392" s="4" t="inlineStr">
+        <is>
+          <t>The account page's day-one line: a linked account whose broker sent no past activity reads "You linked this account today. &lt;Broker&gt; sent no past activity, so its figures start today." (the broker's institution name); an account added by hand today reads "You added this account today, so its figures start today." Before: "Day one: your value is real, your return starts measuring from today. We never back-fill a year we didn't see." A linked account with past activity is not day one. The Performance tab's day-one line is unchanged. Account-page drawing v01 state C, rows 14, 30, 31. Held by src/screens/__tests__/account_page_day_one_line.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D392" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-19: “approved”</t>
+        </is>
+      </c>
+      <c r="E392" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-6075; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B393" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · Home · DEC-6076</t>
+        </is>
+      </c>
+      <c r="C393" s="4" t="inlineStr">
+        <is>
+          <t>The sentence where a holding with no price history is left out now says what Return is on: "Return is on the $40,000 with a price history. Treasury 2031 ($10,000) has no price history, so its gains are not included."; several: "… Treasury 2031 and Muni 2029 ($15,000) have no price history, so their gains are not included." First amount MK-PF-M-021 (today's value of the holdings Return counts), bracketed amount MK-PF-M-022 (today's value of those left out). Before: "Wealth generated and Return do not include Treasury 2031's gains, as it has no price history." Replaces DEC-5068's wording only. Account-page drawing v01 row 32; Performance v17 DEC-5068 row noted. Held by MoneyKeel/functions/networth-and-performance/dec6076_left_out_sentence.test.ts.</t>
+        </is>
+      </c>
+      <c r="D393" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-19, on the account-page drawing v01: “State D - for summary box - we need to explain that 10% return is on 40K and not 50K.”, then “approved.”</t>
+        </is>
+      </c>
+      <c r="E393" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-6076; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B394" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · DEC-6077</t>
+        </is>
+      </c>
+      <c r="C394" s="4" t="inlineStr">
+        <is>
+          <t>The HISTORIC 12-MONTH RETURN card is not shown on a bond's or CD's page where the app works out the yield to maturity (face, rate, value and maturity known; or a CD with a stated rate). It stays where it cannot (no rate entered) and on alternatives. Account-page drawing v01: removed from state E (row 34). Held by src/screens/__tests__/account_page_itemize_and_bond_dot.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D394" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-19, on the account-page drawing v01: “state E - do not need historic 12-month return box as you already have YTM.”</t>
+        </is>
+      </c>
+      <c r="E394" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-6077; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B395" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Net worth · DEC-6078</t>
+        </is>
+      </c>
+      <c r="C395" s="4" t="inlineStr">
+        <is>
+          <t>The amber box of missing information hangs its bullets: the dot in its own column, the words on one left edge, so a wrapped line starts under the words. Before: the dot typed at the start of the line. Account-page drawing v01 row 35. Held by src/components/__tests__/data_gaps_banner_bullets.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D395" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-19, on the account-page drawing v01: “And bullet in amber box text on the left should be aligned.”</t>
+        </is>
+      </c>
+      <c r="E395" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-6078; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B396" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Performance · DEC-6079</t>
+        </is>
+      </c>
+      <c r="C396" s="4" t="inlineStr">
+        <is>
+          <t>The account page carries the Performance tab's own five-window control (Since …, 1M, This year, 1Y, 2Y), one shared component (src/components/WindowSelector.tsx). Before: Performance v17 frame 2 drew no control, and the build had a control of its own, styled differently and never greyed. Account-page drawing v01: drawn on every state (rows 18, 33). Held by src/screens/__tests__/account_page_itemize_and_bond_dot.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D396" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-19: “Also check in perf 17 did we have bar to select time period at the top on account page or not? We should have one.”</t>
+        </is>
+      </c>
+      <c r="E396" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-6079; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E396"/>
+  <dimension ref="A1:E397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13581,6 +13581,33 @@
       <c r="E396" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-6079; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" ht="60" customHeight="1">
+      <c r="A397" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B397" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Performance · Holding · Home · DEC-6212</t>
+        </is>
+      </c>
+      <c r="C397" s="4" t="inlineStr">
+        <is>
+          <t>A bond's or CD's return over a window is its price change plus the interest it was paid in the window (interest and coupon records on or after the window's first day naming that holding). KeyBank CD $5,000, $100 interest, price flat: +2.00%; US Treasury $4,000, $85: +2.13%; the Bonds &amp; CDs bar $9,000, $185: +2.06%. Only an individual bond or CD; a bond fund keeps its adjusted closes (DEC-4644). An account's time-weighted return (DEC-4439) is unchanged. The line under a bond's name shows face value, coupon rate and YTM ($5,000 face · 4.00% · YTM 4.00%); Market value and Return keep one meaning each. The account-page drawing's window bar on states A to E is the app's own figure, read off the built screen; a window the app greys is drawn greyed. Four faults found and fixed: the stand-in purchase date, the Since label, the income line by name, and 2.125% written 2.12%.</t>
+        </is>
+      </c>
+      <c r="D397" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-19: “two marco points (1) the return listed in the timebar at the top is not accurate for all screens except StateA. (2) Rule is to return % should include price change, dividend and interest, so showing 0% return for bond is not accurate. …” and “approved.” on the recommendation.</t>
+        </is>
+      </c>
+      <c r="E397" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-6212; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E397"/>
+  <dimension ref="A1:E398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13608,6 +13608,33 @@
       <c r="E397" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-6212; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="398" ht="60" customHeight="1">
+      <c r="A398" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B398" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · DEC-6323</t>
+        </is>
+      </c>
+      <c r="C398" s="4" t="inlineStr">
+        <is>
+          <t>The line under a bond's or CD's name on the account page gains the maturity date as its fourth part: face value · coupon rate · YTM · maturity date, e.g. KeyBank CD "$5,000 face · 4.00% · YTM 4.00% · matures Mar 31, 2027"; Treasury 2031 "$10,000 face · matures Nov 15, 2031". The date in the app's one format; a part not known is left out; a matured one reads "matured Sep 15, 2026" with no YTM. Before: "$5,000 face · 4.00% · YTM 4.00%". Amends DEC-6212's line. Account-page drawing v01 states A, C, D, row 41. Held by src/screens/__tests__/account_page_drawing_states.test.tsx and dec6212_bond_interest.test.ts</t>
+        </is>
+      </c>
+      <c r="D398" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-19: “Line under a bond - new line missing maturity date.”</t>
+        </is>
+      </c>
+      <c r="E398" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-6323; written here the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -19,7 +19,7 @@
     <sheet name="Changelog" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Changelog'!$A$1:$E$380</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Changelog'!$A$1:$E$399</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E398"/>
+  <dimension ref="A1:E399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13260,7 +13260,7 @@
         </is>
       </c>
     </row>
-    <row r="385">
+    <row r="385" ht="60" customHeight="1">
       <c r="A385" s="4" t="inlineStr">
         <is>
           <t>2026-10-19</t>
@@ -13287,7 +13287,7 @@
         </is>
       </c>
     </row>
-    <row r="386">
+    <row r="386" ht="60" customHeight="1">
       <c r="A386" s="4" t="inlineStr">
         <is>
           <t>2026-10-19</t>
@@ -13314,7 +13314,7 @@
         </is>
       </c>
     </row>
-    <row r="387">
+    <row r="387" ht="60" customHeight="1">
       <c r="A387" s="4" t="inlineStr">
         <is>
           <t>2026-10-19</t>
@@ -13341,7 +13341,7 @@
         </is>
       </c>
     </row>
-    <row r="388">
+    <row r="388" ht="60" customHeight="1">
       <c r="A388" s="4" t="inlineStr">
         <is>
           <t>2026-10-19</t>
@@ -13368,7 +13368,7 @@
         </is>
       </c>
     </row>
-    <row r="389">
+    <row r="389" ht="60" customHeight="1">
       <c r="A389" s="4" t="inlineStr">
         <is>
           <t>2026-10-19</t>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
     </row>
-    <row r="390">
+    <row r="390" ht="60" customHeight="1">
       <c r="A390" s="4" t="inlineStr">
         <is>
           <t>2026-10-19</t>
@@ -13422,7 +13422,7 @@
         </is>
       </c>
     </row>
-    <row r="391">
+    <row r="391" ht="60" customHeight="1">
       <c r="A391" s="4" t="inlineStr">
         <is>
           <t>2026-10-19</t>
@@ -13449,7 +13449,7 @@
         </is>
       </c>
     </row>
-    <row r="392">
+    <row r="392" ht="60" customHeight="1">
       <c r="A392" s="4" t="inlineStr">
         <is>
           <t>2026-10-19</t>
@@ -13476,7 +13476,7 @@
         </is>
       </c>
     </row>
-    <row r="393">
+    <row r="393" ht="60" customHeight="1">
       <c r="A393" s="4" t="inlineStr">
         <is>
           <t>2026-10-19</t>
@@ -13503,7 +13503,7 @@
         </is>
       </c>
     </row>
-    <row r="394">
+    <row r="394" ht="60" customHeight="1">
       <c r="A394" s="4" t="inlineStr">
         <is>
           <t>2026-10-19</t>
@@ -13530,7 +13530,7 @@
         </is>
       </c>
     </row>
-    <row r="395">
+    <row r="395" ht="60" customHeight="1">
       <c r="A395" s="4" t="inlineStr">
         <is>
           <t>2026-10-19</t>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
     </row>
-    <row r="396">
+    <row r="396" ht="60" customHeight="1">
       <c r="A396" s="4" t="inlineStr">
         <is>
           <t>2026-10-19</t>
@@ -13638,8 +13638,35 @@
         </is>
       </c>
     </row>
+    <row r="399" ht="60" customHeight="1">
+      <c r="A399" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B399" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Performance · Home · DEC-6412</t>
+        </is>
+      </c>
+      <c r="C399" s="4" t="inlineStr">
+        <is>
+          <t>A window whose first day is before the daily record begins is joined at the record's first day instead of being worked back whole (amends DEC-5291). The days before the record's first day come from each holding's price history (holdings held that day; a bond's or CD's interest added); from that day on the record's own time-weighted return is used, the one Since shows; Return = (1 + the days before) × (1 + the record's part) − 1, and the walk is joined the same way. Account-page drawing state A: 1Y +7.12% → +8.26% (= Since; VOO did not move Sep 29 → Oct 1, 2025), 2Y +9.57% → +10.87% a year. Performance v17 phone 1: 1Y +6.10% → +7.46% (= Since), 2Y +11.10% → +11.81% a year. Unchanged: a record that begins today (state D), a record that reaches back, states B, C, E. The note under the summary for such a window: Your daily record begins Oct 1, 2025, so the days before it are worked back from each holding's price history. The left-out sentence, where those days leave a holding out, is DEC-6076's said of those days: Before Oct 1, 2025, when the daily record begins: Return is on the $X with a price history. … Drawing: account page v01 READ THIS FIRST row 43, bar and side column; Performance v17 READ THIS FIRST row.</t>
+        </is>
+      </c>
+      <c r="D399" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-19: “state A - Oct 1, 2025 → Sep 30, 2026 return is 8.26% and 1Y return is 7.12%. Why different as Oct 1 to sept 30 is 1 Year.” His word on the fix: “approved.”</t>
+        </is>
+      </c>
+      <c r="E399" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-6412; written here the same day</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E380"/>
+  <autoFilter ref="A1:E399"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -19,7 +19,7 @@
     <sheet name="Changelog" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Changelog'!$A$1:$E$399</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Changelog'!$A$1:$E$499</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E399"/>
+  <dimension ref="A1:E499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13665,8 +13665,2708 @@
         </is>
       </c>
     </row>
+    <row r="400" ht="60" customHeight="1">
+      <c r="A400" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B400" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · DEC-6457</t>
+        </is>
+      </c>
+      <c r="C400" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED: the account-page drawing v01 (MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_account-page_v01.html, five states A to E, READ THIS FIRST rows 1 to 43 with the rulings DEC-5847, 5848, 5849, 5982, 6005, 6074 to 6079, 6212, 6323, 6412) is the design of the Account page / Account detail screen (/account-detail, src/screens/AccountPortfolioScreen.tsx) and replaces Performance v17 frame 2 for that screen; v17's other frames stay the Performance tab's. The page is rebuilt to it in every state: the source chip with its date only when stale (no 'Updated Sep 30, 1:00 AM'), the class line under the name, THIS ACCOUNT · &lt;window&gt; with Market value · Wealth generated · Return, the amber box of missing information (state D), the walk's footnote by row 9, the holding's shares and price under its name, the cash row's interest, the income sum, one 16-point right column with › only on a holding, ACTIVITY · &lt;window&gt; inside its card; the value line, the account's own row, WHAT EACH CATEGORY EARNED and the rebuilt line are gone (row 18). Day one is read from the account's own record, so the DEC-6075 lines show once Home has written today's record. Word for word: A 124/124, B 65/65, C 83/83, D 89/89, E 71/71 lines. Held by src/screens/__tests__/account_page_drawing_states.test.tsx; audit moneykeel_audit_mock-match_account-page_2026-10-19_v01.md.</t>
+        </is>
+      </c>
+      <c r="D400" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-19, on the account-page drawing v01 with READ THIS FIRST rows 1 to 43: “approved.”</t>
+        </is>
+      </c>
+      <c r="E400" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-19) — recorded in the decision log as DEC-6457; written here with the build</t>
+        </is>
+      </c>
+    </row>
+    <row r="401" ht="60" customHeight="1">
+      <c r="A401" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B401" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-6590</t>
+        </is>
+      </c>
+      <c r="C401" s="4" t="inlineStr">
+        <is>
+          <t>NOT BUILT IN THIS PHASE: the liquidity field (how quickly an account can be turned into cash, DEC-0299) is left out. No screen, figure or door uses it today. The liquidity tiers (DEC-0313: Liquid / Sellable / Locked / Not spendable) wait with it, because they need that field and have no drawing (the v08 Net worth drawing notes they need their own mock). Nothing on screen changes.</t>
+        </is>
+      </c>
+      <c r="D401" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-20, on whether to build the liquidity field now (option A = leave it out): his reply chose option A.</t>
+        </is>
+      </c>
+      <c r="E401" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-20) — recorded in the decision log as DEC-6590; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="402" ht="60" customHeight="1">
+      <c r="A402" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B402" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Performance · Q10 · DEC-6614</t>
+        </is>
+      </c>
+      <c r="C402" s="4" t="inlineStr">
+        <is>
+          <t>THE CLASS THE BROKER SENDS COMES FIRST. For a linked or imported holding, the class the broker sends decides its class; the name, a maturity date and the app's other automatic rules are used only when the broker sends no usable class. A class the person sets stays first of all. Settles Q10 (DEC-2159) against brief B7 (DEC-0309). Example: a money-market fund the broker flags as cash is Cash (was Stocks / Funds); a T-bill ETF sent as an ETF is Stocks / Funds (was Bonds &amp; CDs). Built in classifyHoldingClass (holding-class.ts), which the sync, the holdings import and every saved holding read; the class standard's §2 rewritten to this order and a Net worth v08 line added 2026-10-21 (worked example: Cash $10,000 becomes $60,000, the emergency fund 1.7 months becomes 10.0 months, what you own $160,000 either way). Test: holding-class.test.ts. Net worth v08's note row of 2026-10-05 on the money-market fund is replaced by the 2026-10-21 line. New input MK-XS-I-070 (the broker's type and cash-equivalent flag, kept on the holding). Still in force where the broker sends no usable class, or the holding was added by hand: a money-market fund added by hand stays Stocks / Funds (DEC-0051 part 1, DEC-0092, DEC-0451, DEC-0472); individual T-bills and CDs stay Bonds &amp; CDs (DEC-0051 part 2); a gold, bitcoin or currency fund with no type sent stays Alternatives (DEC-2162, PRD F1 #19); an account's maturity date still decides the account's class (the 2026-08-04 rule), while for a holding the broker's type now comes first; VMFXX under Cash (F6, 2026-08-14) is now the rule where the broker flags it.</t>
+        </is>
+      </c>
+      <c r="D402" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-20, asked which of his two conflicting rulings comes first, a holding's name or the class the broker sends: “always the class broker sends.”</t>
+        </is>
+      </c>
+      <c r="E402" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-20) — recorded in the decision log as DEC-6614; written here 2026-10-21, a day late</t>
+        </is>
+      </c>
+    </row>
+    <row r="403" ht="60" customHeight="1">
+      <c r="A403" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B403" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Bonds · Q38 part 1 · DEC-6615</t>
+        </is>
+      </c>
+      <c r="C403" s="4" t="inlineStr">
+        <is>
+          <t>A bond's quantity is its face amount ($10,000 of face is a quantity of 10,000), so the face value box is the quantity and nothing new is asked. A linked bond's quote — per unit like a share, or per $100 of face — is read from the broker's total of the account (MK-XS-I-068); a bond that fits neither is marked unclear and named in the amber box. Test: bond_units.test.ts.</t>
+        </is>
+      </c>
+      <c r="D403" s="4" t="inlineStr">
+        <is>
+          <t>Q38 part 1 and Q01, decided without asking him under his ruling DEC-0281 (the nine facts on a bond). One word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E403" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-20 under his ruling DEC-0281, not a decision of his — recorded in the decision log as DEC-6615; written here 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" ht="60" customHeight="1">
+      <c r="A404" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B404" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Q38 part 2 · DEC-6616</t>
+        </is>
+      </c>
+      <c r="C404" s="4" t="inlineStr">
+        <is>
+          <t>A bond's earned interest is its interest and coupon records dated in the window — the interest DEC-6212 already counts in its return. Nothing new is captured.</t>
+        </is>
+      </c>
+      <c r="D404" s="4" t="inlineStr">
+        <is>
+          <t>Q38 part 2, decided without asking him under DEC-0281, read from his DEC-6212. One word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E404" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-20 under his ruling DEC-0281 and DEC-6212, not a decision of his — recorded in the decision log as DEC-6616; written here 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="405" ht="60" customHeight="1">
+      <c r="A405" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B405" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Q38 part 3 · DEC-6617</t>
+        </is>
+      </c>
+      <c r="C405" s="4" t="inlineStr">
+        <is>
+          <t>Account page, BOND FACTS (drawing v01, READ THIS FIRST row 45): a Price row gives a bond's price per $100 of face, worked out as market value ÷ face value × 100 — never a box to fill in. State B: $10,150 ÷ $10,000 × 100 = $101.50; state E: $98.50. Shown only with both a market value and a face value. Test: account_page_drawing_states.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D405" s="4" t="inlineStr">
+        <is>
+          <t>Q38 part 3 and Q01, decided without asking him under DEC-0281, whose nine facts include the current price. One word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E405" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-20 under his ruling DEC-0281, not a decision of his — recorded in the decision log as DEC-6617; written here 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="406" ht="60" customHeight="1">
+      <c r="A406" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B406" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · Account detail · DEC-6618</t>
+        </is>
+      </c>
+      <c r="C406" s="4" t="inlineStr">
+        <is>
+          <t>A holding page counts only the dividends recorded for its ticker in its own account. VTI at Vanguard ($40) and at Fidelity ($10): before, both pages read $50; now $40 and $10, which add to the $50 received. Test: holding_dividends_one_account.test.ts.</t>
+        </is>
+      </c>
+      <c r="D406" s="4" t="inlineStr">
+        <is>
+          <t>A wrong number on screen, fixed without asking him (DEC-3523, tenet 1: a wrong number ends trust).</t>
+        </is>
+      </c>
+      <c r="E406" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-20 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6618; written here 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="407" ht="60" customHeight="1">
+      <c r="A407" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B407" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Performance · Account detail · DEC-6619</t>
+        </is>
+      </c>
+      <c r="C407" s="4" t="inlineStr">
+        <is>
+          <t>A balance typed with an earlier Value-as-of date is booked on that date: each recorded day from that date to today that still holds the old value gets the new one, and the daily totals move with it. A Treasury on record at $24,650, retyped Oct 20 at $24,900 as of Sep 30: September +$250 and October $0 (before: October +$250), the same on the account page, Performance and Net worth. Never on a day not recorded, a linked account, an account with holdings, a date after today, or past a day holding a different value. Test: typed_value_on_its_date.test.ts.</t>
+        </is>
+      </c>
+      <c r="D407" s="4" t="inlineStr">
+        <is>
+          <t>Closes the last limit on the time-weighted return (a balance typed back-dated). Decided without asking him under DEC-0013 and DEC-0230. One word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E407" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-20 under his ruling DEC-0013 and DEC-0230, not a decision of his — recorded in the decision log as DEC-6619; written here 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="408" ht="60" customHeight="1">
+      <c r="A408" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B408" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Performance · DEC-6620</t>
+        </is>
+      </c>
+      <c r="C408" s="4" t="inlineStr">
+        <is>
+          <t>A new account added with an earlier Value-as-of date is not written into past days: it joins the record on the day it is added, and none of its value counts as earned. A $10,000 savings bond added Oct 20 as of Sep 30 adds $0 to October's return. Test: typed_value_on_its_date.test.ts.</t>
+        </is>
+      </c>
+      <c r="D408" s="4" t="inlineStr">
+        <is>
+          <t>No day is invented (DEC-0230); an account added today starts today (DEC-6075). Decided without asking him.</t>
+        </is>
+      </c>
+      <c r="E408" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-20 under his ruling DEC-0230 and DEC-6075, not a decision of his — recorded in the decision log as DEC-6620; written here 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="409" ht="60" customHeight="1">
+      <c r="A409" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B409" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Performance · DEC-6621</t>
+        </is>
+      </c>
+      <c r="C409" s="4" t="inlineStr">
+        <is>
+          <t>A typed value booked back on its Value-as-of date moves only the daily record; the month records stay as captured, because a month's point is read as its first day. No test of its own yet (owed).</t>
+        </is>
+      </c>
+      <c r="D409" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0230.</t>
+        </is>
+      </c>
+      <c r="E409" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-20 under his ruling DEC-0230, not a decision of his — recorded in the decision log as DEC-6621; written here 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="410" ht="60" customHeight="1">
+      <c r="A410" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B410" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Net worth · Performance · Q15 · DEC-6622</t>
+        </is>
+      </c>
+      <c r="C410" s="4" t="inlineStr">
+        <is>
+          <t>A record the broker sends under a word the app does not know is kept with that word, counted as neither money put in nor taken out, and the balance stays the broker's. A return over a window holding that day shows no percent; the amber box names the broker, the word, the date and the amount, and its door opens the account's ACTIVITY, which shows the word and the amount with no plus or minus. Robinhood, $500, Oct 5, 2026: before, +1.00% earned and a row reading Broker adjustment $0. Drawings: account page v01 rows 49 and 50, Net worth v08, Performance v17. Not built: a sheet to label such a record (no drawing has one). Test: unknown_activity_word.test.ts.</t>
+        </is>
+      </c>
+      <c r="D410" s="4" t="inlineStr">
+        <is>
+          <t>Q15, decided without asking him under DEC-0296, DEC-3523 tenet 3 (unknown is not zero) and DEC-2160. One word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E410" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-20 under his ruling DEC-0296, DEC-3523 and DEC-2160, not a decision of his — recorded in the decision log as DEC-6622; written here 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="411" ht="60" customHeight="1">
+      <c r="A411" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B411" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Performance · DEC-6623</t>
+        </is>
+      </c>
+      <c r="C411" s="4" t="inlineStr">
+        <is>
+          <t>A broker JOURNAL — money moved between the person's own accounts — keeps which way it went. $500 journalled in on Oct 5: before, $500 taken out and +2.02%; now $500 put in, $0 earned, 0.00%. Test: unknown_activity_word.test.ts.</t>
+        </is>
+      </c>
+      <c r="D411" s="4" t="inlineStr">
+        <is>
+          <t>A wrong number on screen, fixed without asking him (DEC-3523, tenet 1).</t>
+        </is>
+      </c>
+      <c r="E411" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-20 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6623; written here 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="412" ht="60" customHeight="1">
+      <c r="A412" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B412" s="4" t="inlineStr">
+        <is>
+          <t>Bonds · Q03 · DEC-6624</t>
+        </is>
+      </c>
+      <c r="C412" s="4" t="inlineStr">
+        <is>
+          <t>Q03 (is a CD under Fixed Income or a class of its own?) is answered by his ruling DEC-0051: a CD or a Treasury bill is Bonds &amp; CDs, whatever its maturity. Nothing changes in the app; the row carries the answer to Q03 so it is not asked again.</t>
+        </is>
+      </c>
+      <c r="D412" s="4" t="inlineStr">
+        <is>
+          <t>Found 2026-10-20 that an existing ruling of his answers the question.</t>
+        </is>
+      </c>
+      <c r="E412" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-20 under his ruling DEC-0051, not a decision of his — recorded in the decision log as DEC-6624; written here 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="413" ht="60" customHeight="1">
+      <c r="A413" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B413" s="4" t="inlineStr">
+        <is>
+          <t>Bonds · Add an account · Account detail · DEC-6625</t>
+        </is>
+      </c>
+      <c r="C413" s="4" t="inlineStr">
+        <is>
+          <t>A bond (not a CD) is entered as paying interest Once a year or Twice a year, nothing chosen until one is tapped; the estimate of interest built up since the last payment, which the yield to maturity adds, steps back 12 or 6 months from maturity. $25,000 face, 4.5%, maturing Sep 30, 2029, on Sep 28, 2026: once a year $1,119; twice a year $556. Not chosen: once a year, as before. Input MK-XS-I-069. Drawings: Bonds v02, Add an account v02, account page v01 row 48. Test: coupons_per_year.test.ts.</t>
+        </is>
+      </c>
+      <c r="D413" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3390: the estimate needs to know how often the bond pays. One word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E413" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-20 under his ruling DEC-3390, not a decision of his — recorded in the decision log as DEC-6625; written here 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="414" ht="60" customHeight="1">
+      <c r="A414" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B414" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-6626</t>
+        </is>
+      </c>
+      <c r="C414" s="4" t="inlineStr">
+        <is>
+          <t>Net worth's add sheet (Cash, then CD) asks the CD's interest rate, optional, then bank or broker, then maturity — Add an account's box, words and order; a CD's edit sheet shows the saved rate. Empty is not entered, never 0%. Net worth v08 READ THIS FIRST line. Test: networth_sheet_cd_rate_and_value_date.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D414" s="4" t="inlineStr">
+        <is>
+          <t>The sheet never asked a CD's rate, so a CD added there had no yield (his DEC-3837: a bank CD's yield is its rate). Decided without asking him.</t>
+        </is>
+      </c>
+      <c r="E414" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-20 under his ruling DEC-3837, not a decision of his — recorded in the decision log as DEC-6626; written here 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="415" ht="60" customHeight="1">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · Q20 · DEC-6627</t>
+        </is>
+      </c>
+      <c r="C415" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail: the gains if sold today, the average price paid and Total paid count the purchases with a price paid on record, and say how many shares they leave out; a price paid left blank is saved as not on record, never $0. 10 shares at $100 and 10 with no price paid, today $120: Total paid $1,000 and the gain +$200 on the 10, with 10 shares named as left out (before: the whole gain refused, and a blank saved as $0 made the top gain +$1,400). Holding detail v02, two lines. Tests: holding_cost_not_on_record.test.tsx, holding_blank_cost_agreement.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D415" s="4" t="inlineStr">
+        <is>
+          <t>Q20, answered without asking him by applying his rule for sales (DEC-4643). One word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E415" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-20 under his ruling DEC-4643, not a decision of his — recorded in the decision log as DEC-6627; written here 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="416" ht="60" customHeight="1">
+      <c r="A416" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B416" s="4" t="inlineStr">
+        <is>
+          <t>Add an account · Alternatives · canon row 22 · DEC-4529</t>
+        </is>
+      </c>
+      <c r="C416" s="4" t="inlineStr">
+        <is>
+          <t>ANNUITIES, ONE WORD. Add an account's chip read Annuity; it now reads its four kinds from the app's one list — Crypto · Gold / commodities · Annuities · Other — as the Alternatives editor does. Canon row 22 is written in the one-term-per-concept table, and a dated correction line is on Add an account v02 (the drawing is not redrawn). Where Annuity names something else (an income source, one account's own name) it stays, as row 22 says.</t>
+        </is>
+      </c>
+      <c r="D416" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-11: “agree - leave the drawing, add line detailing correction. Make sure to have the same level of details so one can understand. ok” — and one word per concept (DEC-0382).</t>
+        </is>
+      </c>
+      <c r="E416" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-11) — recorded in the decision log as DEC-4529; applied here 2026-10-20, written 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="417" ht="60" customHeight="1">
+      <c r="A417" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B417" s="4" t="inlineStr">
+        <is>
+          <t>Alternatives · DEC-4529 · DEC-2334</t>
+        </is>
+      </c>
+      <c r="C417" s="4" t="inlineStr">
+        <is>
+          <t>Correction line on Alternatives v02, phone 1 (not redrawn): its rates (~9%, ~7%, ~3.5%), 7.32% and $4,502 are not the app's, and its Fund III is a kind not offered. The app's figures, Fund III entered as Other: 6.81% = (28,000 × 8% + 25,000 × 5% + 8,500 × 8.2%) ÷ 61,500 = 4,187 ÷ 61,500, and growth $4,187 a year. Kept as private equity (saved earlier): 10.06% and $6,187.</t>
+        </is>
+      </c>
+      <c r="D417" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-11: “agree - leave the drawing, add line detailing correction. …” Private equity is not offered in this phase (DEC-2334).</t>
+        </is>
+      </c>
+      <c r="E417" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-11) — recorded in the decision log as DEC-4529; applied here 2026-10-20, written 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="418" ht="60" customHeight="1">
+      <c r="A418" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B418" s="4" t="inlineStr">
+        <is>
+          <t>Bonds · Alternatives · Itemize · Net worth · DEC-0231</t>
+        </is>
+      </c>
+      <c r="C418" s="4" t="inlineStr">
+        <is>
+          <t>Choice chips drawn and built with semicircle ends are corrected to the app's one choice shape, a 12-point corner — 22 of the app's 68 choice styles: Bonds v02 and Alternatives v02 (phone 3), Itemize v02 (the kind chips), Net worth v08 (By category · By institution, and the add sheet's chips). Dated correction lines; the phones are not redrawn. A second agent is rounding the remaining action buttons app-wide; its rows follow.</t>
+        </is>
+      </c>
+      <c r="D418" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-09-25: “make the buttons same as all radio buttons across all screens — rounded corners not semicircle ends”.</t>
+        </is>
+      </c>
+      <c r="E418" s="4" t="inlineStr">
+        <is>
+          <t>Founder (Changelog 2026-09-25) — recorded in the decision log as DEC-0231; applied here 2026-10-20, written 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="419" ht="60" customHeight="1">
+      <c r="A419" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B419" s="4" t="inlineStr">
+        <is>
+          <t>Add an account · Bonds · Alternatives · Net worth · DEC-2441</t>
+        </is>
+      </c>
+      <c r="C419" s="4" t="inlineStr">
+        <is>
+          <t>Held in offers the app's one list of six, in one order and the same words: Taxable, 401(k), Traditional IRA, Roth IRA, Roth 401(k), HSA — on five forms: Add an account, the Bonds editor, the Alternatives editor, Net worth's add sheet and the question a linked account asks about its wrapper. Before: one choice stood for a 401(k) and an IRA and saved only the tax treatment, so a Vanguard 401(k) typed by hand was named Vanguard 401(k) / IRA and compared with SPY; now it is a 401(k), compared with AOR. Lines on the four drawings. Tests: held_in_and_bond_forms.test.tsx, kept_editors_match.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D419" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-06: “Rest I am good with.” (the one 401(k) / IRA choice, owed and not built) — and 2026-10-07, DEC-2484h: a Roth 401(k) is its own choice.</t>
+        </is>
+      </c>
+      <c r="E419" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-06) — recorded in the decision log as DEC-2441; applied here 2026-10-20, written 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="420" ht="60" customHeight="1">
+      <c r="A420" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B420" s="4" t="inlineStr">
+        <is>
+          <t>Bonds · Add an account · Account detail · Net worth · DEC-0281</t>
+        </is>
+      </c>
+      <c r="C420" s="4" t="inlineStr">
+        <is>
+          <t>A BOND'S VALUE, ONE RULE ON EVERY SCREEN (Bonds, the account page, Net worth): the market value entered, else what was paid, else the face value, else Value not entered, left out of totals. New: a box for what was paid (MK-XS-I-067) on the Bonds editor and Add an account; What you paid in BOND FACTS; a line saying which value is shown. The Bonds editor no longer saves the face value as a market value; the Bonds list no longer counts a bond with no value as $0; each card is headed by the bond's own name, with a line under its value saying which value it is; a bond the average yield leaves out is named, with why. Account page v01 rows 46 and 47 (new state F, a bond valued at its face). Tests: bond_value_agreement.test.tsx, account_page_drawing_states.test.tsx, kept_editors_match.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D420" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-08-26 (his -jj master, MK-NW-M-041/042/045): “nine facts on a bond; value = current, else cost, else face; else ‘need more information’”.</t>
+        </is>
+      </c>
+      <c r="E420" s="4" t="inlineStr">
+        <is>
+          <t>Founder (-jj master, 2026-08-26) — recorded in the decision log as DEC-0281; applied here 2026-10-20, written 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="421" ht="60" customHeight="1">
+      <c r="A421" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B421" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · DEC-0281 · DEC-6212</t>
+        </is>
+      </c>
+      <c r="C421" s="4" t="inlineStr">
+        <is>
+          <t>The holding editor, for a holding classed Bonds &amp; CDs: three optional boxes — face value, interest rate, maturity date — in Add an account's words, saved on the holding and read by the line under the bond on its account page. A linked broker sends none of the three. Empty is not entered; a typed 0% is 0%. Holding detail v02 line.</t>
+        </is>
+      </c>
+      <c r="D421" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-08-26 (his -jj master, MK-NW-M-041/042/045): “nine facts on a bond; value = current, else cost, else face; else ‘need more information’”.</t>
+        </is>
+      </c>
+      <c r="E421" s="4" t="inlineStr">
+        <is>
+          <t>Founder (-jj master, 2026-08-26) — recorded in the decision log as DEC-0281; applied here 2026-10-20, written 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="422" ht="60" customHeight="1">
+      <c r="A422" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B422" s="4" t="inlineStr">
+        <is>
+          <t>Empty-state pattern · DEC-0382</t>
+        </is>
+      </c>
+      <c r="C422" s="4" t="inlineStr">
+        <is>
+          <t>The empty-state pattern drawing's notes (not its phones) use the canon words: expenses for spending (canon row 3), and the debt card for the owe card (canon row 10).</t>
+        </is>
+      </c>
+      <c r="D422" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-09-02: “Always use same words to describe same thing in the app. There is no score for creative writing use different terms to describe same thing.”</t>
+        </is>
+      </c>
+      <c r="E422" s="4" t="inlineStr">
+        <is>
+          <t>Founder (Changelog 2026-09-02) — recorded in the decision log as DEC-0382; applied here 2026-10-20, written 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="423" ht="60" customHeight="1">
+      <c r="A423" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B423" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · DEC-0343</t>
+        </is>
+      </c>
+      <c r="C423" s="4" t="inlineStr">
+        <is>
+          <t>Net worth's section totals and institution totals are the one total function (MK-NW-F-039 buildAssetsState) called over each section's or institution's accounts, not added up on the screen; an account with no value is left out of every total the same way. Test: nw_totals_one_function.test.tsx — sections, categories and institutions each add up to WHAT YOU OWN ($998,000).</t>
+        </is>
+      </c>
+      <c r="D423" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-09-13: “one concept, one function — a concept is computed by exactly one dependent function, called over whatever set it is asked about.”</t>
+        </is>
+      </c>
+      <c r="E423" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-09-13) — recorded in the decision log as DEC-0343; applied here 2026-10-20, written 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="424" ht="60" customHeight="1">
+      <c r="A424" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B424" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Home · Insights · DEC-0345</t>
+        </is>
+      </c>
+      <c r="C424" s="4" t="inlineStr">
+        <is>
+          <t>The Net worth family's inputs are built once (MK-NW-F-145 netWorthInputs, src/hooks/useNetWorthInputs.ts) and read by the seven screens that ask its doors: Net worth, Home, Insights, Other investments, Stress test, Job safety and Income manager. No figure moved (a before-and-after test on every Net worth figure); a guard fails if a screen builds them itself. Tests: networth_family_inputs.test.tsx, guard_one_door_networth_inputs.test.ts.</t>
+        </is>
+      </c>
+      <c r="D424" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-09-13: “inputs assembled once per family — one function builds the person’s state for a family and every orchestrator in that family reads it.”</t>
+        </is>
+      </c>
+      <c r="E424" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-09-13) — recorded in the decision log as DEC-0345; applied here 2026-10-20, written 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="425" ht="60" customHeight="1">
+      <c r="A425" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B425" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · fix sheet · DEC-0644</t>
+        </is>
+      </c>
+      <c r="C425" s="4" t="inlineStr">
+        <is>
+          <t>The fix sheet's gap cards carry the ring Net worth v08 draws (state F): a 1-point line at 5% black, 16-point corners, white. Before: no ring. Test: networth_matches_v08.test.tsx (appearance).</t>
+        </is>
+      </c>
+      <c r="D425" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-01: “Quite Instrument v08 - approved all screens from A to G.”</t>
+        </is>
+      </c>
+      <c r="E425" s="4" t="inlineStr">
+        <is>
+          <t>Founder (Net worth v08, 2026-10-01) — recorded in the decision log as DEC-0644; applied here 2026-10-20, written 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="426" ht="60" customHeight="1">
+      <c r="A426" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B426" s="4" t="inlineStr">
+        <is>
+          <t>Bonds · Alternatives · Q49 · DEC-0264</t>
+        </is>
+      </c>
+      <c r="C426" s="4" t="inlineStr">
+        <is>
+          <t>Two saved roundings removed: a sale in the Bonds editor saved the remaining value and face value cut to cents, and a sale in the Alternatives editor saved the value left cut to cents. Both now save the full figure; it is rounded only on screen. The precision guard's list of roundings still carried (src/__tests__/precision_guard.test.ts, CARRIED) is two shorter.</t>
+        </is>
+      </c>
+      <c r="D426" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-09-09 (Q49): “full precision for calculation; display two decimals unless stated (whole dollars for totals, balances, projections; eight for coin quantities); fix the code in one pass”.</t>
+        </is>
+      </c>
+      <c r="E426" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-09-09, Q49) — recorded in the decision log as DEC-0264; applied here 2026-10-20, written 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="427" ht="60" customHeight="1">
+      <c r="A427" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B427" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · a new value is dated today</t>
+        </is>
+      </c>
+      <c r="C427" s="4" t="inlineStr">
+        <is>
+          <t>Net worth's edit sheet dates a new balance today, as Add an account and the account page's Update value do (the one date writer). Before: it saved the new balance and kept the old date, so the account page printed Value as of the old day beside the new value. A save that does not change the value keeps its date.</t>
+        </is>
+      </c>
+      <c r="D427" s="4" t="inlineStr">
+        <is>
+          <t>A wrong date on screen, found by the Net worth launch check.</t>
+        </is>
+      </c>
+      <c r="E427" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a fix to match the other editors; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="428" ht="60" customHeight="1">
+      <c r="A428" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B428" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Plan · Home · MK-XS-M-002</t>
+        </is>
+      </c>
+      <c r="C428" s="4" t="inlineStr">
+        <is>
+          <t>The odds in front of the retirement sentence print under their own identifier, MK-XS-M-002 (the odds of lasting to the age the plan runs to), on Net worth, the Plan tab and Home. Before: under no identifier, so nothing could check them.</t>
+        </is>
+      </c>
+      <c r="D428" s="4" t="inlineStr">
+        <is>
+          <t>Every figure on screen prints under its identifier (objective 3).</t>
+        </is>
+      </c>
+      <c r="E428" s="4" t="inlineStr">
+        <is>
+          <t>Claude — traceability; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="60" customHeight="1">
+      <c r="A429" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B429" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Plan · MK-NW-M-015</t>
+        </is>
+      </c>
+      <c r="C429" s="4" t="inlineStr">
+        <is>
+          <t>MK-NW-M-015's label now describes what the card prints — retire at &lt;age&gt; with ~$X, lasting past &lt;age&gt; with ~$Y to spare, or running short around age &lt;age&gt; — not the old on track for $X by age Y; the card and the Plan tab print the sentence under it. Records that named the old label were corrected 2026-10-21 (the rulings ledger, DEC-0048's rows, the Net worth validation printout, a comment in the master build), and the master's duplicates list no longer folds MK-NW-M-015 into MK-PL-M-033: the cockpit's straight-line pot and the 1,000-run sentence are two figures.</t>
+        </is>
+      </c>
+      <c r="D429" s="4" t="inlineStr">
+        <is>
+          <t>The row described a number no screen has shown since 2026-08-04.</t>
+        </is>
+      </c>
+      <c r="E429" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a record correction; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" ht="60" customHeight="1">
+      <c r="A430" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B430" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · drawing v01 row 51</t>
+        </is>
+      </c>
+      <c r="C430" s="4" t="inlineStr">
+        <is>
+          <t>Account-page drawing v01, READ THIS FIRST row 51: the page is built to rows 45 to 50 and checked word for word — A 124 of 124, B 67 of 67, C 83 of 83, D 89 of 89, E 75 of 75, F 66 of 66 — each line in the card the drawing puts it in.</t>
+        </is>
+      </c>
+      <c r="D430" s="4" t="inlineStr">
+        <is>
+          <t>A drawing the build can drift from is not a design.</t>
+        </is>
+      </c>
+      <c r="E430" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a check of the build against the drawing; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="60" customHeight="1">
+      <c r="A431" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B431" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Update value sheet v01</t>
+        </is>
+      </c>
+      <c r="C431" s="4" t="inlineStr">
+        <is>
+          <t>NEW DRAWING, not yet put to him: moneykeel_pres_mock_update-value-sheet_v01.html — the sheet that changes the value of an account built by hand, states A to H (a cash account, a bond, an amount cleared, a value 7 months old, keeping the value, the sheet from its box, after saving, a value with no date), drawn from today's code. Held word for word by update_value_sheet_drawing.test.tsx (20 of 20 pass, 2026-10-21). Recorded as drawn; it is not a design he has accepted.</t>
+        </is>
+      </c>
+      <c r="D431" s="4" t="inlineStr">
+        <is>
+          <t>The sheet was built with no drawing behind it; DEC-0470 needs every state of updating a value by hand drawn.</t>
+        </is>
+      </c>
+      <c r="E431" s="4" t="inlineStr">
+        <is>
+          <t>Claude — drawn from the code, awaiting his review; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" ht="60" customHeight="1">
+      <c r="A432" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B432" s="4" t="inlineStr">
+        <is>
+          <t>Inputs · MK-XS-I-067 · MK-XS-I-068 · MK-XS-I-069</t>
+        </is>
+      </c>
+      <c r="C432" s="4" t="inlineStr">
+        <is>
+          <t>Three new inputs: MK-XS-I-067 what was paid for a bond or CD held as its own account (amount_paid); MK-XS-I-068 how a linked bond's price is quoted — per $100 of face, or per unit like a share (price_quote); MK-XS-I-069 how many times a year a bond or CD pays its interest (coupons_per_year). And MK-XS-I-070: the class the broker sends for a holding — its type and its cash-equivalent flag, kept on the saved holding exactly as sent (his ruling of 2026-10-20, DEC-6614).</t>
+        </is>
+      </c>
+      <c r="D432" s="4" t="inlineStr">
+        <is>
+          <t>The inputs behind DEC-0281's value rule and the lead's decisions on Q38 part 1 and on how often a bond pays.</t>
+        </is>
+      </c>
+      <c r="E432" s="4" t="inlineStr">
+        <is>
+          <t>Claude — inputs registered for decisions already recorded; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="433" ht="60" customHeight="1">
+      <c r="A433" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B433" s="4" t="inlineStr">
+        <is>
+          <t>Bonds · Account detail · MK-NW-M-026 · MK-NW-M-058</t>
+        </is>
+      </c>
+      <c r="C433" s="4" t="inlineStr">
+        <is>
+          <t>The yield-to-maturity rows (MK-NW-M-026 on the account page, MK-NW-M-058 on Bonds) now say what the code does: the yield at which the coupons still to come and the face value, discounted, equal the value today plus the interest built up since the last coupon — as entered, else estimated as face × rate ÷ payments a year × days since the last payment ÷ days between payments (once a year when how often it pays was not entered).</t>
+        </is>
+      </c>
+      <c r="D433" s="4" t="inlineStr">
+        <is>
+          <t>The rows described the yield without the solved discounting and the accrued estimate (DEC-3390).</t>
+        </is>
+      </c>
+      <c r="E433" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a record correction; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="434" ht="60" customHeight="1">
+      <c r="A434" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B434" s="4" t="inlineStr">
+        <is>
+          <t>App-wide · buttons · DEC-0231</t>
+        </is>
+      </c>
+      <c r="C434" s="4" t="inlineStr">
+        <is>
+          <t>Every button and choice in the app now has the 12-point corner, none with semicircle ends: 8 button styles in 9 places, and the onboarding Monthly · Yearly choice. 14 drawings carry a dated line saying their top bar's button (or the import's main button) is corrected to 12, not redrawn; Bill calendar v02 and Monthly income v02 gained a READ THIS FIRST box to hold it. Round icon buttons stay circles. Test: decisions_are_held.test.ts (4 DEC-0231 tests).</t>
+        </is>
+      </c>
+      <c r="D434" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-09-25: “make the buttons same as all radio buttons across all screens — rounded corners not semicircle ends”.</t>
+        </is>
+      </c>
+      <c r="E434" s="4" t="inlineStr">
+        <is>
+          <t>Founder (Changelog 2026-09-25) — recorded in the decision log as DEC-0231; applied here 2026-10-21, written the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="435" ht="60" customHeight="1">
+      <c r="A435" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B435" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · figures line · DEC-4529 · Q49</t>
+        </is>
+      </c>
+      <c r="C435" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail v02 dated line: fifteen drawn figures are written by the precision rule and the one date writer, not redrawn — $33,858, $24,500, $134, 0.96%, +38.19% ×2, +22.40%, a gap of 15.79, Mar 14, 2023, Jan 9, 2026, $28,000, 0.5 coins (DEC-6682), Jul 2, 2024, 4.05%. Returns carry a sign (DEC-6683); the gap is two decimals (DEC-6684). Test: nw_editors_figures_match.test.tsx 30 of 30.</t>
+        </is>
+      </c>
+      <c r="D435" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-10-11: “agree - leave the drawing, add line detailing correction.” — and his precision rule Q49 (DEC-0264).</t>
+        </is>
+      </c>
+      <c r="E435" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-11) — recorded in the decision log as DEC-4529; applied here 2026-10-21, written the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="436" ht="60" customHeight="1">
+      <c r="A436" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B436" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · Pays interest · DEC-6685</t>
+        </is>
+      </c>
+      <c r="C436" s="4" t="inlineStr">
+        <is>
+          <t>The holding editor asks a held bond (not a CD) Pays interest: Once a year or Twice a year, nothing chosen until tapped; the line under the bond on its account page reads it. $10,000 face at 4.00%, maturing Mar 15, 2030, on Oct 21, 2026: interest built up $241 once a year, $40 twice a year. Test: held_bond_pays_interest.test.tsx 8 of 8.</t>
+        </is>
+      </c>
+      <c r="D436" s="4" t="inlineStr">
+        <is>
+          <t>The yield to maturity needs how often a bond pays (DEC-3390). Decided without asking him.</t>
+        </is>
+      </c>
+      <c r="E436" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3390, not a decision of his — recorded in the decision log as DEC-6685; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="437" ht="60" customHeight="1">
+      <c r="A437" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B437" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · Shares per contract · DEC-6686</t>
+        </is>
+      </c>
+      <c r="C437" s="4" t="inlineStr">
+        <is>
+          <t>Shares per contract counts only for Type Options and is cleared when the Type changes away: an option changed to a stock, 10 shares at $50, read $50,000, now $500. Save stays off for a figure that is not a real number (309 digits read as infinite). Test: holding_editor_shares_per_contract.test.tsx 6 of 6.</t>
+        </is>
+      </c>
+      <c r="D437" s="4" t="inlineStr">
+        <is>
+          <t>A wrong number on screen, found by the outside re-run of Performance, part 3 (DEC-0274, DEC-4646). Decided without asking him.</t>
+        </is>
+      </c>
+      <c r="E437" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0274 and DEC-4646, not a decision of his — recorded in the decision log as DEC-6686; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="438" ht="60" customHeight="1">
+      <c r="A438" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B438" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · drawing v01 row 53 · Performance v17 · DEC-6674</t>
+        </is>
+      </c>
+      <c r="C438" s="4" t="inlineStr">
+        <is>
+          <t>Interest, a dividend or a coupon sent with no amount is unknown: a window holding its day shows no Return, the line under the summary names the record and its date, ACTIVITY shows a dash. Ally savings $10,000 → $10,040, interest with no amount on Oct 5, 2026: no Return (before: $0 in ACTIVITY, Net worth +0.00%). A broker's real $0 is still $0 (DEC-6675). Tests: reversal_and_missing_amount.test.ts 17 of 17, reversal_and_missing_amount_screens.test.tsx 6 of 6.</t>
+        </is>
+      </c>
+      <c r="D438" s="4" t="inlineStr">
+        <is>
+          <t>Unknown is not zero (DEC-3523 tenet 3, DEC-0296). Decided without asking him.</t>
+        </is>
+      </c>
+      <c r="E438" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523 and DEC-0296, not a decision of his — recorded in the decision log as DEC-6674 and DEC-6675; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="439" ht="60" customHeight="1">
+      <c r="A439" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B439" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · drawing v01 row 54 · DEC-6672</t>
+        </is>
+      </c>
+      <c r="C439" s="4" t="inlineStr">
+        <is>
+          <t>A deposit the broker sends with a minus is a reversal, money out, everywhere on the page; with no deposit left to cancel it shows under Withdrawals (DEC-6673). Robinhood $50,000, deposit minus $500 on Oct 5, 2026, $49,500 today: Return +0.00%, Wealth generated $0, Withdrawals $500, ACTIVITY minus $500 (before: −1.98%, Contributions $500, −$1,000, plus $500).</t>
+        </is>
+      </c>
+      <c r="D439" s="4" t="inlineStr">
+        <is>
+          <t>A wrong number ends trust (DEC-3523 tenet 1); kept the way a journal's direction is (DEC-6623). Decided without asking him.</t>
+        </is>
+      </c>
+      <c r="E439" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523 and DEC-6623, not a decision of his — recorded in the decision log as DEC-6672 and DEC-6673; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="440" ht="60" customHeight="1">
+      <c r="A440" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B440" s="4" t="inlineStr">
+        <is>
+          <t>Performance · v17 line of 2026-10-21 · DEC-6672 · DEC-6674</t>
+        </is>
+      </c>
+      <c r="C440" s="4" t="inlineStr">
+        <is>
+          <t>Performance v17 READ THIS FIRST line, not a drawn state: income with no amount gives no Return across its day; a deposit with a minus counts as money taken out (Robinhood $50,000, minus $500 deposit, $49,500 today: Return +0.00%, Wealth generated $0, where it read −1.98% and −$1,000). Nothing is drawn differently.</t>
+        </is>
+      </c>
+      <c r="D440" s="4" t="inlineStr">
+        <is>
+          <t>DEC-3523 tenets 1 and 3, DEC-0296, DEC-6623. Decided without asking him.</t>
+        </is>
+      </c>
+      <c r="E440" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6672 and DEC-6674; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="441" ht="60" customHeight="1">
+      <c r="A441" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B441" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · Home · DEC-6676</t>
+        </is>
+      </c>
+      <c r="C441" s="4" t="inlineStr">
+        <is>
+          <t>A holding worth $0 today keeps its starting value in every reader (12 of 12). A $1,000 → $0, B $1,000 → $1,200, no daily record: Return −40.00%, Wealth generated −$800 from $2,000 on the account page, Performance and Home; Home's market +6.00% (before: +20.00%, +$200, +2.00%). With it: a broker $0 with no shares history is unknown and named (DEC-6677); one holding is the whole account only if no other had value at the start (DEC-6678); a $0 bond that paid interest returns interest ÷ start − 1 (DEC-6679); a $0 close is a price, a broker $0 with no close is no price (DEC-6680); a measured account that lost everything keeps its recorded beginning (DEC-6681). No drawn figure moved. Test: holding_worth_zero_counts.test.tsx 6 of 6.</t>
+        </is>
+      </c>
+      <c r="D441" s="4" t="inlineStr">
+        <is>
+          <t>His DEC-5068 (return for every asset with history) and tenet 4 (DEC-3523). Decided without asking him.</t>
+        </is>
+      </c>
+      <c r="E441" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-5068, not a decision of his — recorded in the decision log as DEC-6676; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="442" ht="60" customHeight="1">
+      <c r="A442" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B442" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · undated purchase · DEC-6687</t>
+        </is>
+      </c>
+      <c r="C442" s="4" t="inlineStr">
+        <is>
+          <t>IF YOU SOLD TODAY: a purchase with no date on record is in neither part; a line gives its gain; with no dated purchase both rows are hidden. 3.25 mini-option contracts at $2.37, no date, today $4.13: $57.20 on the line (before: long-term +$57). Imported holdings keep a missing date blank (DEC-6691); the date reads not on record (DEC-6692). Test: holding_gains_if_sold_today.test.tsx 17 of 17.</t>
+        </is>
+      </c>
+      <c r="D442" s="4" t="inlineStr">
+        <is>
+          <t>Unknown is not zero (DEC-3523 tenet 3); count what is on record, say what is not (DEC-4643). Decided without asking him.</t>
+        </is>
+      </c>
+      <c r="E442" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523 and DEC-4643, not a decision of his — recorded in the decision log as DEC-6687 and DEC-6691 and DEC-6692; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="443" ht="60" customHeight="1">
+      <c r="A443" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B443" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · tax-advantaged accounts · DEC-6688</t>
+        </is>
+      </c>
+      <c r="C443" s="4" t="inlineStr">
+        <is>
+          <t>Inside a 401(k), Traditional IRA, Roth IRA, Roth 401(k), HSA or 529 the card shows one row, Gain, and a line that gains there are not taxed as capital gains. Phone A in a Roth IRA: Gain +$9,358 (before: long-term +$7,384, short-term +$1,974). Not stated keeps the split.</t>
+        </is>
+      </c>
+      <c r="D443" s="4" t="inlineStr">
+        <is>
+          <t>Tax stated plainly (DEC-3523 tenet 7); IRS Publication 550. Decided without asking him.</t>
+        </is>
+      </c>
+      <c r="E443" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6688; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="444" ht="60" customHeight="1">
+      <c r="A444" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B444" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · index options 60/40 · DEC-6689</t>
+        </is>
+      </c>
+      <c r="C444" s="4" t="inlineStr">
+        <is>
+          <t>An option on a broad-based index (SPX, SPXW, XSP, NDX, NDXP, RUT, MRUT, VIX, DJX, OEX, XEO) is split 60% long-term, 40% short-term whatever the holding period. 2 SPX calls at $50, today $80: +$3,600 long-term, +$2,400 short-term (before: $0 and $6,000). SPY and single-company options keep the holding-period split.</t>
+        </is>
+      </c>
+      <c r="D444" s="4" t="inlineStr">
+        <is>
+          <t>IRS Publication 550 (2025), section 1256, read 2026-10-21 (DEC-0378; DEC-3523 tenet 1). Decided without asking him.</t>
+        </is>
+      </c>
+      <c r="E444" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523 and DEC-0378, not a decision of his — recorded in the decision log as DEC-6689; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="445" ht="60" customHeight="1">
+      <c r="A445" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B445" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · no live price · DEC-6690</t>
+        </is>
+      </c>
+      <c r="C445" s="4" t="inlineStr">
+        <is>
+          <t>With no live price, the large figure is Total paid, counting the same purchases (a stored $0 read as not on record). 0.5 coins at $56,000.00 and 0.25 with no price paid: both $28,000 (before: the large figure refused).</t>
+        </is>
+      </c>
+      <c r="D445" s="4" t="inlineStr">
+        <is>
+          <t>One thing, one number (DEC-3523 tenet 4), under DEC-6627. Decided without asking him.</t>
+        </is>
+      </c>
+      <c r="E445" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-6627, not a decision of his — recorded in the decision log as DEC-6690; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="446" ht="60" customHeight="1">
+      <c r="A446" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B446" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · spoken words · DEC-0264 · Q49</t>
+        </is>
+      </c>
+      <c r="C446" s="4" t="inlineStr">
+        <is>
+          <t>What a screen reader says on Holding detail reads percents to two decimals from the screen's formatter: 38.19, 38.19 and 22.40 percent, ahead by 15.79 points (before: 38, 38.2, 22.4 and 15.8); each purchase in its own unit; a missing date said as not on record. Nothing drawn changes. Test: holding_gains_if_sold_today.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D446" s="4" t="inlineStr">
+        <is>
+          <t>Founder, 2026-09-09 (Q49): “full precision for calculation; display two decimals unless stated …”.</t>
+        </is>
+      </c>
+      <c r="E446" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-09-09, Q49) — recorded in the decision log as DEC-0264; applied here 2026-10-21, written the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="447" ht="60" customHeight="1">
+      <c r="A447" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B447" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Performance · DEC-6673</t>
+        </is>
+      </c>
+      <c r="C447" s="4" t="inlineStr">
+        <is>
+          <t>In the walk a reversed deposit lowers what was put in; where the window holds no deposit for it to cancel, it shows under Withdrawals, never as a minus put in. Robinhood example: Withdrawals $500, Contributions $0 (before: Contributions $500). Test: reversal_and_missing_amount_screens.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D447" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E447" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6673; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="448" ht="60" customHeight="1">
+      <c r="A448" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B448" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Performance · Net worth · DEC-6675</t>
+        </is>
+      </c>
+      <c r="C448" s="4" t="inlineStr">
+        <is>
+          <t>The sync keeps a broker's 0 as 0 and a missing amount as not on record, so the two are never confused. A real $0 interest record is measured: Net worth reads the $40 as money moved, 0.00%. Test: reversal_and_missing_amount_screens.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D448" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E448" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6675; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="449" ht="60" customHeight="1">
+      <c r="A449" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B449" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · DEC-6677</t>
+        </is>
+      </c>
+      <c r="C449" s="4" t="inlineStr">
+        <is>
+          <t>A holding the broker sends at $0 with no history of its shares cannot be worked back: its start is unknown, not $0, and the amber box names it. Test: holding_worth_zero_counts.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D449" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-5068; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E449" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-5068, not a decision of his — recorded in the decision log as DEC-6677; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="450" ht="60" customHeight="1">
+      <c r="A450" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B450" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · DEC-6678</t>
+        </is>
+      </c>
+      <c r="C450" s="4" t="inlineStr">
+        <is>
+          <t>isWholeAccount is true only when no other holding in the account had a value at the window's start, so a holding that fell to $0 is never read as the whole account. Test: holding_worth_zero_counts.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D450" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-5068; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E450" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-5068, not a decision of his — recorded in the decision log as DEC-6678; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="451" ht="60" customHeight="1">
+      <c r="A451" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B451" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · DEC-6679</t>
+        </is>
+      </c>
+      <c r="C451" s="4" t="inlineStr">
+        <is>
+          <t>A bond worth $0 today that paid $50 of interest on a $1,000 start: −95.00% = $50 ÷ $1,000 − 1, its interest counted (it read −100.00%). Test: holding_worth_zero_counts.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D451" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-5068 and DEC-6212; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E451" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-5068 and DEC-6212, not a decision of his — recorded in the decision log as DEC-6679; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="452" ht="60" customHeight="1">
+      <c r="A452" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B452" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · DEC-6680</t>
+        </is>
+      </c>
+      <c r="C452" s="4" t="inlineStr">
+        <is>
+          <t>A close of $0 in the price history is counted as $0. A $0 the broker sends with no close behind it is no price, and the amber box names it. Test: holding_worth_zero_counts.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D452" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-5068 and DEC-0019; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E452" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-5068 and DEC-0019, not a decision of his — recorded in the decision log as DEC-6680; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="453" ht="60" customHeight="1">
+      <c r="A453" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B453" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · DEC-6681</t>
+        </is>
+      </c>
+      <c r="C453" s="4" t="inlineStr">
+        <is>
+          <t>An account measured from the daily record whose value fell to $0 is measured from its recorded beginning, so its loss shows. Test: holding_worth_zero_counts.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D453" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-5068; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E453" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-5068, not a decision of his — recorded in the decision log as DEC-6681; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="454" ht="60" customHeight="1">
+      <c r="A454" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B454" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · DEC-6682</t>
+        </is>
+      </c>
+      <c r="C454" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail writes a coin quantity to eight decimals and drops the zeros at the end that carry no value: 0.50000000 reads 0.5 coins, as the purchase row under it already draws it. Test: nw_editors_figures_match.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D454" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0264; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E454" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0264, not a decision of his — recorded in the decision log as DEC-6682; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="455" ht="60" customHeight="1">
+      <c r="A455" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B455" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · DEC-6683</t>
+        </is>
+      </c>
+      <c r="C455" s="4" t="inlineStr">
+        <is>
+          <t>Each return on Holding detail carries its sign, as every return on Performance v17 does: +38.19% since purchase, +38.19% over the past year, +22.40% for the market. Test: nw_editors_figures_match.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D455" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0264 and DEC-4529; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E455" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0264 and DEC-4529, not a decision of his — recorded in the decision log as DEC-6683; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="456" ht="60" customHeight="1">
+      <c r="A456" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B456" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · DEC-6684</t>
+        </is>
+      </c>
+      <c r="C456" s="4" t="inlineStr">
+        <is>
+          <t>The gap between the holding's return and the market's, 38.19 − 22.40, reads 15.79 points, to two decimals like the two returns, not 15.8. Test: nw_editors_figures_match.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D456" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0264; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E456" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0264, not a decision of his — recorded in the decision log as DEC-6684; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="457" ht="60" customHeight="1">
+      <c r="A457" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B457" s="4" t="inlineStr">
+        <is>
+          <t>Import holdings · Holding detail · DEC-6691</t>
+        </is>
+      </c>
+      <c r="C457" s="4" t="inlineStr">
+        <is>
+          <t>An imported holding with no purchase date, or a day that does not exist, is saved with no date, not the day of the import, so it is not short-term and not bought today. To reverse: give it the import day again (h.date || todayIso()). Test: holding_gains_if_sold_today.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D457" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E457" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6691; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="458" ht="60" customHeight="1">
+      <c r="A458" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B458" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · DEC-6692</t>
+        </is>
+      </c>
+      <c r="C458" s="4" t="inlineStr">
+        <is>
+          <t>In WHAT YOU BOUGHT, a purchase with no date says its date is not on record, where it was blank; the line under the gains says the same. Test: holding_gains_if_sold_today.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D458" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-4643; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E458" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-4643, not a decision of his — recorded in the decision log as DEC-6692; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="459" ht="60" customHeight="1">
+      <c r="A459" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B459" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Net worth · DEC-6759</t>
+        </is>
+      </c>
+      <c r="C459" s="4" t="inlineStr">
+        <is>
+          <t>Schwab valued at $50,000, listing $40,000 of shares and $5,000 of cash: Cash $10,000, and the rows add to $50,000 on the account page and on Net worth (before: a gap over 1% of the total sat under Unclassified and in no row of the account page). An account that lists no holdings keeps its gap under its own class. To reverse: restore the 1% limit in linkedSplit. Test: networth_rerun01_fixes.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D459" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0095; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E459" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0095, not a decision of his — recorded in the decision log as DEC-6759; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="460" ht="60" customHeight="1">
+      <c r="A460" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B460" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · emergency fund · DEC-6760</t>
+        </is>
+      </c>
+      <c r="C460" s="4" t="inlineStr">
+        <is>
+          <t>Checking $18,000, a $2,400 mortgage and a car loan with no payment entered: the card reads 7.5 months and $2,400 a month of debt payments with the car loan named beneath, and a tap opens it (before: the same figures with nothing said, as if complete). The months count only what is known. To reverse: drop the line. Test: networth_rerun01_fixes.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D460" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 3, unknown is not zero) and DEC-3769; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E460" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523 and DEC-3769, not a decision of his — recorded in the decision log as DEC-6760; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="461" ht="60" customHeight="1">
+      <c r="A461" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B461" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · emergency fund · DEC-6761</t>
+        </is>
+      </c>
+      <c r="C461" s="4" t="inlineStr">
+        <is>
+          <t>A typed $0, a lump due in full and a payment entered without a minimum are entered: the months count them and none is named as not entered. Test: networth_rerun01_fixes.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D461" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 3); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E461" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6761; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="462" ht="60" customHeight="1">
+      <c r="A462" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B462" s="4" t="inlineStr">
+        <is>
+          <t>Home · DEC-6762</t>
+        </is>
+      </c>
+      <c r="C462" s="4" t="inlineStr">
+        <is>
+          <t>Home showed Net worth $119,200 with no note when one balance was missing; it now carries the same line the Net worth tab's amber box prints. With every balance entered there is no line. Home has no recorded drawing. Test: networth_rerun01_fixes.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D462" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4, one thing, one number); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E462" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6762; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="463" ht="60" customHeight="1">
+      <c r="A463" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B463" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Net worth · Account detail · DEC-6763</t>
+        </is>
+      </c>
+      <c r="C463" s="4" t="inlineStr">
+        <is>
+          <t>A holding with no class read as Stocks / Funds on the Performance tab; it now reads Unclassified on all three screens, its $1,000 and its $50 nowhere else. Test: networth_rerun01_fixes.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D463" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-2160; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E463" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-2160, not a decision of his — recorded in the decision log as DEC-6763; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" ht="60" customHeight="1">
+      <c r="A464" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B464" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · CD · DEC-6764</t>
+        </is>
+      </c>
+      <c r="C464" s="4" t="inlineStr">
+        <is>
+          <t>The card said the CD was marked as bought from the bank when nobody had marked it. It now says where it was bought is not entered and asks the one question with two buttons; the answer is saved on the CD. To reverse: show the bank wording again. Test: networth_rerun01_fixes.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D464" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3837 and DEC-3523 (tenet 3); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E464" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3837 and DEC-3523, not a decision of his — recorded in the decision log as DEC-6764; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="465" ht="60" customHeight="1">
+      <c r="A465" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B465" s="4" t="inlineStr">
+        <is>
+          <t>Job safety · Net worth · DEC-6765</t>
+        </is>
+      </c>
+      <c r="C465" s="4" t="inlineStr">
+        <is>
+          <t>Checking $18,000: Job safety's savings cover $18,000 and $2,820 is still needed (before: an old savings log, $0 covered and $20,820 needed). Savings and investments are Net worth's cash and Investments lines. Job safety has no recorded drawing. Test: networth_rerun01_fixes.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D465" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4, one thing, one number); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E465" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6765; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="466" ht="60" customHeight="1">
+      <c r="A466" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B466" s="4" t="inlineStr">
+        <is>
+          <t>Home · concentration · DEC-6766</t>
+        </is>
+      </c>
+      <c r="C466" s="4" t="inlineStr">
+        <is>
+          <t>$142,000 of $175,200 invested is 81% (before: $310,000 (160%), counting a rental property and a checking account as invested). An account's invested part leaves its cash out; with one investment account the card can read 100%; nothing invested means no card. Test: networth_rerun01_fixes.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D466" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0457; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E466" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0457, not a decision of his — recorded in the decision log as DEC-6766; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="467" ht="60" customHeight="1">
+      <c r="A467" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B467" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Performance · DEC-6767</t>
+        </is>
+      </c>
+      <c r="C467" s="4" t="inlineStr">
+        <is>
+          <t>With no daily record, a 1M walk on the account page began on the first day money moved (Nov 20, 2024); it now begins on the Performance tab's day. The holding line under Since names the Since chip's day (Feb 1, 2024, where it read Jan 31, 2024). Test: networth_rerun01_fixes.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D467" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-6412 and MK-ST-F-078; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E467" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-6412 and MK-ST-F-078, not a decision of his — recorded in the decision log as DEC-6767; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="468" ht="60" customHeight="1">
+      <c r="A468" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B468" s="4" t="inlineStr">
+        <is>
+          <t>Plan · MK-PL-F-081 · DEC-6768</t>
+        </is>
+      </c>
+      <c r="C468" s="4" t="inlineStr">
+        <is>
+          <t>The gain share is the Holding page's gain over the value it counts: 16.67%, not 58.33%, when a purchase was stored at $0. To reverse: read costBasis in taxableGainShare. Test: paid_read_one_way_agreement.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D468" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-6627 and DEC-3523 (tenets 3 and 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E468" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-6627 and DEC-3523, not a decision of his — recorded in the decision log as DEC-6768; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="469" ht="60" customHeight="1">
+      <c r="A469" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B469" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Account detail · account balance · DEC-6769</t>
+        </is>
+      </c>
+      <c r="C469" s="4" t="inlineStr">
+        <is>
+          <t>The Holding page reads $1,000 where the account balance adds $1,000; a holding with no price and nothing paid on record keeps its earlier value, never $0. To reverse: read costBasis in recomputeBalances. Test: paid_read_one_way_agreement.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D469" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-6627 and DEC-3523 (tenets 3 and 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E469" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-6627 and DEC-3523, not a decision of his — recorded in the decision log as DEC-6769; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="470" ht="60" customHeight="1">
+      <c r="A470" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B470" s="4" t="inlineStr">
+        <is>
+          <t>Sync · cost · DEC-6770</t>
+        </is>
+      </c>
+      <c r="C470" s="4" t="inlineStr">
+        <is>
+          <t>$100.00 a share, not $50.00, when only some purchases carry the cost the person typed. To reverse: spread the typed cost over every share. Test: paid_read_one_way_agreement.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D470" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-6627 and DEC-2161; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E470" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-6627 and DEC-2161, not a decision of his — recorded in the decision log as DEC-6770; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="471" ht="60" customHeight="1">
+      <c r="A471" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B471" s="4" t="inlineStr">
+        <is>
+          <t>Performance · window return · DEC-6771</t>
+        </is>
+      </c>
+      <c r="C471" s="4" t="inlineStr">
+        <is>
+          <t>A purchase inside the window stored at $0 is read as a missing cost: the window's return refuses and the left-out sentence names it, as for any missing cost. Test: paid_read_one_way_agreement.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D471" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-6627 and DEC-3523 (tenet 3); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E471" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-6627 and DEC-3523, not a decision of his — recorded in the decision log as DEC-6771; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="472" ht="60" customHeight="1">
+      <c r="A472" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B472" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · history · DEC-6772</t>
+        </is>
+      </c>
+      <c r="C472" s="4" t="inlineStr">
+        <is>
+          <t>The day written for Net worth's history never puts $0 for a worth that is not known. To reverse: read basis ?? 0 in buildDayFromAccounts. Test: paid_read_one_way_agreement.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D472" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-6627 and DEC-3523 (tenets 3 and 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E472" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-6627 and DEC-3523, not a decision of his — recorded in the decision log as DEC-6772; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="473" ht="60" customHeight="1">
+      <c r="A473" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B473" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · oldest-first sale · DEC-6773</t>
+        </is>
+      </c>
+      <c r="C473" s="4" t="inlineStr">
+        <is>
+          <t>A purchase dated 31 February sorted by its text as a real date; it is now no date and goes last with the undated purchases. Test: paid_read_one_way_agreement.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D473" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 3); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E473" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6773; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="474" ht="60" customHeight="1">
+      <c r="A474" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B474" s="4" t="inlineStr">
+        <is>
+          <t>Sync · Account detail · Performance · DEC-6796</t>
+        </is>
+      </c>
+      <c r="C474" s="4" t="inlineStr">
+        <is>
+          <t>A −$50 dividend reversal and a +$5 fee refund on a $10,000 brokerage: ACTIVITY −$50 and +$5, dividends −$50, Return −0.45% on the account page, Performance and Net worth alike (before: +$50 and −$5, dividends $50, the income +$50). To reverse: restore the three-kind check in ingest.ts. Test: dividend_fee_signs.test.ts.</t>
+        </is>
+      </c>
+      <c r="D474" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 1, a wrong number ends trust) and DEC-6623; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E474" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523 and DEC-6623, not a decision of his — recorded in the decision log as DEC-6796; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="475" ht="60" customHeight="1">
+      <c r="A475" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B475" s="4" t="inlineStr">
+        <is>
+          <t>Sync · one-time re-fetch · DEC-6797</t>
+        </is>
+      </c>
+      <c r="C475" s="4" t="inlineStr">
+        <is>
+          <t>Records saved before 2026-10-21 had no direction and could not tell a real $0 from a missing amount; the sync re-fetches each linked account's full activity once, imports nothing twice, then returns to the weekly overlap. An account that cannot be reached keeps no marker and is tried again. To reverse: drop refetchDue. Test: dividend_fee_signs.test.ts.</t>
+        </is>
+      </c>
+      <c r="D475" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenets 1 and 3); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E475" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6797; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="476" ht="60" customHeight="1">
+      <c r="A476" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B476" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Performance · the walk · DEC-6798</t>
+        </is>
+      </c>
+      <c r="C476" s="4" t="inlineStr">
+        <is>
+          <t>A window whose dividends net to −$50 shows Dividends −$50, so the walk still adds up to the change in value. To reverse: restore Math.max(0, …) on those lines in buildChangeWalk. Test: dividend_fee_signs.test.ts.</t>
+        </is>
+      </c>
+      <c r="D476" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 1); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E476" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6798; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="477" ht="60" customHeight="1">
+      <c r="A477" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B477" s="4" t="inlineStr">
+        <is>
+          <t>Outside tests · Performance part 3 · DEC-6799</t>
+        </is>
+      </c>
+      <c r="C477" s="4" t="inlineStr">
+        <is>
+          <t>The outside brief read BND's −$58.20 dividend as $58.20 earned (Bonds &amp; CDs $183.20). A negative dividend is a reversal, $58.20 that left, so the signed total is $66.80, as the walk gives. The app's number is kept. Test: outside_performance_claude_03.test.ts.</t>
+        </is>
+      </c>
+      <c r="D477" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E477" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6799; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="478" ht="60" customHeight="1">
+      <c r="A478" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B478" s="4" t="inlineStr">
+        <is>
+          <t>Sync · money out · DEC-6800</t>
+        </is>
+      </c>
+      <c r="C478" s="4" t="inlineStr">
+        <is>
+          <t>isMoneyOut reads the stated direction: a fee refunded (+$5) and a journal in are money in, never out. Test: dividend_fee_signs.test.ts.</t>
+        </is>
+      </c>
+      <c r="D478" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 1); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E478" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6800; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="479" ht="60" customHeight="1">
+      <c r="A479" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B479" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · undo · DEC-6801</t>
+        </is>
+      </c>
+      <c r="C479" s="4" t="inlineStr">
+        <is>
+          <t>The cash kept by hand moves −$50 then +$5, and undoing each puts it back, because inverseOf flips the stated direction. Test: dividend_fee_signs.test.ts.</t>
+        </is>
+      </c>
+      <c r="D479" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 1); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E479" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6801; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="480" ht="60" customHeight="1">
+      <c r="A480" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B480" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · trade sheet · DEC-6824</t>
+        </is>
+      </c>
+      <c r="C480" s="4" t="inlineStr">
+        <is>
+          <t>A $1,000 deposit typed on Sep 2 for Sep 5: $1,000 put in, Wealth generated $0, Return +0.00% (before: +100.00%). The trade sheet's transaction and purchase dates stop at today. To reverse: drop the clamp in thePerformance and the pickers' maximumDate. Test: nwfix_performance_rerun_01.test.ts.</t>
+        </is>
+      </c>
+      <c r="D480" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenets 1 and 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E480" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6824; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="481" ht="60" customHeight="1">
+      <c r="A481" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B481" s="4" t="inlineStr">
+        <is>
+          <t>Performance · categories · DEC-6825</t>
+        </is>
+      </c>
+      <c r="C481" s="4" t="inlineStr">
+        <is>
+          <t>An alternative's $83.27 dividend reads Alternatives earned $83.27 (before: under Stocks / Funds). Day one draws the row only where one is held. To reverse: remove the row; the income must then go under no wrong class name. Test: nwfix_performance_rerun_01.test.ts.</t>
+        </is>
+      </c>
+      <c r="D481" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenets 1 and 4) and DEC-2160; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E481" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523 and DEC-2160, not a decision of his — recorded in the decision log as DEC-6825; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="482" ht="60" customHeight="1">
+      <c r="A482" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B482" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · price band · DEC-6826</t>
+        </is>
+      </c>
+      <c r="C482" s="4" t="inlineStr">
+        <is>
+          <t>The band names the latest close's day, whatever order the prices arrived in (lastCloseLabel), where the drawing says live; the app holds closing prices, not live ones. To reverse: restore the old band title. Test: nwfix_performance_rerun_01.test.ts.</t>
+        </is>
+      </c>
+      <c r="D482" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenets 1, 2 and 7); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E482" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6826; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="483" ht="60" customHeight="1">
+      <c r="A483" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B483" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · realized gain · DEC-6827</t>
+        </is>
+      </c>
+      <c r="C483" s="4" t="inlineStr">
+        <is>
+          <t>10 bought at $100, sold at $120 with a $5 fee: $195 (before: $200); no fee recorded: $200. 15 sold with a $6 fee, 10 with a cost on record: the 10 carry $4 of it, $196. Source: IRS Publication 550 and Form 8949. To reverse: drop feeOnCovered in realized.ts. Test: nwfix_performance_rerun_01.test.ts.</t>
+        </is>
+      </c>
+      <c r="D483" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenets 1 and 7); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E483" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6827; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="484" ht="60" customHeight="1">
+      <c r="A484" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B484" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · amber box · DEC-6828</t>
+        </is>
+      </c>
+      <c r="C484" s="4" t="inlineStr">
+        <is>
+          <t>A broker's $0 price with no close behind it: the box says the $0 price Schwab sent (before: what you paid, while the row showed $0). A holding with no price at all keeps the sentence about what was paid. To reverse: restore the one sentence. Test: nwfix_performance_rerun_01.test.ts.</t>
+        </is>
+      </c>
+      <c r="D484" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 2, the sentence says what the row shows); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E484" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6828; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="485" ht="60" customHeight="1">
+      <c r="A485" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B485" s="4" t="inlineStr">
+        <is>
+          <t>Sync / Holding page · trade fee · DEC-6873</t>
+        </is>
+      </c>
+      <c r="C485" s="4" t="inlineStr">
+        <is>
+          <t>The broker's trade fee is kept on record; the realized gain (MK-NW-M-035) takes it off once; a purchase fee counts in what was paid; older trades take the fee at the next sync. A sale with a $5 fee: +$195 all time (before: +$200); a $5 fee to buy: +$190. To reverse: delete the tradeFeeOnRecord line in ingest.ts. Test: trade_fee_at_sync.test.tsx 8 of 8. Drawing to make: the trade sheet's fee box.</t>
+        </is>
+      </c>
+      <c r="D485" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenets 1 and 3); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E485" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6873; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="486" ht="60" customHeight="1">
+      <c r="A486" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B486" s="4" t="inlineStr">
+        <is>
+          <t>Sync · trade fee before or after · DEC-6874</t>
+        </is>
+      </c>
+      <c r="C486" s="4" t="inlineStr">
+        <is>
+          <t>$1,200 of cash for 10 shares at $120 with a $5 fee is before the fee; $1,195 is after it. Anything else is read as after the fee. To reverse: drop the leftOut test in tradeFeeOnRecord. Test: trade_fee_at_sync.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D486" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 1); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E486" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6874; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="487" ht="60" customHeight="1">
+      <c r="A487" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B487" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · purchase fee · DEC-6875</t>
+        </is>
+      </c>
+      <c r="C487" s="4" t="inlineStr">
+        <is>
+          <t>A $5 fee to buy is part of what was paid: +$190 all time, whichever way the broker reports the cash. Only the realized gain reads it. To reverse: remove buyFees in realized.ts. Test: trade_fee_at_sync.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D487" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenets 1 and 7); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E487" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6875; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="488" ht="60" customHeight="1">
+      <c r="A488" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B488" s="4" t="inlineStr">
+        <is>
+          <t>Sync · older trades take the fee · DEC-6876</t>
+        </is>
+      </c>
+      <c r="C488" s="4" t="inlineStr">
+        <is>
+          <t>A sale stored at +$200 with its fee dropped reads +$195 after the next sync (fixStoredFees). To reverse: unwrap fixStoredFees in useStore. Test: trade_fee_at_sync.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D488" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 1); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E488" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6876; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="489" ht="60" customHeight="1">
+      <c r="A489" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B489" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Net worth · holding with no price · DEC-6877</t>
+        </is>
+      </c>
+      <c r="C489" s="4" t="inlineStr">
+        <is>
+          <t>Schwab $50,000, 100 VTI at $400, $5,000 cash and 10 ZZ with no price: ZZ reads $5,000 (the rest of the total), where it read $0; STOCKS / FUNDS $45,000 is the sum of its rows. Net worth v08 draws what you paid; the tenets win and a dated v08 line says so. To reverse: restore that line and show what was paid. Test: networth_rerun01_fixes.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D489" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenets 2 and 3) and DEC-0095; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E489" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523 and DEC-0095, not a decision of his — recorded in the decision log as DEC-6877; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="490" ht="60" customHeight="1">
+      <c r="A490" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B490" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · several holdings with no price · DEC-6878</t>
+        </is>
+      </c>
+      <c r="C490" s="4" t="inlineStr">
+        <is>
+          <t>With more than one unpriced holding, each row says no price today in place of a figure, and one row, Holdings with no price today, carries the rest under their class (Unclassified when they span classes), as Net worth files it. Test: networth_rerun01_fixes.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D490" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenets 2 and 3); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E490" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6878; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="491" ht="60" customHeight="1">
+      <c r="A491" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B491" s="4" t="inlineStr">
+        <is>
+          <t>Home · YOUR INVESTMENTS note · DEC-6879</t>
+        </is>
+      </c>
+      <c r="C491" s="4" t="inlineStr">
+        <is>
+          <t>A brokerage with no balance: the line sits under the Investments figure and under Net worth. A checking account with no balance is not invested money: named under Net worth only. Home has no recorded drawing. Test: networth_rerun01_fixes.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D491" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0457 and DEC-3523; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E491" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0457 and DEC-3523, not a decision of his — recorded in the decision log as DEC-6879; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="492" ht="60" customHeight="1">
+      <c r="A492" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B492" s="4" t="inlineStr">
+        <is>
+          <t>Debt editor · Net worth · blank payment · DEC-6880</t>
+        </is>
+      </c>
+      <c r="C492" s="4" t="inlineStr">
+        <is>
+          <t>A blank minimum is saved as not entered and Net worth names it; a typed 0 is 0; a payment worked out from an end date counts as entered. The debt editor has no recorded drawing. Test: networth_rerun01_fixes.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D492" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 3); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E492" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6880; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="493" ht="60" customHeight="1">
+      <c r="A493" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B493" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · Since with no daily record · DEC-6881</t>
+        </is>
+      </c>
+      <c r="C493" s="4" t="inlineStr">
+        <is>
+          <t>Left as approved: the account page starts at the first day money moved (DEC-6075); Performance v17 phone 3 starts today. The case cannot occur: Home (the landing tab) writes today's daily record on first mount (HomeScreen.tsx, captureDailyNw → buildDayFromAccounts) and the app has no deep links, so once a record exists both read the same date. To reverse: make Performance's Since start at the first day money moved. Test: networth_rerun01_fixes.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D493" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-6075; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E493" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-6075, not a decision of his — recorded in the decision log as DEC-6881; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="494" ht="60" customHeight="1">
+      <c r="A494" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B494" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · class split reads what was paid one way</t>
+        </is>
+      </c>
+      <c r="C494" s="4" t="inlineStr">
+        <is>
+          <t>The class split inside an account weighs each holding by what the one reading (paidOnRecord) says was paid: a $0 cost adds nothing, a contract counts its 100 shares; nothing paid on record and no price weighs nothing. Test: networth_rerun01_fixes.test.tsx, section 12.</t>
+        </is>
+      </c>
+      <c r="D494" s="4" t="inlineStr">
+        <is>
+          <t>Applies DEC-6627 and tenet 4 to the 15th cost reader.</t>
+        </is>
+      </c>
+      <c r="E494" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a reader brought onto the one reading; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="495" ht="60" customHeight="1">
+      <c r="A495" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B495" s="4" t="inlineStr">
+        <is>
+          <t>Performance · v14 gaps test · unanswered CD</t>
+        </is>
+      </c>
+      <c r="C495" s="4" t="inlineStr">
+        <is>
+          <t>performance_mock_v14_gaps.test.tsx now expects an unanswered CD to be asked bank or broker, not called a bank CD (DEC-6764). Test: 8 of 8.</t>
+        </is>
+      </c>
+      <c r="D495" s="4" t="inlineStr">
+        <is>
+          <t>A test expectation brought to the decision already recorded.</t>
+        </is>
+      </c>
+      <c r="E495" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a test brought to a recorded decision; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="496" ht="60" customHeight="1">
+      <c r="A496" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B496" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · amber box · holding with no price · DEC-6926</t>
+        </is>
+      </c>
+      <c r="C496" s="4" t="inlineStr">
+        <is>
+          <t>A broker's $0: the $0 price the broker sent. Linked, no price, money left over: it counts as the rest of the broker's total. Linked, nothing left over: it counts for nothing. Built by hand: what you paid. Net worth v08 draws one sentence (what you paid); the tenets win, and a dated v08 line covers all four. To reverse: restore the drawn sentence and show what was paid on the row. Test: networth_rerun01_fixes.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D496" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenets 2 and 3); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E496" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6926; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="497" ht="60" customHeight="1">
+      <c r="A497" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B497" s="4" t="inlineStr">
+        <is>
+          <t>Cash flow · Account detail · undo of a transfer · DEC-6993</t>
+        </is>
+      </c>
+      <c r="C497" s="4" t="inlineStr">
+        <is>
+          <t>Undoing a $500 transfer swapped the accounts and also flipped the direction, so the two cancelled and the $500 moved a second time. Now a transfer's undo swaps the accounts and keeps the direction; every other kind flips its direction. All 17 kinds, applied then undone, give the starting balances to the cent. Test: undo_round_trip.test.ts.</t>
+        </is>
+      </c>
+      <c r="D497" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 1, a wrong number ends trust); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E497" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-6993; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="498" ht="60" customHeight="1">
+      <c r="A498" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B498" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Account detail · MK-NW-F-027 class split</t>
+        </is>
+      </c>
+      <c r="C498" s="4" t="inlineStr">
+        <is>
+          <t>The class split inside an account (MK-NW-F-027 accountClassBreakdown) values every holding kind as the balance and the Holding page do, one scaling each: a bond quoted per $100 of face was scaled twice and an option's price was not × 100. A $9,900 bond beside a $10,000 fund read Bonds $195.08, now $9,900; 2 contracts at $8 beside 10 shares at $40 read Alternatives $76.92, now $1,600. Test: networth_rerun01_fixes.test.tsx, section 14 (34 of 34).</t>
+        </is>
+      </c>
+      <c r="D498" s="4" t="inlineStr">
+        <is>
+          <t>Found by the RULES check of 2026-10-21; a wrong number fixed under his DEC-0274 (an option is contracts × 100 × price) and DEC-0281, with the lead's DEC-6615 (a bond's quantity is its face amount).</t>
+        </is>
+      </c>
+      <c r="E498" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a fix under existing rulings; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="499" ht="60" customHeight="1">
+      <c r="A499" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B499" s="4" t="inlineStr">
+        <is>
+          <t>Tooling · build check B7</t>
+        </is>
+      </c>
+      <c r="C499" s="4" t="inlineStr">
+        <is>
+          <t>Build check B7 (build-outside-test-cards.py, body_of) now fingerprints each whole function, where it read only the first 400 lines, and stops if a function is not closed; thePerformance (MK-NW-O-008) is read whole.</t>
+        </is>
+      </c>
+      <c r="D499" s="4" t="inlineStr">
+        <is>
+          <t>A guard must prove it looked: a function longer than 400 lines changed without the check seeing it.</t>
+        </is>
+      </c>
+      <c r="E499" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a guard widened to the whole function; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E399"/>
+  <autoFilter ref="A1:E499"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx
@@ -19,7 +19,7 @@
     <sheet name="Changelog" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Changelog'!$A$1:$E$499</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Changelog'!$A$1:$E$622</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E499"/>
+  <dimension ref="A1:E622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>The line reads “Monthly debt payments” and two amounts could go there: the minimum each debt obliges, or the money that actually goes. On a card with a  minimum paid at , it read  and now reads . HIS WORDS: “what actually leaves.” The words say payments, and what a person pays is what they pay. The minimum stays on the door for debt-to-income.</t>
+          <t>The line reads “Monthly debt payments” and two amounts could go there: the minimum each debt obliges, or the money that actually goes. On a card with a $200 minimum paid at $600, it read $200 and now reads $600. HIS WORDS: “what actually leaves.” The words say payments, and what a person pays is what they pay. The minimum stays on the door for debt-to-income.</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
@@ -16365,8 +16365,3329 @@
         </is>
       </c>
     </row>
+    <row r="500">
+      <c r="A500" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B500" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · Price paid (average) · Q34 · DEC-7170</t>
+        </is>
+      </c>
+      <c r="C500" s="4" t="inlineStr">
+        <is>
+          <t>An info dot beside Price paid (average) states the rule: what you paid per share over the purchases with a price paid on record; shares with no price paid on record (or $0) left out, and What you bought says how many; no share count on record, no average. One wording on the card: no price paid on record (purchase rows, the average, Total paid); a missing share count reads Not stated. 10 at $100 and 10 at $0: $100.00, not $50.00. Canon row 24. Holding detail v02, one line. Test: holding_cost_not_on_record.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D500" s="4" t="inlineStr">
+        <is>
+          <t>Master question Q34, answered without asking him: his comment of 2026-08-26 asked for the dot; the words are those of his sale line (DEC-4643); tenets 2 and 4 (DEC-3523). One word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E500" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-4643 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7170; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B501" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · Income · trailing twelve months · Q35 · DEC-7171</t>
+        </is>
+      </c>
+      <c r="C501" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail reads Dividends received (trailing twelve months), where it read (12 mo); the Income line for an account reads paid out over the trailing twelve months, where it read over the last year. The figures do not change. Canon row 23. Holding detail v02 and Income v07, one line each. Tests: holding_cost_not_on_record.test.tsx, kept_editors_match.test.tsx, income_manager_matches_v07.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D501" s="4" t="inlineStr">
+        <is>
+          <t>Master question Q35, answered without asking him, following his comment of 2026-08-26 on the figure. Q36 prints DEC-6618 (dividends of this account only). One word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E501" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 on master question Q35, not a decision of his — recorded in the decision log as DEC-7171; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B502" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Update value sheet · DEC-0470</t>
+        </is>
+      </c>
+      <c r="C502" s="4" t="inlineStr">
+        <is>
+          <t>His question of 2026-07-01, what the screen looks like for a manual update, is answered on its row in the decision log: the Update value sheet drawing v01, eight states A to H, built in AccountPortfolioScreen.tsx and held word for word by update_value_sheet_drawing.test.tsx (20 of 20). Its anchor re-mapped by reading to that sheet.</t>
+        </is>
+      </c>
+      <c r="D502" s="4" t="inlineStr">
+        <is>
+          <t>A question of his left with no answer on the launch answer list.</t>
+        </is>
+      </c>
+      <c r="E502" s="4" t="inlineStr">
+        <is>
+          <t>Claude — the answer to his question DEC-0470, written on its row; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B503" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · return since purchase with an undated purchase · DEC-7216</t>
+        </is>
+      </c>
+      <c r="C503" s="4" t="inlineStr">
+        <is>
+          <t>A holding with one purchase dated and another whose date is not on record shows no return since purchase; the card says a purchase has no date on record, so its return since purchase cannot be measured. Its value, what was paid and the gain stand. 7.25 shares dated Sep 17 at $83.17 and 3.125 undated at $91.43, $97.31 today: no return (before: +13.60%, the undated purchase put on the dated day). To reverse: put an undated purchase on the first dated purchase's day again. Test: returns_and_windows_agree.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D503" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 3, unknown is not zero); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E503" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7216; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B504" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · Holding detail · one rule for a yearly rate · DEC-7217</t>
+        </is>
+      </c>
+      <c r="C504" s="4" t="inlineStr">
+        <is>
+          <t>Every screen makes a window longer than a year yearly by one rule: (1 + the window's total) to the power 365 ÷ its days, less 1. A window of a year or less, counted on the calendar, is never made yearly. 21% over the 731 days of a 2Y window is +9.99% a year on the Performance tab, the account page and a holding's own page; the holding read +10.00% (exactly two years). Over 2Y the account page says the window's own total and the yearly rate, in the Performance tab's sentence. To reverse: set periodReturnParts back to years = 2. Test: returns_and_windows_agree.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D504" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0237 and DEC-3768b; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E504" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0237 and DEC-3768b, not a decision of his — recorded in the decision log as DEC-7217; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B505" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · a value below $0 · DEC-7218</t>
+        </is>
+      </c>
+      <c r="C505" s="4" t="inlineStr">
+        <is>
+          <t>On a day the investments together, or one account, are worth less than $0, there is no Return: the line under the summary names the day, says a return cannot be measured across it, and that the dollar figures are still right. An account worth $1,000.17, then −$83.19: no return (before: −100.00%, the value read as $0). To reverse: remove the two VALUE_BELOW_ZERO checks. Test: returns_and_windows_agree.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D505" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 1, a wrong number ends trust); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E505" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7218; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B506" s="4" t="inlineStr">
+        <is>
+          <t>Performance · outside re-run · a close dated after today · DEC-7219</t>
+        </is>
+      </c>
+      <c r="C506" s="4" t="inlineStr">
+        <is>
+          <t>The outside reviewer asked that a close dated after today be left out of a window's end. The app keeps it: it is the latest real price, the same one the holding's value uses, and the price feed dates it by London's day. The window's first day is still read on the person's own calendar. The reviewer's cases on this are marked REVIEWER WRONG. To reverse: cap a window's end at the person's today. Test: outside_performance_rerun_openai_04.test.ts.</t>
+        </is>
+      </c>
+      <c r="D506" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0189 and DEC-0282; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E506" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0189 and DEC-0282, not a decision of his — recorded in the decision log as DEC-7219; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B507" s="4" t="inlineStr">
+        <is>
+          <t>Look back · words kept · outside re-run · DEC-7220</t>
+        </is>
+      </c>
+      <c r="C507" s="4" t="inlineStr">
+        <is>
+          <t>The outside reviewer asked Look back to say its figures are hypothetical, before taxes and costs, and not what actual money did. Look back keeps the words of his approved drawing, word for word: tenet 6 (his decision is the design) ranks above tenet 7. The reviewer's points #36 to #38 of part 1, MK-PF-F-023 of part 3 and the screen checks MK-PF-M-010, -011 and -012 are marked REVIEWER WRONG. To reverse: add the reviewer's words to Look back, which needs a redrawn drawing first. Test: kept_editors_match.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D507" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 6 over tenet 7) and DEC-1069; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E507" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523 and DEC-1069, not a decision of his — recorded in the decision log as DEC-7220; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B508" s="4" t="inlineStr">
+        <is>
+          <t>Home · Holding detail · a holding's start in the window · DEC-7221</t>
+        </is>
+      </c>
+      <c r="C508" s="4" t="inlineStr">
+        <is>
+          <t>A holding's start is what was held when the window began, from the shares held then, never today's shares worked back through the price move; the market figure weighs each holding by that start. 10 shares held, 10 more bought inside the window, $2,420 now: start $1,000 (before: $2,000). On Home, 50 VTI held and 50 bought inside the 1M window beside $10,000 of BND: market +8.00% (before: +8.80%). To reverse: work the start back from today's shares again. Test: pfb_cross_screen_agreement_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D508" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-1669 and DEC-3035b; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E508" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-1669 and DEC-3035b, not a decision of his — recorded in the decision log as DEC-7221; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B509" s="4" t="inlineStr">
+        <is>
+          <t>Home · YOUR INVESTMENTS · the change's base · Performance v17 READ THIS FIRST (Home) · DEC-7222</t>
+        </is>
+      </c>
+      <c r="C509" s="4" t="inlineStr">
+        <is>
+          <t>Home's investments figure leaves out the cash inside investment accounts (DEC-0457), and its month's change is the Performance tab's 1M figure, which counts the accounts whole (Q-PF-1). Where the two differ, a line under the change names its base: This month's change is on $46,600: your investment accounts with the cash in them. A brokerage of $46,600 with $10,825 of cash: YOUR INVESTMENTS $35,775, up $8,200 (21.35%) this month, and the line. With no cash in the accounts the line does not show. To reverse: delete that line in HomeScreen.tsx. Test: pfb_cross_screen_agreement_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D509" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 2, every number shows how it was made) and DEC-0457; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E509" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523 and DEC-0457, not a decision of his — recorded in the decision log as DEC-7222; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B510" s="4" t="inlineStr">
+        <is>
+          <t>Home · the market over each holding's own dates · DEC-7223</t>
+        </is>
+      </c>
+      <c r="C510" s="4" t="inlineStr">
+        <is>
+          <t>Each holding is compared with its yardstick over the same dates as its own return: from the window's start, or from the day it was bought inside the window. The market figure blends each holding's comparison over its own dates, as his invest-v3 rule of 2026-07-19 says. The outside reviewer asked to refuse when holdings' dates differ; that is marked REVIEWER WRONG. To reverse: refuse the market figure when the purchase dates differ. Test: outside_performance_rerun_openai_03.test.ts.</t>
+        </is>
+      </c>
+      <c r="D510" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 6, his decision is the design); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E510" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7223; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B511" s="4" t="inlineStr">
+        <is>
+          <t>Home · the market when a holding has no yardstick · DEC-7224</t>
+        </is>
+      </c>
+      <c r="C511" s="4" t="inlineStr">
+        <is>
+          <t>If any holding counted in your return has no yardstick, the market figure is not known and is not shown, as when none can be priced. It read +5.00%, the covered holding's yardstick alone, set against a return on all the money. To reverse: leave such holdings out of the blend again. Test: outside_performance_rerun_openai_03.test.ts.</t>
+        </is>
+      </c>
+      <c r="D511" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenets 1, 3 and 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E511" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7224; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B512" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · a sale dated after today · DEC-7225</t>
+        </is>
+      </c>
+      <c r="C512" s="4" t="inlineStr">
+        <is>
+          <t>A sale recorded with a date after today is read on today, as every other record is: its shares have already left the holding, and its gain counts in this year's figure. A sale recorded for 2 Jan 2027 on 30 Dec 2026: $200 this year and $200 all time. To reverse: leave such sales out of realizedFromLedger. Test: outside_performance_rerun_openai_03.test.ts.</t>
+        </is>
+      </c>
+      <c r="D512" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenets 1 and 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E512" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7225; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B513" s="4" t="inlineStr">
+        <is>
+          <t>Insights · the largest holding · DEC-7226</t>
+        </is>
+      </c>
+      <c r="C513" s="4" t="inlineStr">
+        <is>
+          <t>Three rules for the largest-holding card. A holding worth less than $0 means no card (it read 112% of the net total). One ticker held in two accounts is one holding: VTI $30,000 in each of two accounts beside SCHD $50,000 reads VTI $60,000 of $110,000, 55% (it named SCHD at 45%). Of two equal holdings the card names the first listed. To reverse: in topHoldingConcentration. Test: outside_performance_rerun_openai_03.test.ts.</t>
+        </is>
+      </c>
+      <c r="D513" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenets 1 and 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E513" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7226; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B514" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · a kind with no yardstick of its own · DEC-7227</t>
+        </is>
+      </c>
+      <c r="C514" s="4" t="inlineStr">
+        <is>
+          <t>A holding the app can describe but whose kind has no yardstick of its own is compared with the stock market (SPY), as his approved Holding page drawing names it. A holding nothing describes has no yardstick (DEC-2160). To reverse: give such a kind no yardstick. Test: outside_performance_rerun_openai_02.test.ts.</t>
+        </is>
+      </c>
+      <c r="D514" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 6) and DEC-0650; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E514" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523 and DEC-0650, not a decision of his — recorded in the decision log as DEC-7227; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B515" s="4" t="inlineStr">
+        <is>
+          <t>Prices · two closes for one day · DEC-7228</t>
+        </is>
+      </c>
+      <c r="C515" s="4" t="inlineStr">
+        <is>
+          <t>The price feed writes its points in time order, so of two closes for one day the later one is the newer quote. Sep 20 at $91.43 and Sep 20 at $97.31: the price is $97.31. To reverse: in latestClose, take the first of the two. Test: outside_performance_rerun_openai_02.test.ts.</t>
+        </is>
+      </c>
+      <c r="D515" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 1); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E515" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7228; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B516" s="4" t="inlineStr">
+        <is>
+          <t>Home · Holding detail · Look back · which yardstick (Q33) · DEC-7229</t>
+        </is>
+      </c>
+      <c r="C516" s="4" t="inlineStr">
+        <is>
+          <t>Master question Q33 asked which index each class is compared with, and whether the person can change it. As built: a class the person set decides first (a bond → AGG, a stock or fund → SPY); then the class the broker sends (DEC-6614); then the holding's kind (stocks and funds SPY; bonds and annuities AGG; gold GLD; bitcoin BTC; private equity PSP; hedge funds QAI; 401(k), IRA, Roth, HSA and 529 AOR, a 60/40 fund); a kind with none of its own, SPY. Every yardstick includes its dividends and interest (DEC-4645). The person changes it by setting the holding's class; Look back lets them pick SPY, AGG, GLD, BTC or AOR (DEC-1624). No separate setting. One word from him adds one. Test: outside_performance_rerun_openai_02.test.ts.</t>
+        </is>
+      </c>
+      <c r="D516" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-4645, DEC-6614 and DEC-1624; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E516" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-4645 and DEC-6614 and DEC-1624, not a decision of his — recorded in the decision log as DEC-7229; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B517" s="4" t="inlineStr">
+        <is>
+          <t>Performance v17 · READ THIS FIRST row of 2026-10-21 · returns and windows · DEC-7217</t>
+        </is>
+      </c>
+      <c r="C517" s="4" t="inlineStr">
+        <is>
+          <t>A dated line, no drawn figure moves: (1) one rule for a yearly rate, 21% over 731 days is +9.99% a year on every screen (a holding read +10.00%); (2) a holding bought in two pieces counts each purchase from the start of its day, +15.24% for the holding and its category (it read +26.76%); (3) a window's first day is the person's own calendar day, so a 1Y figure no longer reads +21.00% in the morning and +10.00% in the evening; (4) a day the investments are worth less than $0 gives no Return, and the line names the day (it read −100.00%). Test: returns_and_windows_agree.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D517" s="4" t="inlineStr">
+        <is>
+          <t>Found by the outside Performance re-run, parts 1, 2 and 4 and its tax file. (1) and (4) are the lead's decisions; (2) and (3) apply his DEC-4439, DEC-0189 and DEC-0282.</t>
+        </is>
+      </c>
+      <c r="E517" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-4439, DEC-0189, DEC-0282 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7217 and DEC-7218; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B518" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · drawing v01 row 60 · DEC-7217</t>
+        </is>
+      </c>
+      <c r="C518" s="4" t="inlineStr">
+        <is>
+          <t>A dated line, no drawn figure moves: (1) over 2Y the note under the trio gives the window's own total and the yearly rate, in the Performance tab's sentence, and no longer says the return is not a yearly rate; (2) a holding's figure in BY CATEGORY &amp; HOLDING is measured from the close of the day before the window's first day, as the account's own return is (a 1Y row read +10.00% where +21.00% is right); (3) a day the account is worth less than $0 gives no Return, and the note names the day (it read −100.00%). Test: returns_and_windows_agree.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D518" s="4" t="inlineStr">
+        <is>
+          <t>Found by the outside Performance re-run (MK-PF-M-016, MK-PF-M-017). (1) and (3) are the lead's decisions; (2) applies his DEC-0315.</t>
+        </is>
+      </c>
+      <c r="E518" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0315 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7217 and DEC-7218; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B519" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail v02 · READ THIS FIRST row of 2026-10-21 · VS THE STOCK MARKET · DEC-7216</t>
+        </is>
+      </c>
+      <c r="C519" s="4" t="inlineStr">
+        <is>
+          <t>A dated line, no drawn figure moves: (1) the return since purchase of a holding bought in pieces counts each purchase from the start of its day, +15.24% (it read +26.76%); (2) over 2Y a yearly rate over the window's own days ÷ 365, +9.99% (it read +10.00%); (3) the window's first day is the person's own calendar day; (4) a holding with a purchase whose date is not on record shows no return since purchase and says why. Test: returns_and_windows_agree.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D519" s="4" t="inlineStr">
+        <is>
+          <t>Found by the outside Performance re-run (MK-PF-F-040, MK-PF-F-039, MK-PF-F-012). (2) and (4) are the lead's decisions; (1) and (3) apply his DEC-4439, DEC-0189 and DEC-0282.</t>
+        </is>
+      </c>
+      <c r="E519" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-4439, DEC-0189, DEC-0282 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7216 and DEC-7217; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B520" s="4" t="inlineStr">
+        <is>
+          <t>Performance v17 · READ THIS FIRST row of 2026-10-21 · the walk, Home's market, the broker's class · DEC-7221</t>
+        </is>
+      </c>
+      <c r="C520" s="4" t="inlineStr">
+        <is>
+          <t>A dated line; figures can move by a dollar or a few points: (1) every walk prints whole dollars that add up to its Ending — $10,000.50 + $1,000.50 paid in + a $100.50 dividend, worth $11,500.49, reads $10,001, $1,000, $100, $399 = $11,500 and Wealth generated $499 (it read $10,001 + $1,001 + $101 + $399 = $11,502); (2) Home's market figure weighs each holding by what was held when the window began, +8.00% where it read +8.80%, and shows nothing when a holding in your return has no yardstick; (3) a holding's yardstick follows the class the broker sends: a bond inside a 401(k) is set beside AGG (it was AOR). Test: pfb_cross_screen_agreement_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D520" s="4" t="inlineStr">
+        <is>
+          <t>Found by the outside Performance re-run, parts 1 to 3. (1) applies tenet 2 and the walk's own rule; (2) is the lead's decision under DEC-1669 and DEC-3035b; (3) applies his DEC-6614.</t>
+        </is>
+      </c>
+      <c r="E520" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-1669, DEC-3035b and DEC-6614, not a decision of his — recorded in the decision log as DEC-7221 and DEC-7224; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B521" s="4" t="inlineStr">
+        <is>
+          <t>Performance v17 · READ THIS FIRST row of 2026-10-21 · Available cash not entered</t>
+        </is>
+      </c>
+      <c r="C521" s="4" t="inlineStr">
+        <is>
+          <t>The sheet for recording a transaction: an investment account whose cash was never entered shows Available cash not entered, and a buy, a withdrawal or a transfer is no longer refused for want of cash it cannot see (it read $0 and refused). An account with $0 of cash entered still shows $0 and refuses as before. Test: pfb_cross_screen_agreement_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D521" s="4" t="inlineStr">
+        <is>
+          <t>Found by the outside Performance re-run, part 1 (MK-PF-M-020); his DEC-3279e and tenet 3 (unknown is not zero).</t>
+        </is>
+      </c>
+      <c r="E521" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a fix under existing rulings; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B522" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Holding detail · a lot of 0 shares, a window not begun, a day that does not exist</t>
+        </is>
+      </c>
+      <c r="C522" s="4" t="inlineStr">
+        <is>
+          <t>A purchase lot of 0 shares is no purchase: a holding bought in May 2026 beside a 0-share lot dated 2024 is measured from May 19, +17.00% (it read +21.64% over the whole year, MK-PF-F-012). A window that starts after today has no figure (it read +0.00%, MK-PF-F-011). A price asked for 31 February, or a close that is not a number, is no price (it read $87.29, MK-PF-F-034). Tests: outside_performance_rerun_openai_02.test.ts and _03.test.ts.</t>
+        </is>
+      </c>
+      <c r="D522" s="4" t="inlineStr">
+        <is>
+          <t>Found by the outside Performance re-run, parts 2 and 3; tenet 3 (DEC-3523) and DEC-1669.</t>
+        </is>
+      </c>
+      <c r="E522" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a fix under existing rulings; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B523" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · realized gain · a purchase with no price paid keeps its place</t>
+        </is>
+      </c>
+      <c r="C523" s="4" t="inlineStr">
+        <is>
+          <t>Oldest-first matching keeps a purchase with no price paid on record in its place in line: bought 10 with no price, then 10 at $50, sold 10 at $70 — no gain is counted and the sale reads 0 of 10 matched (it matched the $50 purchase and counted $200, MK-PF-F-028). Test: outside_performance_rerun_openai_03.test.ts.</t>
+        </is>
+      </c>
+      <c r="D523" s="4" t="inlineStr">
+        <is>
+          <t>Found by the outside Performance re-run, part 3; his DEC-4643 and tenet 3.</t>
+        </is>
+      </c>
+      <c r="E523" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a fix under existing rulings; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B524" s="4" t="inlineStr">
+        <is>
+          <t>Home · ahead by from one function</t>
+        </is>
+      </c>
+      <c r="C524" s="4" t="inlineStr">
+        <is>
+          <t>Home's "ahead by" comes from marketGap, the same function as each holding's own "You are ahead by": 3.6851% − 2.8349% = 0.85%. It was worked out on the Home screen itself; the figure does not move. Test: pfb_cross_screen_agreement_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D524" s="4" t="inlineStr">
+        <is>
+          <t>Found by the outside Performance re-run, tax and cross-card file; tenet 4 (one thing, one number).</t>
+        </is>
+      </c>
+      <c r="E524" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a fix under existing rulings; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B525" s="4" t="inlineStr">
+        <is>
+          <t>Home · the month's return, spoken and traced</t>
+        </is>
+      </c>
+      <c r="C525" s="4" t="inlineStr">
+        <is>
+          <t>Home's month return (MK-XS-M-004) is printed under its ID and spoken to two decimals: "up 21.35 percent this month" (it said "21.4 percent"); the printed (21.35%) does not change. Test: outside_performance_rerun_openai_01_screens.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D525" s="4" t="inlineStr">
+        <is>
+          <t>Found by the outside Performance re-run, part 1 screens; his precision order (DEC-0264, Q49).</t>
+        </is>
+      </c>
+      <c r="E525" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a fix under existing rulings; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B526" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · a holding worth a known $0</t>
+        </is>
+      </c>
+      <c r="C526" s="4" t="inlineStr">
+        <is>
+          <t>A holding row worth a known $0 reads $0, never an older broker mark: $0 where 10 × $20 read $200 (MK-NW-F-128). Test: outside_performance_rerun_openai_01.test.ts.</t>
+        </is>
+      </c>
+      <c r="D526" s="4" t="inlineStr">
+        <is>
+          <t>Found by the outside Performance re-run, part 1; tenets 3 and 4 (DEC-3523).</t>
+        </is>
+      </c>
+      <c r="E526" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a fix under existing rulings; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B527" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · unit words from the one plural list</t>
+        </is>
+      </c>
+      <c r="C527" s="4" t="inlineStr">
+        <is>
+          <t>A quantity's unit comes from the one list of words and plurals (coin, ounce and unit added): "1 coin", "1 unit", never a final s dropped by hand (MK-PF-F-033). Test: outside_performance_rerun_openai_03.test.ts.</t>
+        </is>
+      </c>
+      <c r="D527" s="4" t="inlineStr">
+        <is>
+          <t>Found by the outside Performance re-run, part 3; his DEC-4082 (one list of words and plurals).</t>
+        </is>
+      </c>
+      <c r="E527" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a fix under existing rulings; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B528" s="4" t="inlineStr">
+        <is>
+          <t>Master · five rows' words match the screens</t>
+        </is>
+      </c>
+      <c r="C528" s="4" t="inlineStr">
+        <is>
+          <t>The master rows of MK-NW-M-013 (the emergency fund, with DEC-0251's fallback in his words), MK-NW-M-035 (named Realized from sales, as the screen and the drawing name it), MK-PF-M-007, MK-PF-M-013 and MK-PF-M-018 now say what the screens do. No figure moves. Test: outside_performance_rerun_openai_01_screens.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D528" s="4" t="inlineStr">
+        <is>
+          <t>Found by the outside Performance re-run, part 1 screens: the rows contradicted the screens (tenet 4).</t>
+        </is>
+      </c>
+      <c r="E528" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a records fix; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B529" s="4" t="inlineStr">
+        <is>
+          <t>Master · MK-PF-M-008 and MK-XS-M-004 out of DRAFT; Q-PF-1 tested</t>
+        </is>
+      </c>
+      <c r="C529" s="4" t="inlineStr">
+        <is>
+          <t>MK-PF-M-008 (market +X%) and MK-XS-M-004 (Home's month return) read RULED 2026-09-30 (his "Q51 -approved.", DEC-0640, with DEC-0595 and DEC-4645), no longer DRAFT. MK-PF-M-008's refusal, period and formula are the code as built: no market figure when no yardstick can be priced or a holding in your return has none; the 1M window; weighed by the shares held when the window began. Q33 is answered (DEC-7229). The one-door ruling Q-PF-1 is TESTED (guard_one_door_performance.test.ts). MK-PF-M-009, retired 2026-09-30, is off the Q-PF-1 question.</t>
+        </is>
+      </c>
+      <c r="D529" s="4" t="inlineStr">
+        <is>
+          <t>Performance audit of 2026-10-21, items 11, 12 and 48: the rows waited on him for things he had already ruled.</t>
+        </is>
+      </c>
+      <c r="E529" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a records fix; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B530" s="4" t="inlineStr">
+        <is>
+          <t>Design record · Update value sheet v01; the What-if door</t>
+        </is>
+      </c>
+      <c r="C530" s="4" t="inlineStr">
+        <is>
+          <t>The design record names the Update value sheet drawing v01 (eight states, A to H, held word for word by update_value_sheet_drawing.test.tsx, 20 of 20) as drawn and built, with no approval recorded; approving it is his. Its line on Look ahead now says the What-if screen's one door is Contribution room, not Performance.</t>
+        </is>
+      </c>
+      <c r="D530" s="4" t="inlineStr">
+        <is>
+          <t>Performance audit of 2026-10-21, items 23 and 45.</t>
+        </is>
+      </c>
+      <c r="E530" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a records fix; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B531" s="4" t="inlineStr">
+        <is>
+          <t>Performance · his question on realized, unrealized, dividends and interest · DEC-0479</t>
+        </is>
+      </c>
+      <c r="C531" s="4" t="inlineStr">
+        <is>
+          <t>His question of 2026-07-01 — whether total return captures realized and unrealized gains, and whether they, dividends and interest are shown separately — is answered on its row: Return counts everything (DEC-1669); the walk gives Dividends, Interest and Change in investment value on their own lines (Performance v17, account page v01); a holding's page gives the gain if sold today, Realized from sales and Dividends received (Holding detail v02). Held by perf_matches_v17.test.tsx, account_page_drawing_states.test.tsx and kept_editors_match.test.tsx. Its anchor re-mapped by reading.</t>
+        </is>
+      </c>
+      <c r="D531" s="4" t="inlineStr">
+        <is>
+          <t>A question of his left with no answer on the launch answer list (Performance audit item 19).</t>
+        </is>
+      </c>
+      <c r="E531" s="4" t="inlineStr">
+        <is>
+          <t>Claude — the answer to his question DEC-0479, written on its row; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B532" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · his question on dividends received · DEC-0483</t>
+        </is>
+      </c>
+      <c r="C532" s="4" t="inlineStr">
+        <is>
+          <t>His question of 2026-07-01 — will a stock with dividends show the dividends received — is answered on its row: yes, Dividends received (trailing twelve months) on the holding's own page (Holding detail v02 phone A, MK-NW-M-034), and the dividends in the window on the Performance tab (v17). Held by kept_editors_match.test.tsx and perf_matches_v17.test.tsx. Its anchor re-mapped by reading.</t>
+        </is>
+      </c>
+      <c r="D532" s="4" t="inlineStr">
+        <is>
+          <t>A question of his left with no answer on the launch answer list (Performance audit item 19).</t>
+        </is>
+      </c>
+      <c r="E532" s="4" t="inlineStr">
+        <is>
+          <t>Claude — the answer to his question DEC-0483, written on its row; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B533" s="4" t="inlineStr">
+        <is>
+          <t>Performance · his question on the level of detail · DEC-0497</t>
+        </is>
+      </c>
+      <c r="C533" s="4" t="inlineStr">
+        <is>
+          <t>His question of 2026-06-30 — the level of detail and how it is shown — is answered on its row: three steps, each an approved drawing — the Performance tab (v17), an account's own page (account page v01, with Look back), a holding's own page (Holding detail v02). Held by perf_matches_v17.test.tsx, account_page_drawing_states.test.tsx and kept_editors_match.test.tsx. Its anchor re-mapped by reading.</t>
+        </is>
+      </c>
+      <c r="D533" s="4" t="inlineStr">
+        <is>
+          <t>A question of his left with no answer on the launch answer list (Performance audit item 19).</t>
+        </is>
+      </c>
+      <c r="E533" s="4" t="inlineStr">
+        <is>
+          <t>Claude — the answer to his question DEC-0497, written on its row; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B534" s="4" t="inlineStr">
+        <is>
+          <t>Performance · his question on the level of detail (v1.0 review) · DEC-0510</t>
+        </is>
+      </c>
+      <c r="C534" s="4" t="inlineStr">
+        <is>
+          <t>His question of 2026-06-30 in the v1.0 review — Invest: what level of detail, and how? — is the same as DEC-0497 and has the same answer, written on its row. Its anchor re-mapped by reading.</t>
+        </is>
+      </c>
+      <c r="D534" s="4" t="inlineStr">
+        <is>
+          <t>A question of his left with no answer on the launch answer list (Performance audit item 19).</t>
+        </is>
+      </c>
+      <c r="E534" s="4" t="inlineStr">
+        <is>
+          <t>Claude — the answer to his question DEC-0510, written on its row; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B535" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · the comparison band names its yardstick · DEC-7297</t>
+        </is>
+      </c>
+      <c r="C535" s="4" t="inlineStr">
+        <is>
+          <t>The band over a holding's comparison names what it is measured against, in his Look back names: the stock market, the bond market (AGG), gold, bitcoin, a balanced fund. The rows keep "The market, same dates". A bond fund at $250 → $290 beside AGG $550 → $616 reads VS THE BOND MARKET · SAME DATES, +16.00% / +12.00%, ahead by 4.00 points (before: VS THE STOCK MARKET over AGG's figure). An Unclassified holding reads VS THE MARKET and a line saying why. To reverse: put the stock market's band back. Test: holding_page_comparison_and_unknowns_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D535" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-1624 and DEC-3523 (tenet 2); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E535" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-1624 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7297; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B536" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · a purchase line's unit · DEC-7298</t>
+        </is>
+      </c>
+      <c r="C536" s="4" t="inlineStr">
+        <is>
+          <t>Each purchase line under WHAT YOU BOUGHT says the holding's own unit, as the Quantity row does. Shares stay 100 sh as drawn; 2 option contracts read 2 contracts @ $5.00 (before: 2 sh @ $5.00); a coin reads 0.5 coins; ounces and units are written in full. To reverse: always write sh. Test: holding_page_comparison_and_unknowns_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D536" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0277 and DEC-3523 (tenet 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E536" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0277 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7298; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B537" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · the dividends line · DEC-7299</t>
+        </is>
+      </c>
+      <c r="C537" s="4" t="inlineStr">
+        <is>
+          <t>The dividends line is drawn only when at least one dividend record in this account names the holding, as its own row says. A holding typed in by hand with no record shows Realized from sales alone (before: Dividends received $0, as if it had paid nothing). A record older than twelve months gives a real $0. To reverse: draw the line at $0 again. Test: holding_page_comparison_and_unknowns_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D537" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 3) and DEC-6618; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E537" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523 and DEC-6618, not a decision of his — recorded in the decision log as DEC-7299; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B538" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · Account detail · a short price history in days · DEC-7300</t>
+        </is>
+      </c>
+      <c r="C538" s="4" t="inlineStr">
+        <is>
+          <t>When a holding's prices begin after the window opens and are younger than a month, the line counts days: three days of prices go back 3 days and the figure covers 3 days (before: 0 months); prices that begin today say they begin today. A month or more keeps the approved words. To reverse: count months only. Test: holding_page_comparison_and_unknowns_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D538" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-4641 and DEC-4082; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E538" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-4641 and DEC-4082, not a decision of his — recorded in the decision log as DEC-7300; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B539" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · the LAST CLOSE day · DEC-7301</t>
+        </is>
+      </c>
+      <c r="C539" s="4" t="inlineStr">
+        <is>
+          <t>The price feed dates each close by London's day, so at 8 pm in California a coin's latest price came dated the next day and the band read LAST CLOSE · OCT 22 on Oct 21. The band now shows the earlier of the close's day and the person's today: OCT 21. A close dated on or before today keeps its own day. To reverse: drop the cap. Test: last_close_day_on_persons_calendar.test.ts.</t>
+        </is>
+      </c>
+      <c r="D539" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0189 and DEC-0282; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E539" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0189 and DEC-0282, not a decision of his — recorded in the decision log as DEC-7301; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B540" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · 2Y returns say /year and each total · DEC-7302</t>
+        </is>
+      </c>
+      <c r="C540" s="4" t="inlineStr">
+        <is>
+          <t>Over a window longer than a year both returns say they are yearly: +9.91%/year, behind by 1.07 points/year. Two lines give each window's own total, in the Performance tab's sentence, each starting with its subject: Your return: +20.83% over the two years, which is +9.91%/year; The market: +23.20%. VTI $240 → $290 over 731 days (before: +9.91% with no word that it was yearly). To reverse: remove the two lines and the /year. Test: holding_page_comparison_and_unknowns_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D540" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0237, DEC-0404 and DEC-0368; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E540" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0237 and DEC-0404 and DEC-0368, not a decision of his — recorded in the decision log as DEC-7302; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B541" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · five percents by ID · DEC-7303</t>
+        </is>
+      </c>
+      <c r="C541" s="4" t="inlineStr">
+        <is>
+          <t>Five percents the Holding page printed with its own formatter now print by ID, each with a worked example a test runs: +28.48% (MK-NW-M-067), 0.80% (068), +16.00% (069), +12.00% (070), ahead by 4.00 points (071). They are in the Net worth family, as the page's other figures are. To reverse: delete the five rows. Test: holding_page_comparison_and_unknowns_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D541" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0402 and DEC-3523 (tenet 2); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E541" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0402 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7303; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B542" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Look back · six percents by ID · DEC-7304</t>
+        </is>
+      </c>
+      <c r="C542" s="4" t="inlineStr">
+        <is>
+          <t>Six percents printed with no ID now print by one, each marked ruled on 2026-10-21 as MK-NW-M-065 and 066 were, each with a worked example: one holding's return on the account page (MK-PF-M-023), one class's return there (024), Look back's two percents (025, 026), the typical yearly return for an alternative's type (MK-NW-M-072), the historic 12-month return a person types (073). To reverse: delete the rows. Test: performance_spoken_and_agree_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D542" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0402 and DEC-3523 (tenet 2); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E542" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0402 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7304; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B543" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · a bond's stated rate · DEC-7305</t>
+        </is>
+      </c>
+      <c r="C543" s="4" t="inlineStr">
+        <is>
+          <t>Where a bond's row shows its stated yearly rate in the Return column, that figure is the bond's coupon rate and prints under its existing ID, MK-NW-M-024, not a new one. To reverse: give it its own ID. Test: performance_spoken_and_agree_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D543" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E543" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7305; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B544" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · record buttons spoken by name · DEC-7306</t>
+        </is>
+      </c>
+      <c r="C544" s="4" t="inlineStr">
+        <is>
+          <t>Each record button is spoken by its record's own name: Record a withdrawal, Record a coupon, Record interest (it said "Record a interest" and "Record a withdraw"). The words on the buttons do not change. The same article rule fixed "an HSA account" and "Pick an expense date". To reverse: speak the type word again. Test: article.test.ts.</t>
+        </is>
+      </c>
+      <c r="D544" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4) and DEC-0287; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E544" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523 and DEC-0287, not a decision of his — recorded in the decision log as DEC-7306; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B545" s="4" t="inlineStr">
+        <is>
+          <t>Performance · the value graph spoken · DEC-7307</t>
+        </is>
+      </c>
+      <c r="C545" s="4" t="inlineStr">
+        <is>
+          <t>VoiceOver reads the graph as: Value of your investments since the first day: $30,000, up to $46,600 on Sep 28, 2026, a return of the printed Return. It names no figure the screen does not print. To reverse: make the graph silent again. Test: performance_spoken_and_agree_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D545" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 2); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E545" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7307; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B546" s="4" t="inlineStr">
+        <is>
+          <t>Performance · hidden balances, spoken as hidden · DEC-7308</t>
+        </is>
+      </c>
+      <c r="C546" s="4" t="inlineStr">
+        <is>
+          <t>With balances hidden, every sentence on the Performance tab that carries a dollar amount shows dots, and VoiceOver says hidden, never the dots or the amount; returns stay. Home already did this. To reverse: let those sentences show their dollars. Test: performance_spoken_and_agree_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D546" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0013 and DEC-3523; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E546" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0013 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7308; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B547" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Performance · Investments and Ending value pinned · DEC-7309</t>
+        </is>
+      </c>
+      <c r="C547" s="4" t="inlineStr">
+        <is>
+          <t>The cross-screen test pins the two figures as: Investments + the cash held inside investment accounts = Ending value. With $2,000 of cash in the brokerage: $50,000 + $2,000 = $52,000; with none: $121,000 = $121,000. Plain equality would contradict DEC-0457 (Investments leave cash out). To reverse: pin plain equality. Test: performance_spoken_and_agree_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D547" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0457 and DEC-7222; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E547" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0457 and DEC-7222, not a decision of his — recorded in the decision log as DEC-7309; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B548" s="4" t="inlineStr">
+        <is>
+          <t>Holding editor · the Save button's spoken name · DEC-7310</t>
+        </is>
+      </c>
+      <c r="C548" s="4" t="inlineStr">
+        <is>
+          <t>The Save holding button keeps the spoken name voice control and tests find it by; what the holding cost is read as a hint after it. To reverse: put the cost in the name. Test: performance_spoken_and_agree_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D548" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E548" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7310; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B549" s="4" t="inlineStr">
+        <is>
+          <t>Performance · the photograph test's spoken lines · DEC-7311</t>
+        </is>
+      </c>
+      <c r="C549" s="4" t="inlineStr">
+        <is>
+          <t>The photograph of the Performance tab (photograph_figures, two entries) was updated only by adding the new spoken lines; no printed figure or word in it changed. To reverse: restore the old photograph. Test: performance_spoken_and_agree_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D549" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 2); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E549" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7311; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B550" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Add a buy or sale opens the trade sheet · DEC-7312</t>
+        </is>
+      </c>
+      <c r="C550" s="4" t="inlineStr">
+        <is>
+          <t>The third door under ACTIVITY, Add a buy or sale, opens the trade sheet with the account chosen, for a stock or mixed account: a buy of 10 VTI at $100.00 then lists under ACTIVITY (before: it sent you to the Performance tab, which cannot record a trade). Bonds and alternatives keep their own screens. A 529 gets no third door. To reverse: point the door back at the Performance tab. Test: sheet_doors_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D550" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-6457 and DEC-3523; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E550" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-6457 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7312; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B551" s="4" t="inlineStr">
+        <is>
+          <t>Performance · six sheets with no door removed · DEC-7313</t>
+        </is>
+      </c>
+      <c r="C551" s="4" t="inlineStr">
+        <is>
+          <t>The Performance tab mounted six sheets nothing could open (add a holding, edit a holding, record a transaction, history, the bond editor, the alternatives editor) and the editor's Add a holding mode, which no approved drawing gives a door. They are removed; the tab keeps its one sheet, the three ways to add an account. Holdings are added by a buy, by Itemize or by adding an account. To reverse: restore the mounts and draw a door. Test: sheet_doors_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D551" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0647; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E551" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0647, not a decision of his — recorded in the decision log as DEC-7313; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B552" s="4" t="inlineStr">
+        <is>
+          <t>Holding editor · controls that do what they say · DEC-7314</t>
+        </is>
+      </c>
+      <c r="C552" s="4" t="inlineStr">
+        <is>
+          <t>Tapping a type chip sets the type, and Options asks for contracts (five chips did nothing). The account row shows only the account the holding is in (picking another saved nothing). Private equity and hedge funds are hidden unless the holding is already saved as one (DEC-2334). A 9-character security ID such as 91282CGM7 gets no "doesn't look like a ticker" warning. To reverse: revert the holding editor. Test: sheet_doors_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D552" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-2334 and DEC-3523; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E552" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-2334 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7314; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B553" s="4" t="inlineStr">
+        <is>
+          <t>Trade sheet · keeps the holding's ticker · DEC-7315</t>
+        </is>
+      </c>
+      <c r="C553" s="4" t="inlineStr">
+        <is>
+          <t>Opened from a holding's page, the trade sheet keeps the holding's ticker when it picks the account: AAPL stays (it was wiped as soon as the sheet chose its account). To reverse: revert that line. Test: sheet_doors_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D553" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E553" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7315; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B554" s="4" t="inlineStr">
+        <is>
+          <t>Activity sheet · newest first, its words · DEC-7316</t>
+        </is>
+      </c>
+      <c r="C554" s="4" t="inlineStr">
+        <is>
+          <t>The activity sheet's line reads Every record of this holding, newest first, and the records are sorted that way (it said "Every transaction you've recorded", in stored order). A delete the app refuses shows its alert from the Holding page too. To reverse: revert those lines. Test: sheet_doors_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D554" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0287 and DEC-3523; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E554" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0287 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7316; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B555" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · the recorder's name, case and bar · DEC-7317</t>
+        </is>
+      </c>
+      <c r="C555" s="4" t="inlineStr">
+        <is>
+          <t>The recorder names the account one way everywhere: Deposit — Vanguard Brokerage (it said Deposit — Brokerage). Labels are in sentence case: Coupon received (it read Coupon Received). The dark-green INTO bar runs edge to edge with square corners (it sat inside the sheet's padding). To reverse: revert those lines. Test: sheet_doors_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D555" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0079 and DEC-3523 (tenet 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E555" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0079 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7317; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B556" s="4" t="inlineStr">
+        <is>
+          <t>Activity and edit sheets · dates in one way · DEC-7318</t>
+        </is>
+      </c>
+      <c r="C556" s="4" t="inlineStr">
+        <is>
+          <t>A record's date on the two sheets reads Aug 2, 2026 (it read 2026-08-02), written by MK-ST-F-078 dateShown, the app's one way to write a date. To reverse: revert those lines. Test: sheet_doors_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D556" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E556" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7318; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B557" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · the two buttons' style · DEC-7319</t>
+        </is>
+      </c>
+      <c r="C557" s="4" t="inlineStr">
+        <is>
+          <t>The two buttons take the drawn 1-point edge and sit 4 points below the card (they sat 2 below). To reverse: revert the two style lines. Test: sheet_doors_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D557" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0650; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E557" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0650, not a decision of his — recorded in the decision log as DEC-7319; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B558" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · the rates card's info dot · DEC-7320</t>
+        </is>
+      </c>
+      <c r="C558" s="4" t="inlineStr">
+        <is>
+          <t>The rates card's info dot is drawn at 11 points, matching the drawing and his rule that a dot is the size of its text (it was 13). Found by checking every line's size, weight and colour in state F. To reverse: revert that line. Test: account_page_drawing_states.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D558" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0142 and DEC-0143; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E558" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-0142 and DEC-0143, not a decision of his — recorded in the decision log as DEC-7320; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B559" s="4" t="inlineStr">
+        <is>
+          <t>Info dot · weight, a known difference · DEC-7321</t>
+        </is>
+      </c>
+      <c r="C559" s="4" t="inlineStr">
+        <is>
+          <t>The app draws its one shared info dot at weight 700; the account-page drawing draws it at 400, and the approved drawings disagree among themselves. The dot stays at 700 and the match test lists it as a known difference. To reverse: set the dot's weight to 400. Test: account_page_drawing_states.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D559" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E559" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7321; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B560" s="4" t="inlineStr">
+        <is>
+          <t>Amber box · headline weight, a known difference · DEC-7322</t>
+        </is>
+      </c>
+      <c r="C560" s="4" t="inlineStr">
+        <is>
+          <t>The one shared amber box draws its headline at 800; the account-page drawing's headline is 700. It stays at 800 and the match test lists it as a known difference. To reverse: set its weight to 700. Test: account_page_drawing_states.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D560" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E560" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7322; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B561" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · Home · a gain with shares bought inside the window · DEC-7323</t>
+        </is>
+      </c>
+      <c r="C561" s="4" t="inlineStr">
+        <is>
+          <t>Worked back, a holding's gain is its value plus interest, less what the shares held at the start were worth, less what was paid inside the window. 10 shares held at $100, 10 more at $110, now 20 at $121: gain $320 (before: $420), Beginning $1,000 (before: $900). One household over 1M: Beginning $21,000, Wealth generated −$4,450, Return −14.55% on all three screens (before: $20,550, −$4,000, −13.33%). A purchase with no price paid makes the gain unknown and names the holding. To reverse: delete the paidInside line in gainOfRow. Test: dec3656_shares_added_inside_window.test.ts.</t>
+        </is>
+      </c>
+      <c r="D561" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3656 and DEC-3523 (tenet 3); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E561" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3656 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7323; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B562" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · a category's return split at each purchase · DEC-7324</t>
+        </is>
+      </c>
+      <c r="C562" s="4" t="inlineStr">
+        <is>
+          <t>A class's return, and the return of holdings worked back from prices, is split at every day money went into them, each piece's growth multiplied (returnSplitAtPurchases). The reviewer's A and B read −21.60% (before: −20.00%; weighing by real starts gives −44.55%, which is why it is split). VTI +10% all month beside NEW bought Sep 25 and flat: +10.00% (before: +5.00%). To reverse: remove the path branch in classReturnOf. Test: dec3656_shares_added_inside_window.test.ts.</t>
+        </is>
+      </c>
+      <c r="D562" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-1669; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E562" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-1669, not a decision of his — recorded in the decision log as DEC-7324; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B563" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail v02 · seven READ THIS FIRST rows of 2026-10-21 · DEC-7297</t>
+        </is>
+      </c>
+      <c r="C563" s="4" t="inlineStr">
+        <is>
+          <t>Seven dated lines, the phones not redrawn: the band names its yardstick (VS THE BOND MARKET for a bond); a purchase whose share count is not on record says so on Current value, Quantity and its line; Dividends received is drawn only with a record; a purchase line carries its own unit (2 contracts @ $5.00, 0.5 coins); over 2Y both returns end /year with each window's total said; a price history younger than a month counts days; the band never names a day after the person's today. Account page v01 row 61 says the same of its holding rows. Test: holding_page_comparison_and_unknowns_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D563" s="4" t="inlineStr">
+        <is>
+          <t>Performance launch audit items 4, 5, 6, 34 and the outside re-run part 1 (MK-NW-M-030, -031, -034, -061, F3). Five lines are the lead's decisions; the share-count line applies tenet 3 and DEC-7170.</t>
+        </is>
+      </c>
+      <c r="E563" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-21 under his ruling DEC-1624, DEC-0277, DEC-0189, DEC-0237 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7297 and DEC-7298; written here the same day (written 2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B564" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · a purchase whose share count is not on record</t>
+        </is>
+      </c>
+      <c r="C564" s="4" t="inlineStr">
+        <is>
+          <t>Current value and Quantity say the share count is not on record, in the words Price paid (average) and Total paid already use; the purchase line reads no share count on record @ $210.00. Before, Current value printed a refusal that blamed a missing price under a price of $290.00, and Quantity said every share was sold. Test: holding_page_comparison_and_unknowns_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D564" s="4" t="inlineStr">
+        <is>
+          <t>Found by the outside Performance re-run, part 1 (MK-NW-M-030#3, MK-NW-M-031#3); tenet 3 (unknown is not zero) and DEC-7170 (one wording).</t>
+        </is>
+      </c>
+      <c r="E564" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a fix under existing rulings; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B565" s="4" t="inlineStr">
+        <is>
+          <t>Guards · percents counted, true accessibility numbers, a and an</t>
+        </is>
+      </c>
+      <c r="C565" s="4" t="inlineStr">
+        <is>
+          <t>The figures guard now counts percents as well as dollars and says how many places it read (159 in 89 files; 119 untagged in 27 other files, a number that may only fall). The accessibility baseline carries true counts (the Performance tab 0, not 29; 16 stale lines lowered) and fails when a count is too high or too low. Hand-typed a and an are held by a test (10 left in 8 files, may only fall). Tests: guard_figures_declared.test.ts, a11y_guard.test.ts, article.test.ts.</t>
+        </is>
+      </c>
+      <c r="D565" s="4" t="inlineStr">
+        <is>
+          <t>Performance launch audit items 9, 30 and 31: a guard must prove it looked, and a ratchet carries the true number.</t>
+        </is>
+      </c>
+      <c r="E565" s="4" t="inlineStr">
+        <is>
+          <t>Claude — guards widened to prove they looked; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B566" s="4" t="inlineStr">
+        <is>
+          <t>Performance · one rule for a worked-back return</t>
+        </is>
+      </c>
+      <c r="C566" s="4" t="inlineStr">
+        <is>
+          <t>MK-NW-F-138 knownHoldingsReturn calls classReturnOf, the one function that splits at each purchase, and the second copy of the start choice inside portfolioBenchReturn is gone. No figure moves. Test: dec3656_shares_added_inside_window.test.ts.</t>
+        </is>
+      </c>
+      <c r="D566" s="4" t="inlineStr">
+        <is>
+          <t>The standard already said "the same method" (how an account is classed and counted); one concept, one function.</t>
+        </is>
+      </c>
+      <c r="E566" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a fix under existing rulings; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B567" s="4" t="inlineStr">
+        <is>
+          <t>Design record · five sheets drawn from the code, approval pending</t>
+        </is>
+      </c>
+      <c r="C567" s="4" t="inlineStr">
+        <is>
+          <t>Five drawings made from the built sheets, each with a READ THIS FIRST table and held word for word by sheets_drawn_from_code.test.tsx: the trade sheet (12 states), the holding editor (9), the activity sheet (2), the record-activity sheet (9), the edit-record sheet (3). No approval is recorded; approving them is his. Account page v01 row 62 notes the third door.</t>
+        </is>
+      </c>
+      <c r="D567" s="4" t="inlineStr">
+        <is>
+          <t>Performance launch audit item 24: five sheets had no drawing (DEC-0470: every state drawn).</t>
+        </is>
+      </c>
+      <c r="E567" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a records fix; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B568" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Holding detail · one holding return, one ID · DEC-7369</t>
+        </is>
+      </c>
+      <c r="C568" s="4" t="inlineStr">
+        <is>
+          <t>The account page's holding return (MK-PF-M-023) and the Holding page's Your return (MK-NW-M-069) were one figure under two IDs, worked out by two functions. MK-PF-M-023, the older ID, is kept and now names both pages; MK-NW-M-069 is retired, its number never reused, with the reason in the register's retired block. Both pages read the figure through holdingRowsIn. To reverse: re-issue MK-NW-M-069. Test: holding_return_one_figure_2026_10_22.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D568" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4) and DEC-0402; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E568" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523 and DEC-0402, not a decision of his — recorded in the decision log as DEC-7369; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B569" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · a holding's row reads its own figure · DEC-7370</t>
+        </is>
+      </c>
+      <c r="C569" s="4" t="inlineStr">
+        <is>
+          <t>The account page's holding row now shows what the Holding page shows for the same holding and window. 10 shares bought at $100 on Mar 2 and 10 more at $110 on Jun 1, $121 today, 1Y: the account page read +51.25% (the whole year's price move), the Holding page +21.00%; both read +21.00%. Over 2Y, VTI $240 → $300 over 731 days: both +11.79% a year (the account page showed the +25.00% total beside yearly rates). To reverse: show the whole window's price move again, and the two pages differ. Test: holding_return_one_figure_2026_10_22.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D569" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E569" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7370; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B570" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · the market and gap keep their IDs · DEC-7371</t>
+        </is>
+      </c>
+      <c r="C570" s="4" t="inlineStr">
+        <is>
+          <t>The Holding page's market figure and its gap keep their Net worth IDs, MK-NW-M-070 and MK-NW-M-071; they are not moved into the Performance family. The Performance check already reads the Holding page through MK-PF-M-023, and renumbering would cost two retirements for nothing. To reverse: re-issue both as Performance figures. Test: holding_return_one_figure_2026_10_22.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D570" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E570" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7371; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B571" s="4" t="inlineStr">
+        <is>
+          <t>Guards · the screens-compute-nothing check reads D1 and D1b · DEC-7372</t>
+        </is>
+      </c>
+      <c r="C571" s="4" t="inlineStr">
+        <is>
+          <t>The check that holds his rule that screens compute nothing now reads two guards: D1's list of what a screen imports, and D1b's list of screens that still do arithmetic on figures. It requires no Net worth or Performance screen on D1b's list. Guard D1b reads 6,985 expressions in 150 files, counts what it sets aside, and catches the four sites of 2026-10-22 written as they stood. To reverse: go back to the import check alone. Test: dec0346_screens_compute_nothing.test.ts.</t>
+        </is>
+      </c>
+      <c r="D571" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0346; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E571" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-0346, not a decision of his — recorded in the decision log as DEC-7372; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B572" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · a share count not on record · DEC-7373</t>
+        </is>
+      </c>
+      <c r="C572" s="4" t="inlineStr">
+        <is>
+          <t>Under the holding's name the account page says Not stated — a purchase has no share count on record., the words the Holding page uses. 10 shares at $40 plus a purchase with no count, $50 today: it read 10 shares and $500, and the class band added the $500 in. To reverse: count a purchase with no share count as 0 again. Test: holding_return_one_figure_2026_10_22.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D572" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 3) and DEC-7170; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E572" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523 and DEC-7170, not a decision of his — recorded in the decision log as DEC-7373; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B573" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · the value column says not stated · DEC-7374</t>
+        </is>
+      </c>
+      <c r="C573" s="4" t="inlineStr">
+        <is>
+          <t>The narrow value column holds only the short refusal, not stated, like no price today; the full sentence sits under the holding's name. To reverse: put the full sentence in the column. Test: holding_return_one_figure_2026_10_22.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D573" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 3); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E573" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7374; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B574" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · a class band with an unknown count · DEC-7375</t>
+        </is>
+      </c>
+      <c r="C574" s="4" t="inlineStr">
+        <is>
+          <t>The class band refuses its total when a holding in it has a share count not on record, instead of a total that silently leaves it out; the band's return still shows. To reverse: let classValueOf ignore the flag. Test: holding_return_one_figure_2026_10_22.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D574" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 3); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E574" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7375; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B575" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · one share-count function · DEC-7376</t>
+        </is>
+      </c>
+      <c r="C575" s="4" t="inlineStr">
+        <is>
+          <t>listedShares now uses MK-PF-F-001 totalShares, the function the Holding page uses. A holding with no price and an unknown count therefore counts as an unpriced holding on the account page. To reverse: count the unknown purchase as 0 again. Test: dec0346_screens_compute_nothing.test.ts.</t>
+        </is>
+      </c>
+      <c r="D575" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E575" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7376; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B576" s="4" t="inlineStr">
+        <is>
+          <t>Guards · the date guard reads a record's date; Plan and Income dates in words · DEC-7377</t>
+        </is>
+      </c>
+      <c r="C576" s="4" t="inlineStr">
+        <is>
+          <t>The guard that every stored date is written in words now also reads a record's date field and a date wrapped in String(): 90 files, 54 date mentions, a floor of 50, with self-checks built from the two sheets' old lines; a React key is not flagged. It caught two more raw dates, both fixed: Restores the plan saved 2026-10-01 on Plan, and one-time payments on Income. To reverse: drop the date and String() patterns. Test: date_writer_guard.test.ts.</t>
+        </is>
+      </c>
+      <c r="D576" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E576" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7377; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B577" s="4" t="inlineStr">
+        <is>
+          <t>Look back · each missing ticker named (replaced the same day) · DEC-7378</t>
+        </is>
+      </c>
+      <c r="C577" s="4" t="inlineStr">
+        <is>
+          <t>Look back said, per missing ticker, that a refresh brings it or that the app never fetches it: We don't have prices for AGG or SPY: the app fetches prices only for what you hold and the yardstick each holding is compared with. It read pick a shorter window, which was not true. Replaced within the hour by LB2 of the same day, once Look back fetched its own prices. To reverse: restore the one shared sentence. Test: kept_editors_match.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D577" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 2); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E577" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7378; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B578" s="4" t="inlineStr">
+        <is>
+          <t>Update value sheet · its title names the account · DEC-7379</t>
+        </is>
+      </c>
+      <c r="C578" s="4" t="inlineStr">
+        <is>
+          <t>The sheet's title uses the page's account name (accountDisplayNames): Update value — Ally Savings, where it read Update value — Savings. A holding with no institution reads as before. Drawn as Update value sheet v02. To reverse: go back to the bare label. Test: update_value_sheet_drawing.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D578" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E578" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7379; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B579" s="4" t="inlineStr">
+        <is>
+          <t>Trade sheet · Record activity (canon row 12) · DEC-7380</t>
+        </is>
+      </c>
+      <c r="C579" s="4" t="inlineStr">
+        <is>
+          <t>The records the sheet makes are what every list of them calls activity, so its title reads Record activity, where it read Record a transaction. The old phrase is now in canon row 12's Retired column, so the word guard catches it. Drawn as trade sheet v02. To reverse: remove the entry and the new title. Test: sheets_drawn_from_code.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D579" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0287; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E579" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-0287, not a decision of his — recorded in the decision log as DEC-7380; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B580" s="4" t="inlineStr">
+        <is>
+          <t>Holding editor · Retirement · setup · Settings · Net worth with a small w (canon row 9) · DEC-7381</t>
+        </is>
+      </c>
+      <c r="C580" s="4" t="inlineStr">
+        <is>
+          <t>The tab is Net worth, so Net Worth with a capital W is retired wherever it is written: 33 places in 19 files, 10 of them visible (the holding editor's note, the Retirement page twice, setup five times, a Settings alert, the setup summary title), the rest comments. The guard saw only the phrase open Net Worth or Investments; /\bNet Worth\b/ is now in canon row 9's Retired column. Drawn as holding editor v02. To reverse: remove the entry and the 33 edits. Test: sheets_drawn_from_code.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D580" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0284; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E580" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-0284, not a decision of his — recorded in the decision log as DEC-7381; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B581" s="4" t="inlineStr">
+        <is>
+          <t>Every sheet · one 40% fade for a button that waits · DEC-7382</t>
+        </is>
+      </c>
+      <c r="C581" s="4" t="inlineStr">
+        <is>
+          <t>A button that cannot be pressed yet fades to 40% on every sheet and in the shared Button, as Add an account v02 and Itemize v02 draw it; the edit-record sheet faded to 50%. Fades that mean working (60% and 50% on Import, Connect, Settings delete, the setup check, Tax Organizer share) are left alone. Drawn as edit-record sheet v02. To reverse: two style lines. Test: sheets_drawn_from_code.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D581" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E581" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7382; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B582" s="4" t="inlineStr">
+        <is>
+          <t>Look back · fetches what it compares · DEC-7383</t>
+        </is>
+      </c>
+      <c r="C582" s="4" t="inlineStr">
+        <is>
+          <t>Look back hands the store's one price refresh the tickers it compares — its pairing, SPY and his four yardsticks — when it opens and when the pairing changes; nothing else fetches prices. With nothing held, AGG to SPY: Left in AGG it became $20,500 (up $500, +2.50%); Moved to SPY it would be $23,200 (up $3,200, +16.00%); Difference: $2,700 more if you had moved (before: no answer ever, those tickers were never fetched). To reverse: Look back stops passing tickers. Test: look_back_fetches_what_it_compares.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D582" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-1624; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E582" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-1624, not a decision of his — recorded in the decision log as DEC-7383; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B583" s="4" t="inlineStr">
+        <is>
+          <t>Look back · the waiting and failure lines · DEC-7384</t>
+        </is>
+      </c>
+      <c r="C583" s="4" t="inlineStr">
+        <is>
+          <t>While the refresh runs: Getting prices for AGG and SPY…. If it brings nothing: Couldn't refresh prices for AGG or SPY, so there is nothing to compare yet. Look back tries again each time it opens. If one arrives, the one still missing is named. No figure is printed. Couldn't refresh is the app's wording for a refresh that brought nothing (Home's banner). It replaces SF3 of the same day. To reverse: drop the waiting line. Test: look_back_fetches_what_it_compares.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D583" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 2); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E583" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7384; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B584" s="4" t="inlineStr">
+        <is>
+          <t>Look back · Home · the shared price-refresh failure · DEC-7385</t>
+        </is>
+      </c>
+      <c r="C584" s="4" t="inlineStr">
+        <is>
+          <t>When Look back's refresh brings nothing, the shared failure flag is set and Home's Couldn't refresh banner shows, which is true: the price source gave nothing. A partial success leaves the flag clear. To reverse: give Look back its own flag. Test: look_back_fetches_what_it_compares.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D584" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 2); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E584" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7385; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B585" s="4" t="inlineStr">
+        <is>
+          <t>Home · the gap's own ID, MK-PF-M-027 · DEC-7386</t>
+        </is>
+      </c>
+      <c r="C585" s="4" t="inlineStr">
+        <is>
+          <t>Home's ahead by is the gap for all investments together, so it is MK-PF-M-027; MK-NW-M-071 is one holding's. Both come from one function, marketGap, as the market is split the same way (MK-PF-M-008 for Home, MK-NW-M-070 for a holding). Home now prints you, market and ahead by through MK-XS-M-004, MK-PF-M-008 and MK-PF-M-027, in his Q51 words. To reverse: delete MK-PF-M-027 and reuse 071. Test: perf_decisions_held_4.test.ts.</t>
+        </is>
+      </c>
+      <c r="D585" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0402 and DEC-3523; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E585" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-0402 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7386; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B586" s="4" t="inlineStr">
+        <is>
+          <t>Section bands · spoken words · DEC-7387</t>
+        </is>
+      </c>
+      <c r="C586" s="4" t="inlineStr">
+        <is>
+          <t>A band's spoken words follow its printed ones; it says hidden or a period's words only when the printed band contains a hidden balance or a period. Everything else is said exactly as printed. To reverse: speak bands as printed always. Test: performance_spoken_and_agree_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D586" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 2); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E586" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7387; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B587" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · spoken record dates · DEC-7388</t>
+        </is>
+      </c>
+      <c r="C587" s="4" t="inlineStr">
+        <is>
+          <t>VoiceOver reads a record's date as the screen prints it, Jul 5, 2026, never the stored 2026-07-05. Five tests that pinned the stored form were updated. To reverse: speak the stored date. Test: performance_spoken_and_agree_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D587" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E587" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7388; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B588" s="4" t="inlineStr">
+        <is>
+          <t>Guards · a figure on a second screen needs an agreement test · DEC-7389</t>
+        </is>
+      </c>
+      <c r="C588" s="4" t="inlineStr">
+        <is>
+          <t>The register's list of Performance figures printed on two or more screens must equal the figures the agreement test holds. It caught MK-PF-M-023 once the Holding page printed it; its pin: VTI's month reads +2.46% on both pages ($312.50 ÷ $305.00 − 1). To reverse: delete the check. Test: performance_spoken_and_agree_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D588" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E588" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7389; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B589" s="4" t="inlineStr">
+        <is>
+          <t>Guards · the precision guard's floor 16 · DEC-7390</t>
+        </is>
+      </c>
+      <c r="C589" s="4" t="inlineStr">
+        <is>
+          <t>Home's own percent writer is gone, so one place fewer rounds a figure; the guard's floor is 16, with a dated note. To reverse: raise it to 17. Test: precision_guard.test.ts.</t>
+        </is>
+      </c>
+      <c r="D589" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0264; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E589" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-0264, not a decision of his — recorded in the decision log as DEC-7390; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B590" s="4" t="inlineStr">
+        <is>
+          <t>Home · the month's dollars are MK-PF-M-002 · DEC-7391</t>
+        </is>
+      </c>
+      <c r="C590" s="4" t="inlineStr">
+        <is>
+          <t>The $8,200 of the month on Home's investments card is the same figure as the Performance tab's 1M Wealth generated ($46,600 − $38,400 = $8,200), so it prints and is spoken as MK-PF-M-002, whose screens now include /home. The card's spoken label is built from its printed lines, in order; under hidden balances its dollars say hidden. To reverse: drop /home from MK-PF-M-002 and print it as before. Test: performance_spoken_and_agree_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D590" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0402 and DEC-3523 (tenet 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E590" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-0402 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7391; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B591" s="4" t="inlineStr">
+        <is>
+          <t>Home · the hero card's door, spoken · DEC-7392</t>
+        </is>
+      </c>
+      <c r="C591" s="4" t="inlineStr">
+        <is>
+          <t>VoiceOver reads the hero card as one control, so the door inside it, the line naming a balance not entered, could not be reached. The card now offers it as a spoken action: Fidelity Brokerage has no balance. Opens the Net worth tab — the same route as a tap; with no such line there is no action. To reverse: remove the card's accessibilityActions. Test: performance_spoken_and_agree_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D591" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 2); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E591" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7392; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B592" s="4" t="inlineStr">
+        <is>
+          <t>Master · YOUR ANSWER prints the log's answer · DEC-7393</t>
+        </is>
+      </c>
+      <c r="C592" s="4" t="inlineStr">
+        <is>
+          <t>The build kept its own earlier printing of an answer as if he had typed it, so Q10, Q51, Q52 and Q53 showed frozen text. It now reads back only what he typed and prints the log's current answer; the build names the 4 rows. His 38 cells read word for word. To reverse: limit the reader's fix to ROW VERIFIED. Test: build-moneykeel-master.py.</t>
+        </is>
+      </c>
+      <c r="D592" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0011; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E592" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-0011, not a decision of his — recorded in the decision log as DEC-7393; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B593" s="4" t="inlineStr">
+        <is>
+          <t>Master · a ruled date from a Row status override · DEC-7394</t>
+        </is>
+      </c>
+      <c r="C593" s="4" t="inlineStr">
+        <is>
+          <t>MK-XS-M-004's declaration has no ruled date; its Row status override records his ruling of 2026-09-30, so the build reads the date from it. To reverse: remove _ruled_of in the builder. Test: build-moneykeel-master.py.</t>
+        </is>
+      </c>
+      <c r="D593" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0011; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E593" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-0011, not a decision of his — recorded in the decision log as DEC-7394; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B594" s="4" t="inlineStr">
+        <is>
+          <t>Master · MK-PF-M-008's Row status override retired · DEC-7395</t>
+        </is>
+      </c>
+      <c r="C594" s="4" t="inlineStr">
+        <is>
+          <t>The override said it retires once performance.ts carries the date, and it now does (ruled 2026-09-30, DEC-0640). The override is removed; the earlier file is kept as moneykeel_overrides.before-retire.json in the session's scratchpad. To reverse: restore the override. Test: build-moneykeel-master.py.</t>
+        </is>
+      </c>
+      <c r="D594" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0640; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E594" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-0640, not a decision of his — recorded in the decision log as DEC-7395; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B595" s="4" t="inlineStr">
+        <is>
+          <t>Master · every screen keeps its line · DEC-7396</t>
+        </is>
+      </c>
+      <c r="C595" s="4" t="inlineStr">
+        <is>
+          <t>The 60 screen lines are kept, one per screen, and built from the declared figures: 40 read READ with the figures named, 16 say no figure, 4 are the same screen as /invest, none NOT STARTED. Floors stop the build if the counts collapse. To reverse: drop the lines. Test: build-moneykeel-master.py.</t>
+        </is>
+      </c>
+      <c r="D595" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 2); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E595" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7396; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B596" s="4" t="inlineStr">
+        <is>
+          <t>Master · the capital-gains citation §4.03 · DEC-7397</t>
+        </is>
+      </c>
+      <c r="C596" s="4" t="inlineStr">
+        <is>
+          <t>Found fixing the standard deduction's citation: the capital-gains row named §3.03; the 2026 thresholds are in §4.03. To reverse: restore §3.03. Test: guard_d4_published_sources.test.ts.</t>
+        </is>
+      </c>
+      <c r="D596" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 2); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E596" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7397; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B597" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · Home · a holding's start counts its sales · DEC-7398</t>
+        </is>
+      </c>
+      <c r="C597" s="4" t="inlineStr">
+        <is>
+          <t>Worked back, a holding's start is the shares held when the window began: today's shares, less those bought since, plus those sold since; its gain adds what the sales brought in. 20 held at $100, 10 sold at $110, 10 left at $121: gain $310, beginning $2,000 (before: $210, $2,100). Read off the screens, AAA and BND: Beginning $12,000, Wealth generated $150, Return +1.29% on all three (before: $12,050, $100, +0.91%). Sold out and bought again: $260 from $1,000 (before: $160). If an oldest-first sale may have taken a purchase inside the window that no record sizes, the start is unknown, never guessed. To reverse: stop tradesAfter reading sales. Test: dec3656_shares_added_inside_window.test.ts.</t>
+        </is>
+      </c>
+      <c r="D597" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3656 and DEC-3523 (tenet 3); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E597" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3656 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7398; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B598" s="4" t="inlineStr">
+        <is>
+          <t>Home · the market split on the same days as your return (amends DEC-7221) · DEC-7399</t>
+        </is>
+      </c>
+      <c r="C598" s="4" t="inlineStr">
+        <is>
+          <t>Your return is split on each day money went in, so the market is split on the same days with the same weights. One household: 50 more VTI bought Sep 10; piece 1 ×1, piece 2 (40,000 × 1.10 + 10,000 × 1.04) ÷ 50,000 = ×1.088, so the market is +8.80% (weighed by the starts alone it read +8.00%). VTI $10,000 up 10%, $10,000 more bought Sep 25, the market flat after: +10.00%, level with your return (before: +5.00%, ahead by 5.00%). With no money moved the figure is what DEC-7221 gives. To reverse: delete the new branch in portfolioBenchReturn. Test: dec3656_shares_added_inside_window.test.ts.</t>
+        </is>
+      </c>
+      <c r="D598" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-0595 and DEC-3523 (tenets 1 and 7); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E598" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-0595 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7399; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B599" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · Home · each left-out holding's true reason · DEC-7400</t>
+        </is>
+      </c>
+      <c r="C599" s="4" t="inlineStr">
+        <is>
+          <t>A holding left out because a purchase in the window has no price paid on record is named for that: has a purchase with no price paid on record (canon row 24), where it read has no price history; a sale with no amount gets its own reason. To reverse: make whyLeftOut always return the price-history reason. Test: dec3656_shares_added_inside_window.test.ts.</t>
+        </is>
+      </c>
+      <c r="D599" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 2) and DEC-7170; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E599" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523 and DEC-7170, not a decision of his — recorded in the decision log as DEC-7400; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B600" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · a holding bought inside the window · DEC-7401</t>
+        </is>
+      </c>
+      <c r="C600" s="4" t="inlineStr">
+        <is>
+          <t>A holding first bought inside the window is measured over every purchase and sale in it. If a purchase's price paid is not on record, its gain is unknown and the holding is named (before: counted as $0, silently). To reverse: drop the cappedSince paid branch in gainOfRow. Test: dec3656_shares_added_inside_window.test.ts.</t>
+        </is>
+      </c>
+      <c r="D600" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 3); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E600" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7401; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B601" s="4" t="inlineStr">
+        <is>
+          <t>Master · MK-PF-M-005's refusal says what the screen does · DEC-7402</t>
+        </is>
+      </c>
+      <c r="C601" s="4" t="inlineStr">
+        <is>
+          <t>The declaration's refusal said One account only — the whole walk above already says it, which the screen does not do (a lone account is listed). It now reads: No account line while nothing is entered: the one line and its door stand in their place (Q48). An account is listed once it has a balance above $0 or a holding in it. To reverse: restore the one line at the MK-PF-M-005 declaration in performance.ts. Test: build-moneykeel-master.py.</t>
+        </is>
+      </c>
+      <c r="D601" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 4); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E601" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7402; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B602" s="4" t="inlineStr">
+        <is>
+          <t>Master · Realized from sales has its period · DEC-7403</t>
+        </is>
+      </c>
+      <c r="C602" s="4" t="inlineStr">
+        <is>
+          <t>MK-NW-M-035 sums every sale ever recorded, so its Period column reads every sale on record, to today, where it read as of today. To reverse: remove its period. Test: build-moneykeel-master.py.</t>
+        </is>
+      </c>
+      <c r="D602" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 2); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E602" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7403; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B603" s="4" t="inlineStr">
+        <is>
+          <t>Master · the window picked, from the screen's code · DEC-7404</t>
+        </is>
+      </c>
+      <c r="C603" s="4" t="inlineStr">
+        <is>
+          <t>The walk's title (MK-PF-M-003) declares the window picked, a special period value; the build reads the screen's own window choices from its code and prints them: Over a window. Performance (/invest): picked from Since … · 1M · This year · 1Y · 2Y. Nothing is typed by hand. To reverse: give it a typed period. Test: build-moneykeel-master.py.</t>
+        </is>
+      </c>
+      <c r="D603" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3523 (tenet 2); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E603" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3523, not a decision of his — recorded in the decision log as DEC-7404; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B604" s="4" t="inlineStr">
+        <is>
+          <t>Master · three overrides retired · DEC-7405</t>
+        </is>
+      </c>
+      <c r="C604" s="4" t="inlineStr">
+        <is>
+          <t>Overrides whose declarations now carry the right words are retired, each with a dated CLOSED note, as MK-PF-M-008's Row status was; among them MK-PF-F-003's, which could never be placed because avgCost was retired on 2026-10-12 by his approval DEC-4642. The file as it was is kept in the session's scratchpad (moneykeel_overrides.before-round2.json). To reverse: restore those entries. Test: build-moneykeel-master.py.</t>
+        </is>
+      </c>
+      <c r="D604" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-4642 and DEC-3523; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E604" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-4642 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7405; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B605" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · Trade sheet · a 529 that lists holdings takes a buy or sale · DEC-2484g</t>
+        </is>
+      </c>
+      <c r="C605" s="4" t="inlineStr">
+        <is>
+          <t>A 529 that lists its funds now shows the account page's third door and is offered on the trade sheet; one that lists nothing is not. College fund holding 50 VTSAX: no door before, the trade sheet with that 529 chosen now. The outside reviewers' cases saying a 529 stays refused are marked BRIEF WRONG, each with a pin of the app. Account page v01 row 62; trade sheet v02. Test: sheet_doors_2026_10_21.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D605" s="4" t="inlineStr">
+        <is>
+          <t>His ruling DEC-2484g: "Any account that already lists holdings can take a recorded buy or sale." It replaces the 529 clause of DEC-7312.</t>
+        </is>
+      </c>
+      <c r="E605" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-07) — recorded in the decision log as DEC-2484g; applied here 2026-10-22, written the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B606" s="4" t="inlineStr">
+        <is>
+          <t>Look back · his four yardsticks are fetched · DEC-1624</t>
+        </is>
+      </c>
+      <c r="C606" s="4" t="inlineStr">
+        <is>
+          <t>Look back now fetches what it compares — its pairing, SPY and the four yardsticks he named — so with nothing held it answers: Left in AGG it became $20,500 (up $500, +2.50%); Moved to SPY it would be $23,200; Difference: $2,700 more if you had moved. Before, those tickers were never fetched and Look back could not answer. Look back v01 READ THIS FIRST row of 2026-10-22. Test: look_back_fetches_what_it_compares.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D606" s="4" t="inlineStr">
+        <is>
+          <t>His ruling DEC-1624 offered the four yardsticks; they were never fetched until now (DEC-7383, DEC-7384, DEC-7385).</t>
+        </is>
+      </c>
+      <c r="E606" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-10-04) — recorded in the decision log as DEC-1624; applied here 2026-10-22, written the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B607" s="4" t="inlineStr">
+        <is>
+          <t>Performance v17 · READ THIS FIRST row of 2026-10-22 · 2Y total beside the yearly rate · DEC-0237</t>
+        </is>
+      </c>
+      <c r="C607" s="4" t="inlineStr">
+        <is>
+          <t>A dated line, no drawn figure moves: over 2Y the summary and every account row give the two years' own total beside the yearly rate. His phone-1 household: +7.05% over the two years, which is +3.46%/year (before: +3.46% with no total); E*TRADE return +10.00% over the two years, which is +4.87%/year; Vanguard +6.42% and +3.16%/year. Test: perf_decisions_held_1.test.tsx (the two pins flipped).</t>
+        </is>
+      </c>
+      <c r="D607" s="4" t="inlineStr">
+        <is>
+          <t>His ruling of 2026-09-25 (DEC-0237, DEC-0404): over a year, a yearly rate with the window's own total beside it. It was breached on phone 1 and the account rows.</t>
+        </is>
+      </c>
+      <c r="E607" s="4" t="inlineStr">
+        <is>
+          <t>Founder (Changelog 2026-09-25) — recorded in the decision log as DEC-0237; applied here 2026-10-22, written the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B608" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · drawing v01 row 63 · 2Y total beside the yearly rate · DEC-0404</t>
+        </is>
+      </c>
+      <c r="C608" s="4" t="inlineStr">
+        <is>
+          <t>A dated row, no drawn figure moves: over 2Y, where the window is worked back or joined at the record's first day, the account page gives +21.00% over the two years, which is +9.99%/year, where the yearly rate stood alone under the record line. Test: returns_and_windows_agree.test.tsx (test 7).</t>
+        </is>
+      </c>
+      <c r="D608" s="4" t="inlineStr">
+        <is>
+          <t>His ruling DEC-0404 (with DEC-0237).</t>
+        </is>
+      </c>
+      <c r="E608" s="4" t="inlineStr">
+        <is>
+          <t>Founder (the precision standard, 2026-09-25) — recorded in the decision log as DEC-0404; applied here 2026-10-22, written the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B609" s="4" t="inlineStr">
+        <is>
+          <t>Home · market, you and ahead by printed by ID · DEC-0402</t>
+        </is>
+      </c>
+      <c r="C609" s="4" t="inlineStr">
+        <is>
+          <t>Home prints you, market and ahead by through MK-XS-M-004, MK-PF-M-008 and MK-PF-M-027, in his Q51 words, unchanged on screen; before, Home wrote them with its own percent writer and none could be traced to its declaration. Test: perf_decisions_held_4.test.ts.</t>
+        </is>
+      </c>
+      <c r="D609" s="4" t="inlineStr">
+        <is>
+          <t>His rule 11 steps 1 to 3 (DEC-0402): a screen prints a figure only from its door, by identifier. It was breached on Home.</t>
+        </is>
+      </c>
+      <c r="E609" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-09-14) — recorded in the decision log as DEC-0402; applied here 2026-10-22, written the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B610" s="4" t="inlineStr">
+        <is>
+          <t>Net worth · Performance · Account detail · Holding detail · screens compute nothing · DEC-0346</t>
+        </is>
+      </c>
+      <c r="C610" s="4" t="inlineStr">
+        <is>
+          <t>No Net worth or Performance screen works a figure out any more: the All categories total, the account page's share counts, income sum and class values, the composition bar's split, the Itemize bar's share and a bond taken out of an account are each a function (account page 10 places → 0, Performance tab 3 → 0, Net worth 7 → 0, Itemize 1 → 0, Bonds 1 → 0); the numbers do not change. Guard D1b reads every screen for arithmetic on figures and holds the nine at 0. Tests: dec0346_screens_compute_nothing.test.ts, guard_d1_nobody_in_the_kitchen.test.ts.</t>
+        </is>
+      </c>
+      <c r="D610" s="4" t="inlineStr">
+        <is>
+          <t>His rule of 2026-09-13 (DEC-0346): screens compute nothing. It was breached on five screens.</t>
+        </is>
+      </c>
+      <c r="E610" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-09-13) — recorded in the decision log as DEC-0346; applied here 2026-10-22, written the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B611" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · the 2Y lines read as the other screens' do</t>
+        </is>
+      </c>
+      <c r="C611" s="4" t="inlineStr">
+        <is>
+          <t>Over 2Y the Holding page's two lines with each window's own total now come from the one writer the Performance tab and the account page use, so the three read word for word alike; one word only this page said is gone. The figures do not change. Holding detail v02 READ THIS FIRST row of 2026-10-22. Test: returns_and_windows_agree.test.tsx (section 2).</t>
+        </is>
+      </c>
+      <c r="D611" s="4" t="inlineStr">
+        <is>
+          <t>One sentence, one writer (tenet 4).</t>
+        </is>
+      </c>
+      <c r="E611" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a fix under existing rulings; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B612" s="4" t="inlineStr">
+        <is>
+          <t>Home · Account detail · Performance · the left-out sentence under hidden balances</t>
+        </is>
+      </c>
+      <c r="C612" s="4" t="inlineStr">
+        <is>
+          <t>With balances hidden, the sentence that says what a Return leaves out (Treasury 2031, $10,000) shows dots and says hidden when spoken, on Home, the account page and the Performance tab; it showed its dollars on Home. Test: performance_spoken_and_agree_2026_10_21.test.tsx (section F).</t>
+        </is>
+      </c>
+      <c r="D612" s="4" t="inlineStr">
+        <is>
+          <t>His rule that no dollar is readable with balances hidden (DEC-0013).</t>
+        </is>
+      </c>
+      <c r="E612" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a fix under existing rulings; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B613" s="4" t="inlineStr">
+        <is>
+          <t>Master · ROW VERIFIED and YOUR ANSWER read back only what he typed; stale ruled dates</t>
+        </is>
+      </c>
+      <c r="C613" s="4" t="inlineStr">
+        <is>
+          <t>The master build no longer reads its own sentences back as his marks. MK-PF-M-008 and MK-XS-M-004 read "you ruled on this row 2026-09-30" where they asked RULED? NOT YET; MK-NW-M-002, MK-NW-M-047, MK-PF-M-016 and MK-PF-M-017 now carry the ruled date their Row status gives (2026-10-04); Q10, Q51, Q52 and Q53 print the decision log's current answers. Eight self-checks stop the build if the reader regresses; his 38 cells read word for word.</t>
+        </is>
+      </c>
+      <c r="D613" s="4" t="inlineStr">
+        <is>
+          <t>A guard must prove it looked: the reader trusted any text in his columns.</t>
+        </is>
+      </c>
+      <c r="E613" s="4" t="inlineStr">
+        <is>
+          <t>Claude — the master builder fixed; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B614" s="4" t="inlineStr">
+        <is>
+          <t>Master · the Period column for window and span figures</t>
+        </is>
+      </c>
+      <c r="C614" s="4" t="inlineStr">
+        <is>
+          <t>25 figures over a window now say which windows each screen offers (for example MK-PF-M-017: over a window, picked from Since · 1M · This year · 1Y · 2Y), read from each screen's code; seven span figures say their own period (since purchase, since the previous close, the trailing twelve months, every sale on record). Counts: over a window 26 · own period 6 · a month or a year 50 · as of today 97.</t>
+        </is>
+      </c>
+      <c r="D614" s="4" t="inlineStr">
+        <is>
+          <t>The column said as of today for figures that are not.</t>
+        </is>
+      </c>
+      <c r="E614" s="4" t="inlineStr">
+        <is>
+          <t>Claude — the master builder fixed; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B615" s="4" t="inlineStr">
+        <is>
+          <t>Master · Reference · the standard deduction cites Rev. Proc. 2025-32 §4.14</t>
+        </is>
+      </c>
+      <c r="C615" s="4" t="inlineStr">
+        <is>
+          <t>The register cites §4.14 for the 2026 standard deduction and §§4.01, 4.14 for the tables, read from the IRS document itself (its §2.15 is a reporting threshold); the outside tax file's finding S1 is fixed and its case now passes.</t>
+        </is>
+      </c>
+      <c r="D615" s="4" t="inlineStr">
+        <is>
+          <t>A source must be the right section to be checked (outside re-run, tax file).</t>
+        </is>
+      </c>
+      <c r="E615" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a citation corrected; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B616" s="4" t="inlineStr">
+        <is>
+          <t>Master · MK-PF-M-007's refusal</t>
+        </is>
+      </c>
+      <c r="C616" s="4" t="inlineStr">
+        <is>
+          <t>The category table's total says what the screen does when nothing was received: The table does not appear — nothing was received in this window, where the row printed the $0 line meant for dollar figures on an empty account.</t>
+        </is>
+      </c>
+      <c r="D616" s="4" t="inlineStr">
+        <is>
+          <t>The row must say what the screen does.</t>
+        </is>
+      </c>
+      <c r="E616" s="4" t="inlineStr">
+        <is>
+          <t>Claude — a fix under existing rulings; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B617" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · Home · a holding sold in full inside the window · DEC-7450</t>
+        </is>
+      </c>
+      <c r="C617" s="4" t="inlineStr">
+        <is>
+          <t>A holding sold in full inside the window has no shares today but was held when the window began; its row is built from its sale records (soldOutPositions). 10 held at $100, sold at $110: start $1,000, gained $100 (before: no row, and the beginning read $1,100). AAA sold out Sep 15 at $105 beside BND $10,000: Beginning $12,000, Wealth generated $100, Return +0.83%, market +4.34%, on the Performance tab, the account card, the account page and Home. Its class is that of the same ticker elsewhere, else the account's class, else Unclassified. To reverse: drop the rows soldOutPositions adds. Test: dec3656_shares_added_inside_window.test.ts.</t>
+        </is>
+      </c>
+      <c r="D617" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-3656 and DEC-3523 (tenet 3); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E617" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-3656 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7450; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B618" s="4" t="inlineStr">
+        <is>
+          <t>Performance · Account detail · Home · Holding detail · a holding measured from its trades · DEC-7451</t>
+        </is>
+      </c>
+      <c r="C618" s="4" t="inlineStr">
+        <is>
+          <t>A holding bought or sold inside the window is measured from every trade in it, each counted for its whole day. A purchase counts in at what was paid; a sale counts out at what it brought in after its fee. The market for the shares sold ends at the sale day's own close; for the shares kept, at the previous evening's close. 10 held at $100, sold at $110: +10.00%, gained $100, market +10.00%; with a $5 fee, +9.50% and $95. Bought and sold inside the window: +30.00% (1,100 ÷ 1,000 × 2,400 ÷ 2,200 × 1,300 ÷ 1,200 − 1), market +12.00%, gained $400 (before: +18.18%, market +7.69%). ZZ $500 flat beside the sold X: +6.67% (before: +1.80%). EARLIER WORDING, round 3 of the same day: a sale counted out at the previous evening's value, which gave +8.00% for the first example; replaced within the hour by this rule, so a person can see how the number was made. To reverse: eventPath and marketSplitAtPurchases back to the previous close. Test: dec3656_shares_added_inside_window.test.ts.</t>
+        </is>
+      </c>
+      <c r="D618" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-1669 and DEC-3523 (tenet 2); one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E618" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-1669 and DEC-3523, not a decision of his — recorded in the decision log as DEC-7451; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B619" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail · Performance · a sale's fee counted once · DEC-7452</t>
+        </is>
+      </c>
+      <c r="C619" s="4" t="inlineStr">
+        <is>
+          <t>10 shares sold at $120 with a $5 fee not in the price: the sale brought in $1,195, gained $405, beginning $2,000. At $119.50 with the fee already in the price: $1,195, the fee not taken off again. With no fee on record: 10 × $110 = $1,100, as before. To reverse: drop feeNotInPrice from tradesAfter. Test: dec3656_shares_added_inside_window.test.ts.</t>
+        </is>
+      </c>
+      <c r="D619" s="4" t="inlineStr">
+        <is>
+          <t>Decided without asking him under DEC-6873 and DEC-6874; one word from him reverses it.</t>
+        </is>
+      </c>
+      <c r="E619" s="4" t="inlineStr">
+        <is>
+          <t>Claude (the lead) — decided 2026-10-22 under his ruling DEC-6873 and DEC-6874, not a decision of his — recorded in the decision log as DEC-7452; written here the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B620" s="4" t="inlineStr">
+        <is>
+          <t>Performance v17 · READ THIS FIRST row of 2026-10-22 · holdings sold or bought inside the window</t>
+        </is>
+      </c>
+      <c r="C620" s="4" t="inlineStr">
+        <is>
+          <t>A dated line, no drawn figure moves: a holding sold in full inside the window keeps its row (10 held at $100, sold at $110: start $1,000, gained $100); a holding with trades inside the window is measured from every purchase and sale, a purchase in at what was paid and a sale out at what it brought in after its fee. Tests: dec3656_shares_added_inside_window.test.ts, shares_added_inside_window_agree.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D620" s="4" t="inlineStr">
+        <is>
+          <t>W-START round 3 and its correction (DEC-7450, DEC-7451, DEC-7452).</t>
+        </is>
+      </c>
+      <c r="E620" s="4" t="inlineStr">
+        <is>
+          <t>Claude — the drawing rows of the decisions above; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B621" s="4" t="inlineStr">
+        <is>
+          <t>Account detail · drawing v01 row 67 · holdings sold or bought inside the window</t>
+        </is>
+      </c>
+      <c r="C621" s="4" t="inlineStr">
+        <is>
+          <t>A dated row, no drawn figure moves: the account page's class rows include a holding sold in full inside the window; AAA sold out Sep 15 at $105 beside BND $10,000 reads Beginning $12,000, Wealth generated $100, Return +0.83%. Test: shares_added_inside_window_agree.test.tsx.</t>
+        </is>
+      </c>
+      <c r="D621" s="4" t="inlineStr">
+        <is>
+          <t>W-START round 3 and its correction (DEC-7450, DEC-7451).</t>
+        </is>
+      </c>
+      <c r="E621" s="4" t="inlineStr">
+        <is>
+          <t>Claude — the drawing rows of the decisions above; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B622" s="4" t="inlineStr">
+        <is>
+          <t>Holding detail v02 · READ THIS FIRST row of 2026-10-22 · bought and sold inside the window</t>
+        </is>
+      </c>
+      <c r="C622" s="4" t="inlineStr">
+        <is>
+          <t>A dated row (not a drawn state): a holding bought inside the window that also sold reads its return from every purchase and sale in the window, each counted for its whole day, on this page and on its account's page alike: +30.00% (it read +18.18%, from the shares still held). Reworded after the correction: a purchase in at what was paid, a sale out at what it brought in after its fee. Test: dec3656_shares_added_inside_window.test.ts.</t>
+        </is>
+      </c>
+      <c r="D622" s="4" t="inlineStr">
+        <is>
+          <t>W-START round 3 and its correction (DEC-7451).</t>
+        </is>
+      </c>
+      <c r="E622" s="4" t="inlineStr">
+        <is>
+          <t>Claude — the drawing rows of the decisions above; no ruling of his and no new decision, so no decision-log row</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E499"/>
+  <autoFilter ref="A1:E622"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21084,6 +24405,7 @@
       <c r="D86" s="4" t="n"/>
       <c r="E86" s="4" t="n"/>
     </row>
+    <row r="87"/>
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
         <is>
@@ -23040,6 +26362,7 @@
       <c r="D69" s="4" t="n"/>
       <c r="E69" s="4" t="n"/>
     </row>
+    <row r="70"/>
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
@@ -25924,6 +29247,7 @@
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
@@ -26186,6 +29510,7 @@
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25" ht="46" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
@@ -26411,6 +29736,7 @@
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34" ht="46" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
@@ -26697,6 +30023,7 @@
       <c r="D43" s="4" t="n"/>
       <c r="E43" s="4" t="n"/>
     </row>
+    <row r="44"/>
     <row r="45" ht="46" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
@@ -26923,6 +30250,7 @@
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="n"/>
     </row>
+    <row r="53"/>
     <row r="54" ht="46" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
@@ -27093,6 +30421,7 @@
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="n"/>
     </row>
+    <row r="60"/>
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
@@ -27733,6 +31062,7 @@
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
